--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -62871,7 +62871,7 @@
         <v>3722</v>
       </c>
       <c r="C2718" t="n">
-        <v>1.83000004291534</v>
+        <v>1.8400000333786</v>
       </c>
       <c r="D2718" t="n">
         <v>1.79200005531311</v>
@@ -62883,6 +62883,29 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>1055</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>1.83399999141693</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>1.83399999141693</v>
+      </c>
+      <c r="G2719" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>1583</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>1.83599996566772</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>1.7960000038147</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>1.7960000038147</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>1.84800004959106</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -62917,7 +62917,7 @@
         <v>1583</v>
       </c>
       <c r="C2720" t="n">
-        <v>1.83599996566772</v>
+        <v>1.84800004959106</v>
       </c>
       <c r="D2720" t="n">
         <v>1.7960000038147</v>
@@ -62929,6 +62929,29 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>11491</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>1.8400000333786</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>1.79799997806549</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>1.83800005912781</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>1.83000004291534</v>
+      </c>
+      <c r="G2721" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>3251</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>1.80200004577637</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>1.80200004577637</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>17589</v>
+        <v>6617</v>
       </c>
       <c r="C2715" t="n">
-        <v>1.85000002384186</v>
+        <v>1.86000001430511</v>
       </c>
       <c r="D2715" t="n">
-        <v>1.80400002002716</v>
+        <v>1.83599996566772</v>
       </c>
       <c r="E2715" t="n">
-        <v>1.85000002384186</v>
+        <v>1.83800005912781</v>
       </c>
       <c r="F2715" t="n">
-        <v>1.85000002384186</v>
+        <v>1.8400000333786</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>12318</v>
+        <v>17589</v>
       </c>
       <c r="C2716" t="n">
-        <v>1.82000005245209</v>
+        <v>1.85000002384186</v>
       </c>
       <c r="D2716" t="n">
-        <v>1.7940000295639</v>
+        <v>1.80400002002716</v>
       </c>
       <c r="E2716" t="n">
-        <v>1.82000005245209</v>
+        <v>1.85000002384186</v>
       </c>
       <c r="F2716" t="n">
-        <v>1.80200004577637</v>
+        <v>1.85000002384186</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>65886</v>
+        <v>12318</v>
       </c>
       <c r="C2717" t="n">
-        <v>1.80999994277954</v>
+        <v>1.82000005245209</v>
       </c>
       <c r="D2717" t="n">
-        <v>1.71000003814697</v>
+        <v>1.7940000295639</v>
       </c>
       <c r="E2717" t="n">
-        <v>1.78999996185303</v>
+        <v>1.82000005245209</v>
       </c>
       <c r="F2717" t="n">
-        <v>1.80999994277954</v>
+        <v>1.80200004577637</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>3722</v>
+        <v>65886</v>
       </c>
       <c r="C2718" t="n">
-        <v>1.8400000333786</v>
+        <v>1.80999994277954</v>
       </c>
       <c r="D2718" t="n">
-        <v>1.79200005531311</v>
+        <v>1.71000003814697</v>
       </c>
       <c r="E2718" t="n">
-        <v>1.83000004291534</v>
+        <v>1.78999996185303</v>
       </c>
       <c r="F2718" t="n">
-        <v>1.8400000333786</v>
+        <v>1.80999994277954</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>1055</v>
+        <v>3722</v>
       </c>
       <c r="C2719" t="n">
-        <v>1.83399999141693</v>
+        <v>1.8400000333786</v>
       </c>
       <c r="D2719" t="n">
-        <v>1.79999995231628</v>
+        <v>1.79200005531311</v>
       </c>
       <c r="E2719" t="n">
-        <v>1.79999995231628</v>
+        <v>1.83000004291534</v>
       </c>
       <c r="F2719" t="n">
-        <v>1.83399999141693</v>
+        <v>1.8400000333786</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>1583</v>
+        <v>1055</v>
       </c>
       <c r="C2720" t="n">
-        <v>1.84800004959106</v>
+        <v>1.83399999141693</v>
       </c>
       <c r="D2720" t="n">
-        <v>1.7960000038147</v>
+        <v>1.79999995231628</v>
       </c>
       <c r="E2720" t="n">
-        <v>1.7960000038147</v>
+        <v>1.79999995231628</v>
       </c>
       <c r="F2720" t="n">
-        <v>1.84800004959106</v>
+        <v>1.83399999141693</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>11491</v>
+        <v>1583</v>
       </c>
       <c r="C2721" t="n">
-        <v>1.8400000333786</v>
+        <v>1.84800004959106</v>
       </c>
       <c r="D2721" t="n">
-        <v>1.79799997806549</v>
+        <v>1.7960000038147</v>
       </c>
       <c r="E2721" t="n">
-        <v>1.83800005912781</v>
+        <v>1.7960000038147</v>
       </c>
       <c r="F2721" t="n">
-        <v>1.83000004291534</v>
+        <v>1.84800004959106</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>3251</v>
+        <v>11491</v>
       </c>
       <c r="C2722" t="n">
-        <v>1.80200004577637</v>
+        <v>1.8400000333786</v>
       </c>
       <c r="D2722" t="n">
-        <v>1.79999995231628</v>
+        <v>1.79799997806549</v>
       </c>
       <c r="E2722" t="n">
-        <v>1.80200004577637</v>
+        <v>1.83800005912781</v>
       </c>
       <c r="F2722" t="n">
-        <v>1.79999995231628</v>
+        <v>1.83000004291534</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>1543</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>1.82599997520447</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>1.7960000038147</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>1.82599997520447</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>1.7960000038147</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -71277,6 +71277,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>21250</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>1.80200004577637</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>1.7960000038147</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>1.7960000038147</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>1.80200004577637</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>1.80200004577637</v>
+      </c>
+      <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -473,7 +473,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G4" t="n">
-        <v>0.905705690383911</v>
+        <v>0.905705749988556</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G5" t="n">
-        <v>0.845978140830994</v>
+        <v>0.845978081226349</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>0.838500022888184</v>
       </c>
       <c r="G7" t="n">
-        <v>0.821010053157806</v>
+        <v>0.821009993553162</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G9" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G13" t="n">
-        <v>0.704981803894043</v>
+        <v>0.704981744289398</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G15" t="n">
-        <v>0.741699516773224</v>
+        <v>0.741699576377869</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G17" t="n">
-        <v>0.805833280086517</v>
+        <v>0.805833339691162</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>0.799499988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>0.782823443412781</v>
+        <v>0.782823503017426</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G19" t="n">
-        <v>0.769605040550232</v>
+        <v>0.769605100154877</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G28" t="n">
-        <v>0.741699516773224</v>
+        <v>0.741699576377869</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G35" t="n">
-        <v>0.846957206726074</v>
+        <v>0.846957266330719</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G36" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G52" t="n">
-        <v>0.814645528793335</v>
+        <v>0.81464558839798</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G53" t="n">
-        <v>0.820520401000977</v>
+        <v>0.820520460605621</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G58" t="n">
-        <v>0.862623512744904</v>
+        <v>0.862623453140259</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G59" t="n">
-        <v>0.840103209018707</v>
+        <v>0.840103268623352</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G63" t="n">
-        <v>0.829332649707794</v>
+        <v>0.829332709312439</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G65" t="n">
-        <v>0.829332649707794</v>
+        <v>0.829332709312439</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G67" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>0.847500026226044</v>
       </c>
       <c r="G69" t="n">
-        <v>0.829822301864624</v>
+        <v>0.829822242259979</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G79" t="n">
-        <v>0.810239434242249</v>
+        <v>0.810239374637604</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G80" t="n">
-        <v>0.808770716190338</v>
+        <v>0.808770656585693</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G81" t="n">
-        <v>0.810239434242249</v>
+        <v>0.810239374637604</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G82" t="n">
-        <v>0.808770716190338</v>
+        <v>0.808770656585693</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G93" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>0.863499999046326</v>
       </c>
       <c r="G97" t="n">
-        <v>0.845488488674164</v>
+        <v>0.845488548278809</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G98" t="n">
-        <v>0.842061519622803</v>
+        <v>0.842061579227448</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G111" t="n">
-        <v>0.906684875488281</v>
+        <v>0.906684815883636</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G114" t="n">
-        <v>0.910601437091827</v>
+        <v>0.910601377487183</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>0.927500009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>0.908153533935547</v>
+        <v>0.908153593540192</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>0.905216157436371</v>
+        <v>0.905216097831726</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G125" t="n">
-        <v>0.90081000328064</v>
+        <v>0.900810062885284</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G132" t="n">
-        <v>0.877310693264008</v>
+        <v>0.877310633659363</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G135" t="n">
-        <v>0.899830937385559</v>
+        <v>0.899830877780914</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G141" t="n">
-        <v>0.910601437091827</v>
+        <v>0.910601377487183</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G142" t="n">
-        <v>0.930184245109558</v>
+        <v>0.930184185504913</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G145" t="n">
-        <v>0.910601437091827</v>
+        <v>0.910601377487183</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G148" t="n">
-        <v>0.905705690383911</v>
+        <v>0.905705749988556</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>0.912500023841858</v>
       </c>
       <c r="G149" t="n">
-        <v>0.893466413021088</v>
+        <v>0.893466472625732</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>0.918500006198883</v>
       </c>
       <c r="G158" t="n">
-        <v>0.899341285228729</v>
+        <v>0.899341344833374</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G160" t="n">
-        <v>0.899830937385559</v>
+        <v>0.899830877780914</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>0.907000005245209</v>
       </c>
       <c r="G162" t="n">
-        <v>0.888081133365631</v>
+        <v>0.888081192970276</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G174" t="n">
-        <v>0.889060318470001</v>
+        <v>0.889060258865356</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>0.911499977111816</v>
       </c>
       <c r="G175" t="n">
-        <v>0.892487287521362</v>
+        <v>0.892487227916718</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G178" t="n">
-        <v>0.98893266916275</v>
+        <v>0.988932728767395</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G179" t="n">
-        <v>1.01243221759796</v>
+        <v>1.01243209838867</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G181" t="n">
-        <v>0.978162169456482</v>
+        <v>0.978162229061127</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G183" t="n">
-        <v>0.949767112731934</v>
+        <v>0.949767053127289</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G184" t="n">
-        <v>0.965433299541473</v>
+        <v>0.965433359146118</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G185" t="n">
-        <v>0.978162169456482</v>
+        <v>0.978162229061127</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G192" t="n">
-        <v>0.963475048542023</v>
+        <v>0.963475108146667</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G193" t="n">
-        <v>0.963475048542023</v>
+        <v>0.963475108146667</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G196" t="n">
-        <v>0.97081857919693</v>
+        <v>0.970818638801575</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G197" t="n">
-        <v>0.978162169456482</v>
+        <v>0.978162229061127</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G201" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>0.989000022411346</v>
       </c>
       <c r="G205" t="n">
-        <v>0.968370735645294</v>
+        <v>0.968370795249939</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>0.984499990940094</v>
       </c>
       <c r="G207" t="n">
-        <v>0.963964641094208</v>
+        <v>0.963964581489563</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>0.988499999046326</v>
       </c>
       <c r="G213" t="n">
-        <v>0.967881202697754</v>
+        <v>0.967881143093109</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G215" t="n">
-        <v>0.984037041664124</v>
+        <v>0.984036982059479</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G216" t="n">
-        <v>0.97081857919693</v>
+        <v>0.970818638801575</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G222" t="n">
-        <v>0.949767112731934</v>
+        <v>0.949767053127289</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G224" t="n">
-        <v>0.941933929920197</v>
+        <v>0.941933989524841</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G225" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G226" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G227" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G229" t="n">
-        <v>0.90374743938446</v>
+        <v>0.903747379779816</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G232" t="n">
-        <v>0.905216157436371</v>
+        <v>0.905216097831726</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G236" t="n">
-        <v>0.90276825428009</v>
+        <v>0.902768313884735</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G237" t="n">
-        <v>0.90276825428009</v>
+        <v>0.902768313884735</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G238" t="n">
-        <v>0.905216157436371</v>
+        <v>0.905216097831726</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G251" t="n">
-        <v>0.910601437091827</v>
+        <v>0.910601377487183</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G252" t="n">
-        <v>0.899830937385559</v>
+        <v>0.899830877780914</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G253" t="n">
-        <v>0.90081000328064</v>
+        <v>0.900810062885284</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>0.938499987125397</v>
       </c>
       <c r="G255" t="n">
-        <v>0.91892409324646</v>
+        <v>0.918924152851105</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G258" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G260" t="n">
-        <v>0.932142496109009</v>
+        <v>0.932142555713654</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>0.989000022411346</v>
       </c>
       <c r="G262" t="n">
-        <v>0.968370735645294</v>
+        <v>0.968370795249939</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G266" t="n">
-        <v>0.956621050834656</v>
+        <v>0.956621110439301</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G269" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>0.956621050834656</v>
+        <v>0.956621110439301</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G279" t="n">
-        <v>0.949767112731934</v>
+        <v>0.949767053127289</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>0.987500011920929</v>
       </c>
       <c r="G281" t="n">
-        <v>0.966902017593384</v>
+        <v>0.966902077198029</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>0.956621050834656</v>
+        <v>0.956621110439301</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G284" t="n">
-        <v>0.965433299541473</v>
+        <v>0.965433359146118</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>0.986999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>0.966412484645844</v>
+        <v>0.966412425041199</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G291" t="n">
-        <v>0.983057796955109</v>
+        <v>0.983057856559753</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G292" t="n">
-        <v>0.9869744181633</v>
+        <v>0.986974477767944</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G293" t="n">
-        <v>0.983057796955109</v>
+        <v>0.983057856559753</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G295" t="n">
-        <v>0.98893266916275</v>
+        <v>0.988932728767395</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G298" t="n">
-        <v>0.981099605560303</v>
+        <v>0.981099545955658</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>1.01830685138702</v>
+        <v>1.01830697059631</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G301" t="n">
-        <v>1.05257701873779</v>
+        <v>1.0525768995285</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G302" t="n">
-        <v>1.0829302072525</v>
+        <v>1.08293032646179</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G308" t="n">
-        <v>1.22098910808563</v>
+        <v>1.22098922729492</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G310" t="n">
-        <v>1.31694519519806</v>
+        <v>1.31694507598877</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G311" t="n">
-        <v>1.28267502784729</v>
+        <v>1.28267514705658</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>1.29100000858307</v>
       </c>
       <c r="G312" t="n">
-        <v>1.26407134532928</v>
+        <v>1.26407146453857</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>1.27100002765656</v>
       </c>
       <c r="G313" t="n">
-        <v>1.24448871612549</v>
+        <v>1.2444885969162</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.25</v>
       </c>
       <c r="G315" t="n">
-        <v>1.22392654418945</v>
+        <v>1.22392666339874</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G324" t="n">
-        <v>1.32575726509094</v>
+        <v>1.32575738430023</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>1.35699999332428</v>
       </c>
       <c r="G337" t="n">
-        <v>1.32869470119476</v>
+        <v>1.32869482040405</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G341" t="n">
-        <v>1.40996360778809</v>
+        <v>1.4099634885788</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G343" t="n">
-        <v>1.41975498199463</v>
+        <v>1.41975486278534</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>1.41975498199463</v>
+        <v>1.41975486278534</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G357" t="n">
-        <v>1.48437833786011</v>
+        <v>1.48437821865082</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>1.52746045589447</v>
+        <v>1.52746033668518</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G362" t="n">
-        <v>1.5264812707901</v>
+        <v>1.52648138999939</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G364" t="n">
-        <v>1.57641744613647</v>
+        <v>1.57641756534576</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G366" t="n">
-        <v>1.57445931434631</v>
+        <v>1.57445919513702</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G367" t="n">
-        <v>1.55879294872284</v>
+        <v>1.55879306793213</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G370" t="n">
-        <v>1.49319040775299</v>
+        <v>1.49319052696228</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G375" t="n">
-        <v>1.439337849617</v>
+        <v>1.43933773040771</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G379" t="n">
-        <v>1.48242008686066</v>
+        <v>1.48241996765137</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G381" t="n">
-        <v>1.46675360202789</v>
+        <v>1.46675372123718</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G394" t="n">
-        <v>1.38744330406189</v>
+        <v>1.3874431848526</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G397" t="n">
-        <v>1.46675360202789</v>
+        <v>1.46675372123718</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G411" t="n">
-        <v>1.49416959285736</v>
+        <v>1.49416971206665</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G418" t="n">
-        <v>1.88974273204803</v>
+        <v>1.88974261283875</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G420" t="n">
-        <v>1.94261634349823</v>
+        <v>1.94261622428894</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G423" t="n">
-        <v>1.88974273204803</v>
+        <v>1.88974261283875</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G425" t="n">
-        <v>2.165860414505</v>
+        <v>2.16586065292358</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>2.10515403747559</v>
+        <v>2.10515379905701</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G432" t="n">
-        <v>2.08361291885376</v>
+        <v>2.08361268043518</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G435" t="n">
-        <v>2.25398349761963</v>
+        <v>2.25398325920105</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G438" t="n">
-        <v>2.03857231140137</v>
+        <v>2.03857207298279</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G446" t="n">
-        <v>1.93086659908295</v>
+        <v>1.93086671829224</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G451" t="n">
-        <v>2.0150728225708</v>
+        <v>2.01507306098938</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G452" t="n">
-        <v>2.0150728225708</v>
+        <v>2.01507306098938</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G454" t="n">
-        <v>1.98569869995117</v>
+        <v>1.98569881916046</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G456" t="n">
-        <v>2.00723958015442</v>
+        <v>2.007239818573</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G457" t="n">
-        <v>2.0150728225708</v>
+        <v>2.01507306098938</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G461" t="n">
-        <v>1.98374044895172</v>
+        <v>1.98374032974243</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G462" t="n">
-        <v>1.95632433891296</v>
+        <v>1.95632445812225</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G464" t="n">
-        <v>1.98569869995117</v>
+        <v>1.98569881916046</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>1.93869984149933</v>
+        <v>1.93869972229004</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>1.93869984149933</v>
+        <v>1.93869972229004</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G489" t="n">
-        <v>2.05228018760681</v>
+        <v>2.05227994918823</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G490" t="n">
-        <v>2.00723958015442</v>
+        <v>2.007239818573</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G491" t="n">
-        <v>2.00723958015442</v>
+        <v>2.007239818573</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>1.9778653383255</v>
+        <v>1.97786545753479</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>1.9778653383255</v>
+        <v>1.97786545753479</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G508" t="n">
-        <v>1.93674147129059</v>
+        <v>1.93674159049988</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G513" t="n">
-        <v>1.89953422546387</v>
+        <v>1.89953410625458</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G516" t="n">
-        <v>1.9778653383255</v>
+        <v>1.97786545753479</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G522" t="n">
-        <v>1.95632433891296</v>
+        <v>1.95632445812225</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G523" t="n">
-        <v>1.96807408332825</v>
+        <v>1.96807396411896</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G526" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.10515403747559</v>
+        <v>2.10515379905701</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>2.10515403747559</v>
+        <v>2.10515379905701</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G541" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>2.18348526954651</v>
+        <v>2.18348503112793</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G546" t="n">
-        <v>2.19817209243774</v>
+        <v>2.19817233085632</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G547" t="n">
-        <v>2.18348526954651</v>
+        <v>2.18348503112793</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G548" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G550" t="n">
-        <v>2.19327640533447</v>
+        <v>2.19327664375305</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G551" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>1.80200004577637</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>6711</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>1.80799996852875</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>1.76999998092651</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>1.80599999427795</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>1.76999998092651</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>1.76999998092651</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -473,7 +473,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G4" t="n">
-        <v>0.905705749988556</v>
+        <v>0.905705690383911</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G5" t="n">
-        <v>0.845978081226349</v>
+        <v>0.845978140830994</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>0.838500022888184</v>
       </c>
       <c r="G7" t="n">
-        <v>0.821009993553162</v>
+        <v>0.821010053157806</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G9" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G13" t="n">
-        <v>0.704981744289398</v>
+        <v>0.704981803894043</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G15" t="n">
-        <v>0.741699576377869</v>
+        <v>0.741699516773224</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G17" t="n">
-        <v>0.805833339691162</v>
+        <v>0.805833280086517</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>0.799499988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>0.782823503017426</v>
+        <v>0.782823443412781</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G19" t="n">
-        <v>0.769605100154877</v>
+        <v>0.769605040550232</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G28" t="n">
-        <v>0.741699576377869</v>
+        <v>0.741699516773224</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G35" t="n">
-        <v>0.846957266330719</v>
+        <v>0.846957206726074</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G36" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G52" t="n">
-        <v>0.81464558839798</v>
+        <v>0.814645528793335</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G53" t="n">
-        <v>0.820520460605621</v>
+        <v>0.820520401000977</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G58" t="n">
-        <v>0.862623453140259</v>
+        <v>0.862623512744904</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G59" t="n">
-        <v>0.840103268623352</v>
+        <v>0.840103209018707</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G63" t="n">
-        <v>0.829332709312439</v>
+        <v>0.829332649707794</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G65" t="n">
-        <v>0.829332709312439</v>
+        <v>0.829332649707794</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G67" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>0.847500026226044</v>
       </c>
       <c r="G69" t="n">
-        <v>0.829822242259979</v>
+        <v>0.829822301864624</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G79" t="n">
-        <v>0.810239374637604</v>
+        <v>0.810239434242249</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G80" t="n">
-        <v>0.808770656585693</v>
+        <v>0.808770716190338</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G81" t="n">
-        <v>0.810239374637604</v>
+        <v>0.810239434242249</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G82" t="n">
-        <v>0.808770656585693</v>
+        <v>0.808770716190338</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G93" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>0.863499999046326</v>
       </c>
       <c r="G97" t="n">
-        <v>0.845488548278809</v>
+        <v>0.845488488674164</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G98" t="n">
-        <v>0.842061579227448</v>
+        <v>0.842061519622803</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G111" t="n">
-        <v>0.906684815883636</v>
+        <v>0.906684875488281</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G114" t="n">
-        <v>0.910601377487183</v>
+        <v>0.910601437091827</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>0.927500009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>0.908153593540192</v>
+        <v>0.908153533935547</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>0.905216097831726</v>
+        <v>0.905216157436371</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G125" t="n">
-        <v>0.900810062885284</v>
+        <v>0.90081000328064</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G132" t="n">
-        <v>0.877310633659363</v>
+        <v>0.877310693264008</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G135" t="n">
-        <v>0.899830877780914</v>
+        <v>0.899830937385559</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G141" t="n">
-        <v>0.910601377487183</v>
+        <v>0.910601437091827</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G142" t="n">
-        <v>0.930184185504913</v>
+        <v>0.930184245109558</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G145" t="n">
-        <v>0.910601377487183</v>
+        <v>0.910601437091827</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G148" t="n">
-        <v>0.905705749988556</v>
+        <v>0.905705690383911</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>0.912500023841858</v>
       </c>
       <c r="G149" t="n">
-        <v>0.893466472625732</v>
+        <v>0.893466413021088</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>0.918500006198883</v>
       </c>
       <c r="G158" t="n">
-        <v>0.899341344833374</v>
+        <v>0.899341285228729</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G160" t="n">
-        <v>0.899830877780914</v>
+        <v>0.899830937385559</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>0.907000005245209</v>
       </c>
       <c r="G162" t="n">
-        <v>0.888081192970276</v>
+        <v>0.888081133365631</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G174" t="n">
-        <v>0.889060258865356</v>
+        <v>0.889060318470001</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>0.911499977111816</v>
       </c>
       <c r="G175" t="n">
-        <v>0.892487227916718</v>
+        <v>0.892487287521362</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G178" t="n">
-        <v>0.988932728767395</v>
+        <v>0.98893266916275</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G179" t="n">
-        <v>1.01243209838867</v>
+        <v>1.01243221759796</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G181" t="n">
-        <v>0.978162229061127</v>
+        <v>0.978162169456482</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G183" t="n">
-        <v>0.949767053127289</v>
+        <v>0.949767112731934</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G184" t="n">
-        <v>0.965433359146118</v>
+        <v>0.965433299541473</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G185" t="n">
-        <v>0.978162229061127</v>
+        <v>0.978162169456482</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G192" t="n">
-        <v>0.963475108146667</v>
+        <v>0.963475048542023</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G193" t="n">
-        <v>0.963475108146667</v>
+        <v>0.963475048542023</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G196" t="n">
-        <v>0.970818638801575</v>
+        <v>0.97081857919693</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G197" t="n">
-        <v>0.978162229061127</v>
+        <v>0.978162169456482</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G201" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>0.989000022411346</v>
       </c>
       <c r="G205" t="n">
-        <v>0.968370795249939</v>
+        <v>0.968370735645294</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>0.984499990940094</v>
       </c>
       <c r="G207" t="n">
-        <v>0.963964581489563</v>
+        <v>0.963964641094208</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>0.988499999046326</v>
       </c>
       <c r="G213" t="n">
-        <v>0.967881143093109</v>
+        <v>0.967881202697754</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G215" t="n">
-        <v>0.984036982059479</v>
+        <v>0.984037041664124</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G216" t="n">
-        <v>0.970818638801575</v>
+        <v>0.97081857919693</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G222" t="n">
-        <v>0.949767053127289</v>
+        <v>0.949767112731934</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G224" t="n">
-        <v>0.941933989524841</v>
+        <v>0.941933929920197</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G225" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G226" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G227" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G229" t="n">
-        <v>0.903747379779816</v>
+        <v>0.90374743938446</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G232" t="n">
-        <v>0.905216097831726</v>
+        <v>0.905216157436371</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G236" t="n">
-        <v>0.902768313884735</v>
+        <v>0.90276825428009</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G237" t="n">
-        <v>0.902768313884735</v>
+        <v>0.90276825428009</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G238" t="n">
-        <v>0.905216097831726</v>
+        <v>0.905216157436371</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G251" t="n">
-        <v>0.910601377487183</v>
+        <v>0.910601437091827</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G252" t="n">
-        <v>0.899830877780914</v>
+        <v>0.899830937385559</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G253" t="n">
-        <v>0.900810062885284</v>
+        <v>0.90081000328064</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>0.938499987125397</v>
       </c>
       <c r="G255" t="n">
-        <v>0.918924152851105</v>
+        <v>0.91892409324646</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G258" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G260" t="n">
-        <v>0.932142555713654</v>
+        <v>0.932142496109009</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>0.989000022411346</v>
       </c>
       <c r="G262" t="n">
-        <v>0.968370795249939</v>
+        <v>0.968370735645294</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G266" t="n">
-        <v>0.956621110439301</v>
+        <v>0.956621050834656</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G269" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>0.956621110439301</v>
+        <v>0.956621050834656</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G279" t="n">
-        <v>0.949767053127289</v>
+        <v>0.949767112731934</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>0.987500011920929</v>
       </c>
       <c r="G281" t="n">
-        <v>0.966902077198029</v>
+        <v>0.966902017593384</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>0.956621110439301</v>
+        <v>0.956621050834656</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G284" t="n">
-        <v>0.965433359146118</v>
+        <v>0.965433299541473</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>0.986999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>0.966412425041199</v>
+        <v>0.966412484645844</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G291" t="n">
-        <v>0.983057856559753</v>
+        <v>0.983057796955109</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G292" t="n">
-        <v>0.986974477767944</v>
+        <v>0.9869744181633</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G293" t="n">
-        <v>0.983057856559753</v>
+        <v>0.983057796955109</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G295" t="n">
-        <v>0.988932728767395</v>
+        <v>0.98893266916275</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G298" t="n">
-        <v>0.981099545955658</v>
+        <v>0.981099605560303</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>1.01830697059631</v>
+        <v>1.01830685138702</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G301" t="n">
-        <v>1.0525768995285</v>
+        <v>1.05257701873779</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G302" t="n">
-        <v>1.08293032646179</v>
+        <v>1.0829302072525</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G308" t="n">
-        <v>1.22098922729492</v>
+        <v>1.22098910808563</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G310" t="n">
-        <v>1.31694507598877</v>
+        <v>1.31694519519806</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G311" t="n">
-        <v>1.28267514705658</v>
+        <v>1.28267502784729</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>1.29100000858307</v>
       </c>
       <c r="G312" t="n">
-        <v>1.26407146453857</v>
+        <v>1.26407134532928</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>1.27100002765656</v>
       </c>
       <c r="G313" t="n">
-        <v>1.2444885969162</v>
+        <v>1.24448871612549</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.25</v>
       </c>
       <c r="G315" t="n">
-        <v>1.22392666339874</v>
+        <v>1.22392654418945</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G324" t="n">
-        <v>1.32575738430023</v>
+        <v>1.32575726509094</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>1.35699999332428</v>
       </c>
       <c r="G337" t="n">
-        <v>1.32869482040405</v>
+        <v>1.32869470119476</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G341" t="n">
-        <v>1.4099634885788</v>
+        <v>1.40996360778809</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G343" t="n">
-        <v>1.41975486278534</v>
+        <v>1.41975498199463</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>1.41975486278534</v>
+        <v>1.41975498199463</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G357" t="n">
-        <v>1.48437821865082</v>
+        <v>1.48437833786011</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>1.52746033668518</v>
+        <v>1.52746045589447</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G362" t="n">
-        <v>1.52648138999939</v>
+        <v>1.5264812707901</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G364" t="n">
-        <v>1.57641756534576</v>
+        <v>1.57641744613647</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G366" t="n">
-        <v>1.57445919513702</v>
+        <v>1.57445931434631</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G367" t="n">
-        <v>1.55879306793213</v>
+        <v>1.55879294872284</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G370" t="n">
-        <v>1.49319052696228</v>
+        <v>1.49319040775299</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G375" t="n">
-        <v>1.43933773040771</v>
+        <v>1.439337849617</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G379" t="n">
-        <v>1.48241996765137</v>
+        <v>1.48242008686066</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G381" t="n">
-        <v>1.46675372123718</v>
+        <v>1.46675360202789</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G394" t="n">
-        <v>1.3874431848526</v>
+        <v>1.38744330406189</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G397" t="n">
-        <v>1.46675372123718</v>
+        <v>1.46675360202789</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G411" t="n">
-        <v>1.49416971206665</v>
+        <v>1.49416959285736</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G418" t="n">
-        <v>1.88974261283875</v>
+        <v>1.88974273204803</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G420" t="n">
-        <v>1.94261622428894</v>
+        <v>1.94261634349823</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G423" t="n">
-        <v>1.88974261283875</v>
+        <v>1.88974273204803</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G425" t="n">
-        <v>2.16586065292358</v>
+        <v>2.165860414505</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>2.10515379905701</v>
+        <v>2.10515403747559</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G432" t="n">
-        <v>2.08361268043518</v>
+        <v>2.08361291885376</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G435" t="n">
-        <v>2.25398325920105</v>
+        <v>2.25398349761963</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G438" t="n">
-        <v>2.03857207298279</v>
+        <v>2.03857231140137</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G446" t="n">
-        <v>1.93086671829224</v>
+        <v>1.93086659908295</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G451" t="n">
-        <v>2.01507306098938</v>
+        <v>2.0150728225708</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G452" t="n">
-        <v>2.01507306098938</v>
+        <v>2.0150728225708</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G454" t="n">
-        <v>1.98569881916046</v>
+        <v>1.98569869995117</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G456" t="n">
-        <v>2.007239818573</v>
+        <v>2.00723958015442</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G457" t="n">
-        <v>2.01507306098938</v>
+        <v>2.0150728225708</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G461" t="n">
-        <v>1.98374032974243</v>
+        <v>1.98374044895172</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G462" t="n">
-        <v>1.95632445812225</v>
+        <v>1.95632433891296</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G464" t="n">
-        <v>1.98569881916046</v>
+        <v>1.98569869995117</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>1.93869972229004</v>
+        <v>1.93869984149933</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>1.93869972229004</v>
+        <v>1.93869984149933</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G489" t="n">
-        <v>2.05227994918823</v>
+        <v>2.05228018760681</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G490" t="n">
-        <v>2.007239818573</v>
+        <v>2.00723958015442</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G491" t="n">
-        <v>2.007239818573</v>
+        <v>2.00723958015442</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>1.97786545753479</v>
+        <v>1.9778653383255</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>1.97786545753479</v>
+        <v>1.9778653383255</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G508" t="n">
-        <v>1.93674159049988</v>
+        <v>1.93674147129059</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G513" t="n">
-        <v>1.89953410625458</v>
+        <v>1.89953422546387</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G516" t="n">
-        <v>1.97786545753479</v>
+        <v>1.9778653383255</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G522" t="n">
-        <v>1.95632445812225</v>
+        <v>1.95632433891296</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G523" t="n">
-        <v>1.96807396411896</v>
+        <v>1.96807408332825</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G526" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.10515379905701</v>
+        <v>2.10515403747559</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>2.10515379905701</v>
+        <v>2.10515403747559</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G541" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>2.18348503112793</v>
+        <v>2.18348526954651</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G546" t="n">
-        <v>2.19817233085632</v>
+        <v>2.19817209243774</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G547" t="n">
-        <v>2.18348503112793</v>
+        <v>2.18348526954651</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G548" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G550" t="n">
-        <v>2.19327664375305</v>
+        <v>2.19327640533447</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G551" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>1.76999998092651</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>26518</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>1.79799997806549</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>1.79799997806549</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -63265,13 +63265,36 @@
         <v>1.81599998474121</v>
       </c>
       <c r="D2735" t="n">
-        <v>1.77199995517731</v>
+        <v>1.76999998092651</v>
       </c>
       <c r="E2735" t="n">
         <v>1.81400001049042</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>1.76999998092651</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>38903</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>1.79799997806549</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>1.76800000667572</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>1.78999996185303</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -63285,7 +63285,7 @@
         <v>38903</v>
       </c>
       <c r="C2736" t="n">
-        <v>1.79799997806549</v>
+        <v>1.79999995231628</v>
       </c>
       <c r="D2736" t="n">
         <v>1.76800000667572</v>
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>1.78999996185303</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>1.79999995231628</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>17125</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>1.81400001049042</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>1.76800000667572</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>1.76999998092651</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -63311,13 +63311,36 @@
         <v>1.81400001049042</v>
       </c>
       <c r="D2737" t="n">
-        <v>1.76800000667572</v>
+        <v>1.76600003242493</v>
       </c>
       <c r="E2737" t="n">
         <v>1.76999998092651</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>1.76600003242493</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>59051</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>1.817999958992</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>1.72800004482269</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>1.76600003242493</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>1.76600003242493</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>1.817999958992</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>4310</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>1.817999958992</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>1.77199995517731</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>1.817999958992</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>69295</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>1.91799998283386</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>1.87399995326996</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -473,7 +473,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G4" t="n">
-        <v>0.905705690383911</v>
+        <v>0.905705749988556</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G5" t="n">
-        <v>0.845978140830994</v>
+        <v>0.845978081226349</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>0.838500022888184</v>
       </c>
       <c r="G7" t="n">
-        <v>0.821010053157806</v>
+        <v>0.821009993553162</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G9" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G13" t="n">
-        <v>0.704981803894043</v>
+        <v>0.704981744289398</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G15" t="n">
-        <v>0.741699516773224</v>
+        <v>0.741699576377869</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G17" t="n">
-        <v>0.805833280086517</v>
+        <v>0.805833339691162</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>0.799499988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>0.782823443412781</v>
+        <v>0.782823503017426</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G19" t="n">
-        <v>0.769605040550232</v>
+        <v>0.769605100154877</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G28" t="n">
-        <v>0.741699516773224</v>
+        <v>0.741699576377869</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G35" t="n">
-        <v>0.846957206726074</v>
+        <v>0.846957266330719</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G36" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G52" t="n">
-        <v>0.814645528793335</v>
+        <v>0.81464558839798</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G53" t="n">
-        <v>0.820520401000977</v>
+        <v>0.820520460605621</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G58" t="n">
-        <v>0.862623512744904</v>
+        <v>0.862623453140259</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G59" t="n">
-        <v>0.840103209018707</v>
+        <v>0.840103268623352</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G63" t="n">
-        <v>0.829332649707794</v>
+        <v>0.829332709312439</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G65" t="n">
-        <v>0.829332649707794</v>
+        <v>0.829332709312439</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G67" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>0.847500026226044</v>
       </c>
       <c r="G69" t="n">
-        <v>0.829822301864624</v>
+        <v>0.829822242259979</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G79" t="n">
-        <v>0.810239434242249</v>
+        <v>0.810239374637604</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G80" t="n">
-        <v>0.808770716190338</v>
+        <v>0.808770656585693</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G81" t="n">
-        <v>0.810239434242249</v>
+        <v>0.810239374637604</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G82" t="n">
-        <v>0.808770716190338</v>
+        <v>0.808770656585693</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G93" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>0.863499999046326</v>
       </c>
       <c r="G97" t="n">
-        <v>0.845488488674164</v>
+        <v>0.845488548278809</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G98" t="n">
-        <v>0.842061519622803</v>
+        <v>0.842061579227448</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G111" t="n">
-        <v>0.906684875488281</v>
+        <v>0.906684815883636</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G114" t="n">
-        <v>0.910601437091827</v>
+        <v>0.910601377487183</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>0.927500009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>0.908153533935547</v>
+        <v>0.908153593540192</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>0.905216157436371</v>
+        <v>0.905216097831726</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G125" t="n">
-        <v>0.90081000328064</v>
+        <v>0.900810062885284</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G132" t="n">
-        <v>0.877310693264008</v>
+        <v>0.877310633659363</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G135" t="n">
-        <v>0.899830937385559</v>
+        <v>0.899830877780914</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G141" t="n">
-        <v>0.910601437091827</v>
+        <v>0.910601377487183</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G142" t="n">
-        <v>0.930184245109558</v>
+        <v>0.930184185504913</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G145" t="n">
-        <v>0.910601437091827</v>
+        <v>0.910601377487183</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G148" t="n">
-        <v>0.905705690383911</v>
+        <v>0.905705749988556</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>0.912500023841858</v>
       </c>
       <c r="G149" t="n">
-        <v>0.893466413021088</v>
+        <v>0.893466472625732</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>0.918500006198883</v>
       </c>
       <c r="G158" t="n">
-        <v>0.899341285228729</v>
+        <v>0.899341344833374</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G160" t="n">
-        <v>0.899830937385559</v>
+        <v>0.899830877780914</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>0.907000005245209</v>
       </c>
       <c r="G162" t="n">
-        <v>0.888081133365631</v>
+        <v>0.888081192970276</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G174" t="n">
-        <v>0.889060318470001</v>
+        <v>0.889060258865356</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>0.911499977111816</v>
       </c>
       <c r="G175" t="n">
-        <v>0.892487287521362</v>
+        <v>0.892487227916718</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G178" t="n">
-        <v>0.98893266916275</v>
+        <v>0.988932728767395</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G179" t="n">
-        <v>1.01243221759796</v>
+        <v>1.01243209838867</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G181" t="n">
-        <v>0.978162169456482</v>
+        <v>0.978162229061127</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G183" t="n">
-        <v>0.949767112731934</v>
+        <v>0.949767053127289</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G184" t="n">
-        <v>0.965433299541473</v>
+        <v>0.965433359146118</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G185" t="n">
-        <v>0.978162169456482</v>
+        <v>0.978162229061127</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G192" t="n">
-        <v>0.963475048542023</v>
+        <v>0.963475108146667</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G193" t="n">
-        <v>0.963475048542023</v>
+        <v>0.963475108146667</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G196" t="n">
-        <v>0.97081857919693</v>
+        <v>0.970818638801575</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G197" t="n">
-        <v>0.978162169456482</v>
+        <v>0.978162229061127</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G201" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>0.989000022411346</v>
       </c>
       <c r="G205" t="n">
-        <v>0.968370735645294</v>
+        <v>0.968370795249939</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>0.984499990940094</v>
       </c>
       <c r="G207" t="n">
-        <v>0.963964641094208</v>
+        <v>0.963964581489563</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>0.988499999046326</v>
       </c>
       <c r="G213" t="n">
-        <v>0.967881202697754</v>
+        <v>0.967881143093109</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G215" t="n">
-        <v>0.984037041664124</v>
+        <v>0.984036982059479</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G216" t="n">
-        <v>0.97081857919693</v>
+        <v>0.970818638801575</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G222" t="n">
-        <v>0.949767112731934</v>
+        <v>0.949767053127289</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G224" t="n">
-        <v>0.941933929920197</v>
+        <v>0.941933989524841</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G225" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G226" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G227" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G229" t="n">
-        <v>0.90374743938446</v>
+        <v>0.903747379779816</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G232" t="n">
-        <v>0.905216157436371</v>
+        <v>0.905216097831726</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G236" t="n">
-        <v>0.90276825428009</v>
+        <v>0.902768313884735</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G237" t="n">
-        <v>0.90276825428009</v>
+        <v>0.902768313884735</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G238" t="n">
-        <v>0.905216157436371</v>
+        <v>0.905216097831726</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G251" t="n">
-        <v>0.910601437091827</v>
+        <v>0.910601377487183</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G252" t="n">
-        <v>0.899830937385559</v>
+        <v>0.899830877780914</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G253" t="n">
-        <v>0.90081000328064</v>
+        <v>0.900810062885284</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>0.938499987125397</v>
       </c>
       <c r="G255" t="n">
-        <v>0.91892409324646</v>
+        <v>0.918924152851105</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G258" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G260" t="n">
-        <v>0.932142496109009</v>
+        <v>0.932142555713654</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>0.989000022411346</v>
       </c>
       <c r="G262" t="n">
-        <v>0.968370735645294</v>
+        <v>0.968370795249939</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G266" t="n">
-        <v>0.956621050834656</v>
+        <v>0.956621110439301</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G269" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>0.956621050834656</v>
+        <v>0.956621110439301</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G279" t="n">
-        <v>0.949767112731934</v>
+        <v>0.949767053127289</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>0.987500011920929</v>
       </c>
       <c r="G281" t="n">
-        <v>0.966902017593384</v>
+        <v>0.966902077198029</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>0.956621050834656</v>
+        <v>0.956621110439301</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G284" t="n">
-        <v>0.965433299541473</v>
+        <v>0.965433359146118</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>0.986999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>0.966412484645844</v>
+        <v>0.966412425041199</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G291" t="n">
-        <v>0.983057796955109</v>
+        <v>0.983057856559753</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G292" t="n">
-        <v>0.9869744181633</v>
+        <v>0.986974477767944</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G293" t="n">
-        <v>0.983057796955109</v>
+        <v>0.983057856559753</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G295" t="n">
-        <v>0.98893266916275</v>
+        <v>0.988932728767395</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G298" t="n">
-        <v>0.981099605560303</v>
+        <v>0.981099545955658</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>1.01830685138702</v>
+        <v>1.01830697059631</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G301" t="n">
-        <v>1.05257701873779</v>
+        <v>1.0525768995285</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G302" t="n">
-        <v>1.0829302072525</v>
+        <v>1.08293032646179</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G308" t="n">
-        <v>1.22098910808563</v>
+        <v>1.22098922729492</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G310" t="n">
-        <v>1.31694519519806</v>
+        <v>1.31694507598877</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G311" t="n">
-        <v>1.28267502784729</v>
+        <v>1.28267514705658</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>1.29100000858307</v>
       </c>
       <c r="G312" t="n">
-        <v>1.26407134532928</v>
+        <v>1.26407146453857</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>1.27100002765656</v>
       </c>
       <c r="G313" t="n">
-        <v>1.24448871612549</v>
+        <v>1.2444885969162</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.25</v>
       </c>
       <c r="G315" t="n">
-        <v>1.22392654418945</v>
+        <v>1.22392666339874</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G324" t="n">
-        <v>1.32575726509094</v>
+        <v>1.32575738430023</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>1.35699999332428</v>
       </c>
       <c r="G337" t="n">
-        <v>1.32869470119476</v>
+        <v>1.32869482040405</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G341" t="n">
-        <v>1.40996360778809</v>
+        <v>1.4099634885788</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G343" t="n">
-        <v>1.41975498199463</v>
+        <v>1.41975486278534</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>1.41975498199463</v>
+        <v>1.41975486278534</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G357" t="n">
-        <v>1.48437833786011</v>
+        <v>1.48437821865082</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>1.52746045589447</v>
+        <v>1.52746033668518</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G362" t="n">
-        <v>1.5264812707901</v>
+        <v>1.52648138999939</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G364" t="n">
-        <v>1.57641744613647</v>
+        <v>1.57641756534576</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G366" t="n">
-        <v>1.57445931434631</v>
+        <v>1.57445919513702</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G367" t="n">
-        <v>1.55879294872284</v>
+        <v>1.55879306793213</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G370" t="n">
-        <v>1.49319040775299</v>
+        <v>1.49319052696228</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G375" t="n">
-        <v>1.439337849617</v>
+        <v>1.43933773040771</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G379" t="n">
-        <v>1.48242008686066</v>
+        <v>1.48241996765137</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G381" t="n">
-        <v>1.46675360202789</v>
+        <v>1.46675372123718</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G394" t="n">
-        <v>1.38744330406189</v>
+        <v>1.3874431848526</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G397" t="n">
-        <v>1.46675360202789</v>
+        <v>1.46675372123718</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G411" t="n">
-        <v>1.49416959285736</v>
+        <v>1.49416971206665</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G418" t="n">
-        <v>1.88974273204803</v>
+        <v>1.88974261283875</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G420" t="n">
-        <v>1.94261634349823</v>
+        <v>1.94261622428894</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G423" t="n">
-        <v>1.88974273204803</v>
+        <v>1.88974261283875</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G425" t="n">
-        <v>2.165860414505</v>
+        <v>2.16586065292358</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>2.10515403747559</v>
+        <v>2.10515379905701</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G432" t="n">
-        <v>2.08361291885376</v>
+        <v>2.08361268043518</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G435" t="n">
-        <v>2.25398349761963</v>
+        <v>2.25398325920105</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G438" t="n">
-        <v>2.03857231140137</v>
+        <v>2.03857207298279</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G446" t="n">
-        <v>1.93086659908295</v>
+        <v>1.93086671829224</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G451" t="n">
-        <v>2.0150728225708</v>
+        <v>2.01507306098938</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G452" t="n">
-        <v>2.0150728225708</v>
+        <v>2.01507306098938</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G454" t="n">
-        <v>1.98569869995117</v>
+        <v>1.98569881916046</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G456" t="n">
-        <v>2.00723958015442</v>
+        <v>2.007239818573</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G457" t="n">
-        <v>2.0150728225708</v>
+        <v>2.01507306098938</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G461" t="n">
-        <v>1.98374044895172</v>
+        <v>1.98374032974243</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G462" t="n">
-        <v>1.95632433891296</v>
+        <v>1.95632445812225</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G464" t="n">
-        <v>1.98569869995117</v>
+        <v>1.98569881916046</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>1.93869984149933</v>
+        <v>1.93869972229004</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>1.93869984149933</v>
+        <v>1.93869972229004</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G489" t="n">
-        <v>2.05228018760681</v>
+        <v>2.05227994918823</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G490" t="n">
-        <v>2.00723958015442</v>
+        <v>2.007239818573</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G491" t="n">
-        <v>2.00723958015442</v>
+        <v>2.007239818573</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>1.9778653383255</v>
+        <v>1.97786545753479</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>1.9778653383255</v>
+        <v>1.97786545753479</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G508" t="n">
-        <v>1.93674147129059</v>
+        <v>1.93674159049988</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G513" t="n">
-        <v>1.89953422546387</v>
+        <v>1.89953410625458</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G516" t="n">
-        <v>1.9778653383255</v>
+        <v>1.97786545753479</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G522" t="n">
-        <v>1.95632433891296</v>
+        <v>1.95632445812225</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G523" t="n">
-        <v>1.96807408332825</v>
+        <v>1.96807396411896</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G526" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.10515403747559</v>
+        <v>2.10515379905701</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>2.10515403747559</v>
+        <v>2.10515379905701</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G541" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>2.18348526954651</v>
+        <v>2.18348503112793</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G546" t="n">
-        <v>2.19817209243774</v>
+        <v>2.19817233085632</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G547" t="n">
-        <v>2.18348526954651</v>
+        <v>2.18348503112793</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G548" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G550" t="n">
-        <v>2.19327640533447</v>
+        <v>2.19327664375305</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G551" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>1.88999998569489</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>44593</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>1.88800001144409</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>1.80799996852875</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>1.88800001144409</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>1.84800004959106</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>1.84800004959106</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -473,7 +473,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G4" t="n">
-        <v>0.905705749988556</v>
+        <v>0.905705690383911</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G5" t="n">
-        <v>0.845978081226349</v>
+        <v>0.845978140830994</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>0.838500022888184</v>
       </c>
       <c r="G7" t="n">
-        <v>0.821009993553162</v>
+        <v>0.821010053157806</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G9" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G13" t="n">
-        <v>0.704981744289398</v>
+        <v>0.704981803894043</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G15" t="n">
-        <v>0.741699576377869</v>
+        <v>0.741699516773224</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G17" t="n">
-        <v>0.805833339691162</v>
+        <v>0.805833280086517</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>0.799499988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>0.782823503017426</v>
+        <v>0.782823443412781</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G19" t="n">
-        <v>0.769605100154877</v>
+        <v>0.769605040550232</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G28" t="n">
-        <v>0.741699576377869</v>
+        <v>0.741699516773224</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G35" t="n">
-        <v>0.846957266330719</v>
+        <v>0.846957206726074</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G36" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G52" t="n">
-        <v>0.81464558839798</v>
+        <v>0.814645528793335</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G53" t="n">
-        <v>0.820520460605621</v>
+        <v>0.820520401000977</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G58" t="n">
-        <v>0.862623453140259</v>
+        <v>0.862623512744904</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G59" t="n">
-        <v>0.840103268623352</v>
+        <v>0.840103209018707</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G63" t="n">
-        <v>0.829332709312439</v>
+        <v>0.829332649707794</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G65" t="n">
-        <v>0.829332709312439</v>
+        <v>0.829332649707794</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G67" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>0.847500026226044</v>
       </c>
       <c r="G69" t="n">
-        <v>0.829822242259979</v>
+        <v>0.829822301864624</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G79" t="n">
-        <v>0.810239374637604</v>
+        <v>0.810239434242249</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G80" t="n">
-        <v>0.808770656585693</v>
+        <v>0.808770716190338</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G81" t="n">
-        <v>0.810239374637604</v>
+        <v>0.810239434242249</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G82" t="n">
-        <v>0.808770656585693</v>
+        <v>0.808770716190338</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G93" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>0.863499999046326</v>
       </c>
       <c r="G97" t="n">
-        <v>0.845488548278809</v>
+        <v>0.845488488674164</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G98" t="n">
-        <v>0.842061579227448</v>
+        <v>0.842061519622803</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G111" t="n">
-        <v>0.906684815883636</v>
+        <v>0.906684875488281</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G114" t="n">
-        <v>0.910601377487183</v>
+        <v>0.910601437091827</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>0.927500009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>0.908153593540192</v>
+        <v>0.908153533935547</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>0.905216097831726</v>
+        <v>0.905216157436371</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G125" t="n">
-        <v>0.900810062885284</v>
+        <v>0.90081000328064</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G132" t="n">
-        <v>0.877310633659363</v>
+        <v>0.877310693264008</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G135" t="n">
-        <v>0.899830877780914</v>
+        <v>0.899830937385559</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G141" t="n">
-        <v>0.910601377487183</v>
+        <v>0.910601437091827</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G142" t="n">
-        <v>0.930184185504913</v>
+        <v>0.930184245109558</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G145" t="n">
-        <v>0.910601377487183</v>
+        <v>0.910601437091827</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G148" t="n">
-        <v>0.905705749988556</v>
+        <v>0.905705690383911</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>0.912500023841858</v>
       </c>
       <c r="G149" t="n">
-        <v>0.893466472625732</v>
+        <v>0.893466413021088</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>0.918500006198883</v>
       </c>
       <c r="G158" t="n">
-        <v>0.899341344833374</v>
+        <v>0.899341285228729</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G160" t="n">
-        <v>0.899830877780914</v>
+        <v>0.899830937385559</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>0.907000005245209</v>
       </c>
       <c r="G162" t="n">
-        <v>0.888081192970276</v>
+        <v>0.888081133365631</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G174" t="n">
-        <v>0.889060258865356</v>
+        <v>0.889060318470001</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>0.911499977111816</v>
       </c>
       <c r="G175" t="n">
-        <v>0.892487227916718</v>
+        <v>0.892487287521362</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G178" t="n">
-        <v>0.988932728767395</v>
+        <v>0.98893266916275</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G179" t="n">
-        <v>1.01243209838867</v>
+        <v>1.01243221759796</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G181" t="n">
-        <v>0.978162229061127</v>
+        <v>0.978162169456482</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G183" t="n">
-        <v>0.949767053127289</v>
+        <v>0.949767112731934</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G184" t="n">
-        <v>0.965433359146118</v>
+        <v>0.965433299541473</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G185" t="n">
-        <v>0.978162229061127</v>
+        <v>0.978162169456482</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G192" t="n">
-        <v>0.963475108146667</v>
+        <v>0.963475048542023</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G193" t="n">
-        <v>0.963475108146667</v>
+        <v>0.963475048542023</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G196" t="n">
-        <v>0.970818638801575</v>
+        <v>0.97081857919693</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G197" t="n">
-        <v>0.978162229061127</v>
+        <v>0.978162169456482</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G201" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>0.989000022411346</v>
       </c>
       <c r="G205" t="n">
-        <v>0.968370795249939</v>
+        <v>0.968370735645294</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>0.984499990940094</v>
       </c>
       <c r="G207" t="n">
-        <v>0.963964581489563</v>
+        <v>0.963964641094208</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>0.988499999046326</v>
       </c>
       <c r="G213" t="n">
-        <v>0.967881143093109</v>
+        <v>0.967881202697754</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G215" t="n">
-        <v>0.984036982059479</v>
+        <v>0.984037041664124</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G216" t="n">
-        <v>0.970818638801575</v>
+        <v>0.97081857919693</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G222" t="n">
-        <v>0.949767053127289</v>
+        <v>0.949767112731934</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G224" t="n">
-        <v>0.941933989524841</v>
+        <v>0.941933929920197</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G225" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G226" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G227" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G229" t="n">
-        <v>0.903747379779816</v>
+        <v>0.90374743938446</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G232" t="n">
-        <v>0.905216097831726</v>
+        <v>0.905216157436371</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G236" t="n">
-        <v>0.902768313884735</v>
+        <v>0.90276825428009</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G237" t="n">
-        <v>0.902768313884735</v>
+        <v>0.90276825428009</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G238" t="n">
-        <v>0.905216097831726</v>
+        <v>0.905216157436371</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G251" t="n">
-        <v>0.910601377487183</v>
+        <v>0.910601437091827</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G252" t="n">
-        <v>0.899830877780914</v>
+        <v>0.899830937385559</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G253" t="n">
-        <v>0.900810062885284</v>
+        <v>0.90081000328064</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>0.938499987125397</v>
       </c>
       <c r="G255" t="n">
-        <v>0.918924152851105</v>
+        <v>0.91892409324646</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G258" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G260" t="n">
-        <v>0.932142555713654</v>
+        <v>0.932142496109009</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>0.989000022411346</v>
       </c>
       <c r="G262" t="n">
-        <v>0.968370795249939</v>
+        <v>0.968370735645294</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G266" t="n">
-        <v>0.956621110439301</v>
+        <v>0.956621050834656</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G269" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>0.956621110439301</v>
+        <v>0.956621050834656</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G279" t="n">
-        <v>0.949767053127289</v>
+        <v>0.949767112731934</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>0.987500011920929</v>
       </c>
       <c r="G281" t="n">
-        <v>0.966902077198029</v>
+        <v>0.966902017593384</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>0.956621110439301</v>
+        <v>0.956621050834656</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G284" t="n">
-        <v>0.965433359146118</v>
+        <v>0.965433299541473</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>0.986999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>0.966412425041199</v>
+        <v>0.966412484645844</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G291" t="n">
-        <v>0.983057856559753</v>
+        <v>0.983057796955109</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G292" t="n">
-        <v>0.986974477767944</v>
+        <v>0.9869744181633</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G293" t="n">
-        <v>0.983057856559753</v>
+        <v>0.983057796955109</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G295" t="n">
-        <v>0.988932728767395</v>
+        <v>0.98893266916275</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G298" t="n">
-        <v>0.981099545955658</v>
+        <v>0.981099605560303</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>1.01830697059631</v>
+        <v>1.01830685138702</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G301" t="n">
-        <v>1.0525768995285</v>
+        <v>1.05257701873779</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G302" t="n">
-        <v>1.08293032646179</v>
+        <v>1.0829302072525</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G308" t="n">
-        <v>1.22098922729492</v>
+        <v>1.22098910808563</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G310" t="n">
-        <v>1.31694507598877</v>
+        <v>1.31694519519806</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G311" t="n">
-        <v>1.28267514705658</v>
+        <v>1.28267502784729</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>1.29100000858307</v>
       </c>
       <c r="G312" t="n">
-        <v>1.26407146453857</v>
+        <v>1.26407134532928</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>1.27100002765656</v>
       </c>
       <c r="G313" t="n">
-        <v>1.2444885969162</v>
+        <v>1.24448871612549</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.25</v>
       </c>
       <c r="G315" t="n">
-        <v>1.22392666339874</v>
+        <v>1.22392654418945</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G324" t="n">
-        <v>1.32575738430023</v>
+        <v>1.32575726509094</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>1.35699999332428</v>
       </c>
       <c r="G337" t="n">
-        <v>1.32869482040405</v>
+        <v>1.32869470119476</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G341" t="n">
-        <v>1.4099634885788</v>
+        <v>1.40996360778809</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G343" t="n">
-        <v>1.41975486278534</v>
+        <v>1.41975498199463</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>1.41975486278534</v>
+        <v>1.41975498199463</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G357" t="n">
-        <v>1.48437821865082</v>
+        <v>1.48437833786011</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>1.52746033668518</v>
+        <v>1.52746045589447</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G362" t="n">
-        <v>1.52648138999939</v>
+        <v>1.5264812707901</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G364" t="n">
-        <v>1.57641756534576</v>
+        <v>1.57641744613647</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G366" t="n">
-        <v>1.57445919513702</v>
+        <v>1.57445931434631</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G367" t="n">
-        <v>1.55879306793213</v>
+        <v>1.55879294872284</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G370" t="n">
-        <v>1.49319052696228</v>
+        <v>1.49319040775299</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G375" t="n">
-        <v>1.43933773040771</v>
+        <v>1.439337849617</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G379" t="n">
-        <v>1.48241996765137</v>
+        <v>1.48242008686066</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G381" t="n">
-        <v>1.46675372123718</v>
+        <v>1.46675360202789</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G394" t="n">
-        <v>1.3874431848526</v>
+        <v>1.38744330406189</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G397" t="n">
-        <v>1.46675372123718</v>
+        <v>1.46675360202789</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G411" t="n">
-        <v>1.49416971206665</v>
+        <v>1.49416959285736</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G418" t="n">
-        <v>1.88974261283875</v>
+        <v>1.88974273204803</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G420" t="n">
-        <v>1.94261622428894</v>
+        <v>1.94261634349823</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G423" t="n">
-        <v>1.88974261283875</v>
+        <v>1.88974273204803</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G425" t="n">
-        <v>2.16586065292358</v>
+        <v>2.165860414505</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>2.10515379905701</v>
+        <v>2.10515403747559</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G432" t="n">
-        <v>2.08361268043518</v>
+        <v>2.08361291885376</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G435" t="n">
-        <v>2.25398325920105</v>
+        <v>2.25398349761963</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G438" t="n">
-        <v>2.03857207298279</v>
+        <v>2.03857231140137</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G446" t="n">
-        <v>1.93086671829224</v>
+        <v>1.93086659908295</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G451" t="n">
-        <v>2.01507306098938</v>
+        <v>2.0150728225708</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G452" t="n">
-        <v>2.01507306098938</v>
+        <v>2.0150728225708</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G454" t="n">
-        <v>1.98569881916046</v>
+        <v>1.98569869995117</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G456" t="n">
-        <v>2.007239818573</v>
+        <v>2.00723958015442</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G457" t="n">
-        <v>2.01507306098938</v>
+        <v>2.0150728225708</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G461" t="n">
-        <v>1.98374032974243</v>
+        <v>1.98374044895172</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G462" t="n">
-        <v>1.95632445812225</v>
+        <v>1.95632433891296</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G464" t="n">
-        <v>1.98569881916046</v>
+        <v>1.98569869995117</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>1.93869972229004</v>
+        <v>1.93869984149933</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>1.93869972229004</v>
+        <v>1.93869984149933</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G489" t="n">
-        <v>2.05227994918823</v>
+        <v>2.05228018760681</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G490" t="n">
-        <v>2.007239818573</v>
+        <v>2.00723958015442</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G491" t="n">
-        <v>2.007239818573</v>
+        <v>2.00723958015442</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>1.97786545753479</v>
+        <v>1.9778653383255</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>1.97786545753479</v>
+        <v>1.9778653383255</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G508" t="n">
-        <v>1.93674159049988</v>
+        <v>1.93674147129059</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G513" t="n">
-        <v>1.89953410625458</v>
+        <v>1.89953422546387</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G516" t="n">
-        <v>1.97786545753479</v>
+        <v>1.9778653383255</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G522" t="n">
-        <v>1.95632445812225</v>
+        <v>1.95632433891296</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G523" t="n">
-        <v>1.96807396411896</v>
+        <v>1.96807408332825</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G526" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.10515379905701</v>
+        <v>2.10515403747559</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>2.10515379905701</v>
+        <v>2.10515403747559</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G541" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>2.18348503112793</v>
+        <v>2.18348526954651</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G546" t="n">
-        <v>2.19817233085632</v>
+        <v>2.19817209243774</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G547" t="n">
-        <v>2.18348503112793</v>
+        <v>2.18348526954651</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G548" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G550" t="n">
-        <v>2.19327664375305</v>
+        <v>2.19327640533447</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G551" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>1.84800004959106</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>7502</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>1.84200000762939</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>1.80200004577637</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>1.80200004577637</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>1.84200000762939</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>1.84200000762939</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -485,7 +485,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G4" t="n">
-        <v>0.905705749988556</v>
+        <v>0.905705690383911</v>
       </c>
       <c r="H4" t="n">
         <v>67070</v>
@@ -514,7 +514,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G5" t="n">
-        <v>0.845978081226349</v>
+        <v>0.845978140830994</v>
       </c>
       <c r="H5" t="n">
         <v>488400</v>
@@ -572,7 +572,7 @@
         <v>0.838500022888184</v>
       </c>
       <c r="G7" t="n">
-        <v>0.821009993553162</v>
+        <v>0.821010053157806</v>
       </c>
       <c r="H7" t="n">
         <v>198049</v>
@@ -630,7 +630,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G9" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H9" t="n">
         <v>126512</v>
@@ -746,7 +746,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G13" t="n">
-        <v>0.704981744289398</v>
+        <v>0.704981803894043</v>
       </c>
       <c r="H13" t="n">
         <v>214274</v>
@@ -804,7 +804,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G15" t="n">
-        <v>0.741699576377869</v>
+        <v>0.741699516773224</v>
       </c>
       <c r="H15" t="n">
         <v>111111</v>
@@ -862,7 +862,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G17" t="n">
-        <v>0.805833339691162</v>
+        <v>0.805833280086517</v>
       </c>
       <c r="H17" t="n">
         <v>154076</v>
@@ -891,7 +891,7 @@
         <v>0.799499988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>0.782823503017426</v>
+        <v>0.782823443412781</v>
       </c>
       <c r="H18" t="n">
         <v>96322</v>
@@ -920,7 +920,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G19" t="n">
-        <v>0.769605100154877</v>
+        <v>0.769605040550232</v>
       </c>
       <c r="H19" t="n">
         <v>46236</v>
@@ -1181,7 +1181,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G28" t="n">
-        <v>0.741699576377869</v>
+        <v>0.741699516773224</v>
       </c>
       <c r="H28" t="n">
         <v>88730</v>
@@ -1384,7 +1384,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G35" t="n">
-        <v>0.846957266330719</v>
+        <v>0.846957206726074</v>
       </c>
       <c r="H35" t="n">
         <v>118859</v>
@@ -1413,7 +1413,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G36" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H36" t="n">
         <v>64920</v>
@@ -1877,7 +1877,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G52" t="n">
-        <v>0.81464558839798</v>
+        <v>0.814645528793335</v>
       </c>
       <c r="H52" t="n">
         <v>31840</v>
@@ -1906,7 +1906,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G53" t="n">
-        <v>0.820520460605621</v>
+        <v>0.820520401000977</v>
       </c>
       <c r="H53" t="n">
         <v>49839</v>
@@ -2051,7 +2051,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G58" t="n">
-        <v>0.862623453140259</v>
+        <v>0.862623512744904</v>
       </c>
       <c r="H58" t="n">
         <v>72793</v>
@@ -2080,7 +2080,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G59" t="n">
-        <v>0.840103268623352</v>
+        <v>0.840103209018707</v>
       </c>
       <c r="H59" t="n">
         <v>45401</v>
@@ -2196,7 +2196,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G63" t="n">
-        <v>0.829332709312439</v>
+        <v>0.829332649707794</v>
       </c>
       <c r="H63" t="n">
         <v>10567</v>
@@ -2254,7 +2254,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G65" t="n">
-        <v>0.829332709312439</v>
+        <v>0.829332649707794</v>
       </c>
       <c r="H65" t="n">
         <v>7361</v>
@@ -2283,7 +2283,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H66" t="n">
         <v>10600</v>
@@ -2312,7 +2312,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G67" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0.847500026226044</v>
       </c>
       <c r="G69" t="n">
-        <v>0.829822242259979</v>
+        <v>0.829822301864624</v>
       </c>
       <c r="H69" t="n">
         <v>46571</v>
@@ -2660,7 +2660,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G79" t="n">
-        <v>0.810239374637604</v>
+        <v>0.810239434242249</v>
       </c>
       <c r="H79" t="n">
         <v>5486</v>
@@ -2689,7 +2689,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G80" t="n">
-        <v>0.808770656585693</v>
+        <v>0.808770716190338</v>
       </c>
       <c r="H80" t="n">
         <v>1771</v>
@@ -2718,7 +2718,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G81" t="n">
-        <v>0.810239374637604</v>
+        <v>0.810239434242249</v>
       </c>
       <c r="H81" t="n">
         <v>5329</v>
@@ -2747,7 +2747,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G82" t="n">
-        <v>0.808770656585693</v>
+        <v>0.808770716190338</v>
       </c>
       <c r="H82" t="n">
         <v>2500</v>
@@ -3066,7 +3066,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G93" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H93" t="n">
         <v>2843</v>
@@ -3182,7 +3182,7 @@
         <v>0.863499999046326</v>
       </c>
       <c r="G97" t="n">
-        <v>0.845488548278809</v>
+        <v>0.845488488674164</v>
       </c>
       <c r="H97" t="n">
         <v>51892</v>
@@ -3211,7 +3211,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G98" t="n">
-        <v>0.842061579227448</v>
+        <v>0.842061519622803</v>
       </c>
       <c r="H98" t="n">
         <v>8247</v>
@@ -3588,7 +3588,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G111" t="n">
-        <v>0.906684815883636</v>
+        <v>0.906684875488281</v>
       </c>
       <c r="H111" t="n">
         <v>24383</v>
@@ -3675,7 +3675,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G114" t="n">
-        <v>0.910601377487183</v>
+        <v>0.910601437091827</v>
       </c>
       <c r="H114" t="n">
         <v>65821</v>
@@ -3820,7 +3820,7 @@
         <v>0.927500009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>0.908153593540192</v>
+        <v>0.908153533935547</v>
       </c>
       <c r="H119" t="n">
         <v>29744</v>
@@ -3965,7 +3965,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>0.905216097831726</v>
+        <v>0.905216157436371</v>
       </c>
       <c r="H124" t="n">
         <v>130254</v>
@@ -3994,7 +3994,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G125" t="n">
-        <v>0.900810062885284</v>
+        <v>0.90081000328064</v>
       </c>
       <c r="H125" t="n">
         <v>35381</v>
@@ -4197,7 +4197,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G132" t="n">
-        <v>0.877310633659363</v>
+        <v>0.877310693264008</v>
       </c>
       <c r="H132" t="n">
         <v>15386</v>
@@ -4284,7 +4284,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G135" t="n">
-        <v>0.899830877780914</v>
+        <v>0.899830937385559</v>
       </c>
       <c r="H135" t="n">
         <v>87599</v>
@@ -4458,7 +4458,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G141" t="n">
-        <v>0.910601377487183</v>
+        <v>0.910601437091827</v>
       </c>
       <c r="H141" t="n">
         <v>16200</v>
@@ -4487,7 +4487,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G142" t="n">
-        <v>0.930184185504913</v>
+        <v>0.930184245109558</v>
       </c>
       <c r="H142" t="n">
         <v>53191</v>
@@ -4574,7 +4574,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G145" t="n">
-        <v>0.910601377487183</v>
+        <v>0.910601437091827</v>
       </c>
       <c r="H145" t="n">
         <v>11693</v>
@@ -4661,7 +4661,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G148" t="n">
-        <v>0.905705749988556</v>
+        <v>0.905705690383911</v>
       </c>
       <c r="H148" t="n">
         <v>14838</v>
@@ -4690,7 +4690,7 @@
         <v>0.912500023841858</v>
       </c>
       <c r="G149" t="n">
-        <v>0.893466472625732</v>
+        <v>0.893466413021088</v>
       </c>
       <c r="H149" t="n">
         <v>11522</v>
@@ -4951,7 +4951,7 @@
         <v>0.918500006198883</v>
       </c>
       <c r="G158" t="n">
-        <v>0.899341344833374</v>
+        <v>0.899341285228729</v>
       </c>
       <c r="H158" t="n">
         <v>20356</v>
@@ -5009,7 +5009,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G160" t="n">
-        <v>0.899830877780914</v>
+        <v>0.899830937385559</v>
       </c>
       <c r="H160" t="n">
         <v>4032</v>
@@ -5067,7 +5067,7 @@
         <v>0.907000005245209</v>
       </c>
       <c r="G162" t="n">
-        <v>0.888081192970276</v>
+        <v>0.888081133365631</v>
       </c>
       <c r="H162" t="n">
         <v>5150</v>
@@ -5415,7 +5415,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G174" t="n">
-        <v>0.889060258865356</v>
+        <v>0.889060318470001</v>
       </c>
       <c r="H174" t="n">
         <v>7586</v>
@@ -5444,7 +5444,7 @@
         <v>0.911499977111816</v>
       </c>
       <c r="G175" t="n">
-        <v>0.892487227916718</v>
+        <v>0.892487287521362</v>
       </c>
       <c r="H175" t="n">
         <v>49377</v>
@@ -5531,7 +5531,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G178" t="n">
-        <v>0.988932728767395</v>
+        <v>0.98893266916275</v>
       </c>
       <c r="H178" t="n">
         <v>69152</v>
@@ -5560,7 +5560,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G179" t="n">
-        <v>1.01243209838867</v>
+        <v>1.01243221759796</v>
       </c>
       <c r="H179" t="n">
         <v>167469</v>
@@ -5618,7 +5618,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G181" t="n">
-        <v>0.978162229061127</v>
+        <v>0.978162169456482</v>
       </c>
       <c r="H181" t="n">
         <v>92947</v>
@@ -5676,7 +5676,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G183" t="n">
-        <v>0.949767053127289</v>
+        <v>0.949767112731934</v>
       </c>
       <c r="H183" t="n">
         <v>91824</v>
@@ -5705,7 +5705,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G184" t="n">
-        <v>0.965433359146118</v>
+        <v>0.965433299541473</v>
       </c>
       <c r="H184" t="n">
         <v>227509</v>
@@ -5734,7 +5734,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G185" t="n">
-        <v>0.978162229061127</v>
+        <v>0.978162169456482</v>
       </c>
       <c r="H185" t="n">
         <v>24534</v>
@@ -5821,7 +5821,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H188" t="n">
         <v>33543</v>
@@ -5937,7 +5937,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G192" t="n">
-        <v>0.963475108146667</v>
+        <v>0.963475048542023</v>
       </c>
       <c r="H192" t="n">
         <v>195703</v>
@@ -5966,7 +5966,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G193" t="n">
-        <v>0.963475108146667</v>
+        <v>0.963475048542023</v>
       </c>
       <c r="H193" t="n">
         <v>120124</v>
@@ -6024,7 +6024,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H195" t="n">
         <v>5609</v>
@@ -6053,7 +6053,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G196" t="n">
-        <v>0.970818638801575</v>
+        <v>0.97081857919693</v>
       </c>
       <c r="H196" t="n">
         <v>51474</v>
@@ -6082,7 +6082,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G197" t="n">
-        <v>0.978162229061127</v>
+        <v>0.978162169456482</v>
       </c>
       <c r="H197" t="n">
         <v>23009</v>
@@ -6198,7 +6198,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G201" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H201" t="n">
         <v>100047</v>
@@ -6314,7 +6314,7 @@
         <v>0.989000022411346</v>
       </c>
       <c r="G205" t="n">
-        <v>0.968370795249939</v>
+        <v>0.968370735645294</v>
       </c>
       <c r="H205" t="n">
         <v>36445</v>
@@ -6372,7 +6372,7 @@
         <v>0.984499990940094</v>
       </c>
       <c r="G207" t="n">
-        <v>0.963964581489563</v>
+        <v>0.963964641094208</v>
       </c>
       <c r="H207" t="n">
         <v>31937</v>
@@ -6517,7 +6517,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H212" t="n">
         <v>27813</v>
@@ -6546,7 +6546,7 @@
         <v>0.988499999046326</v>
       </c>
       <c r="G213" t="n">
-        <v>0.967881143093109</v>
+        <v>0.967881202697754</v>
       </c>
       <c r="H213" t="n">
         <v>28095</v>
@@ -6604,7 +6604,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G215" t="n">
-        <v>0.984036982059479</v>
+        <v>0.984037041664124</v>
       </c>
       <c r="H215" t="n">
         <v>16570</v>
@@ -6633,7 +6633,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G216" t="n">
-        <v>0.970818638801575</v>
+        <v>0.97081857919693</v>
       </c>
       <c r="H216" t="n">
         <v>41278</v>
@@ -6807,7 +6807,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G222" t="n">
-        <v>0.949767053127289</v>
+        <v>0.949767112731934</v>
       </c>
       <c r="H222" t="n">
         <v>32136</v>
@@ -6865,7 +6865,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G224" t="n">
-        <v>0.941933989524841</v>
+        <v>0.941933929920197</v>
       </c>
       <c r="H224" t="n">
         <v>5100</v>
@@ -6894,7 +6894,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G225" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H225" t="n">
         <v>125</v>
@@ -6923,7 +6923,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G226" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H226" t="n">
         <v>18525</v>
@@ -6952,7 +6952,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G227" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H227" t="n">
         <v>2641</v>
@@ -7010,7 +7010,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G229" t="n">
-        <v>0.903747379779816</v>
+        <v>0.90374743938446</v>
       </c>
       <c r="H229" t="n">
         <v>18509</v>
@@ -7097,7 +7097,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G232" t="n">
-        <v>0.905216097831726</v>
+        <v>0.905216157436371</v>
       </c>
       <c r="H232" t="n">
         <v>21022</v>
@@ -7213,7 +7213,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G236" t="n">
-        <v>0.902768313884735</v>
+        <v>0.90276825428009</v>
       </c>
       <c r="H236" t="n">
         <v>12738</v>
@@ -7242,7 +7242,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G237" t="n">
-        <v>0.902768313884735</v>
+        <v>0.90276825428009</v>
       </c>
       <c r="H237" t="n">
         <v>250</v>
@@ -7271,7 +7271,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G238" t="n">
-        <v>0.905216097831726</v>
+        <v>0.905216157436371</v>
       </c>
       <c r="H238" t="n">
         <v>12284</v>
@@ -7648,7 +7648,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G251" t="n">
-        <v>0.910601377487183</v>
+        <v>0.910601437091827</v>
       </c>
       <c r="H251" t="n">
         <v>31468</v>
@@ -7677,7 +7677,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G252" t="n">
-        <v>0.899830877780914</v>
+        <v>0.899830937385559</v>
       </c>
       <c r="H252" t="n">
         <v>15949</v>
@@ -7706,7 +7706,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G253" t="n">
-        <v>0.900810062885284</v>
+        <v>0.90081000328064</v>
       </c>
       <c r="H253" t="n">
         <v>3795</v>
@@ -7764,7 +7764,7 @@
         <v>0.938499987125397</v>
       </c>
       <c r="G255" t="n">
-        <v>0.918924152851105</v>
+        <v>0.91892409324646</v>
       </c>
       <c r="H255" t="n">
         <v>9204</v>
@@ -7851,7 +7851,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G258" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H258" t="n">
         <v>28836</v>
@@ -7909,7 +7909,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G260" t="n">
-        <v>0.932142555713654</v>
+        <v>0.932142496109009</v>
       </c>
       <c r="H260" t="n">
         <v>20022</v>
@@ -7967,7 +7967,7 @@
         <v>0.989000022411346</v>
       </c>
       <c r="G262" t="n">
-        <v>0.968370795249939</v>
+        <v>0.968370735645294</v>
       </c>
       <c r="H262" t="n">
         <v>22001</v>
@@ -8083,7 +8083,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G266" t="n">
-        <v>0.956621110439301</v>
+        <v>0.956621050834656</v>
       </c>
       <c r="H266" t="n">
         <v>146793</v>
@@ -8170,7 +8170,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G269" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H269" t="n">
         <v>69497</v>
@@ -8199,7 +8199,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H270" t="n">
         <v>61895</v>
@@ -8373,7 +8373,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H276" t="n">
         <v>31565</v>
@@ -8431,7 +8431,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>0.956621110439301</v>
+        <v>0.956621050834656</v>
       </c>
       <c r="H278" t="n">
         <v>48455</v>
@@ -8460,7 +8460,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G279" t="n">
-        <v>0.949767053127289</v>
+        <v>0.949767112731934</v>
       </c>
       <c r="H279" t="n">
         <v>34223</v>
@@ -8489,7 +8489,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H280" t="n">
         <v>16506</v>
@@ -8518,7 +8518,7 @@
         <v>0.987500011920929</v>
       </c>
       <c r="G281" t="n">
-        <v>0.966902077198029</v>
+        <v>0.966902017593384</v>
       </c>
       <c r="H281" t="n">
         <v>2162</v>
@@ -8576,7 +8576,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>0.956621110439301</v>
+        <v>0.956621050834656</v>
       </c>
       <c r="H283" t="n">
         <v>8218</v>
@@ -8605,7 +8605,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G284" t="n">
-        <v>0.965433359146118</v>
+        <v>0.965433299541473</v>
       </c>
       <c r="H284" t="n">
         <v>4642</v>
@@ -8750,7 +8750,7 @@
         <v>0.986999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>0.966412425041199</v>
+        <v>0.966412484645844</v>
       </c>
       <c r="H289" t="n">
         <v>37264</v>
@@ -8808,7 +8808,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G291" t="n">
-        <v>0.983057856559753</v>
+        <v>0.983057796955109</v>
       </c>
       <c r="H291" t="n">
         <v>27881</v>
@@ -8837,7 +8837,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G292" t="n">
-        <v>0.986974477767944</v>
+        <v>0.9869744181633</v>
       </c>
       <c r="H292" t="n">
         <v>63522</v>
@@ -8866,7 +8866,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G293" t="n">
-        <v>0.983057856559753</v>
+        <v>0.983057796955109</v>
       </c>
       <c r="H293" t="n">
         <v>53865</v>
@@ -8924,7 +8924,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G295" t="n">
-        <v>0.988932728767395</v>
+        <v>0.98893266916275</v>
       </c>
       <c r="H295" t="n">
         <v>40379</v>
@@ -8982,7 +8982,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H297" t="n">
         <v>20659</v>
@@ -9011,7 +9011,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G298" t="n">
-        <v>0.981099545955658</v>
+        <v>0.981099605560303</v>
       </c>
       <c r="H298" t="n">
         <v>114382</v>
@@ -9069,7 +9069,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>1.01830697059631</v>
+        <v>1.01830685138702</v>
       </c>
       <c r="H300" t="n">
         <v>269003</v>
@@ -9098,7 +9098,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G301" t="n">
-        <v>1.0525768995285</v>
+        <v>1.05257701873779</v>
       </c>
       <c r="H301" t="n">
         <v>358002</v>
@@ -9127,7 +9127,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G302" t="n">
-        <v>1.08293032646179</v>
+        <v>1.0829302072525</v>
       </c>
       <c r="H302" t="n">
         <v>259801</v>
@@ -9301,7 +9301,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G308" t="n">
-        <v>1.22098922729492</v>
+        <v>1.22098910808563</v>
       </c>
       <c r="H308" t="n">
         <v>47431</v>
@@ -9359,7 +9359,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G310" t="n">
-        <v>1.31694507598877</v>
+        <v>1.31694519519806</v>
       </c>
       <c r="H310" t="n">
         <v>204989</v>
@@ -9388,7 +9388,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G311" t="n">
-        <v>1.28267514705658</v>
+        <v>1.28267502784729</v>
       </c>
       <c r="H311" t="n">
         <v>321537</v>
@@ -9417,7 +9417,7 @@
         <v>1.29100000858307</v>
       </c>
       <c r="G312" t="n">
-        <v>1.26407146453857</v>
+        <v>1.26407134532928</v>
       </c>
       <c r="H312" t="n">
         <v>199047</v>
@@ -9446,7 +9446,7 @@
         <v>1.27100002765656</v>
       </c>
       <c r="G313" t="n">
-        <v>1.2444885969162</v>
+        <v>1.24448871612549</v>
       </c>
       <c r="H313" t="n">
         <v>96734</v>
@@ -9504,7 +9504,7 @@
         <v>1.25</v>
       </c>
       <c r="G315" t="n">
-        <v>1.22392666339874</v>
+        <v>1.22392654418945</v>
       </c>
       <c r="H315" t="n">
         <v>114680</v>
@@ -9765,7 +9765,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G324" t="n">
-        <v>1.32575738430023</v>
+        <v>1.32575726509094</v>
       </c>
       <c r="H324" t="n">
         <v>88859</v>
@@ -10142,7 +10142,7 @@
         <v>1.35699999332428</v>
       </c>
       <c r="G337" t="n">
-        <v>1.32869482040405</v>
+        <v>1.32869470119476</v>
       </c>
       <c r="H337" t="n">
         <v>108123</v>
@@ -10258,7 +10258,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G341" t="n">
-        <v>1.4099634885788</v>
+        <v>1.40996360778809</v>
       </c>
       <c r="H341" t="n">
         <v>114493</v>
@@ -10316,7 +10316,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G343" t="n">
-        <v>1.41975486278534</v>
+        <v>1.41975498199463</v>
       </c>
       <c r="H343" t="n">
         <v>91345</v>
@@ -10664,7 +10664,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>1.41975486278534</v>
+        <v>1.41975498199463</v>
       </c>
       <c r="H355" t="n">
         <v>66611</v>
@@ -10722,7 +10722,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G357" t="n">
-        <v>1.48437821865082</v>
+        <v>1.48437833786011</v>
       </c>
       <c r="H357" t="n">
         <v>402550</v>
@@ -10751,7 +10751,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>1.52746033668518</v>
+        <v>1.52746045589447</v>
       </c>
       <c r="H358" t="n">
         <v>214036</v>
@@ -10867,7 +10867,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G362" t="n">
-        <v>1.52648138999939</v>
+        <v>1.5264812707901</v>
       </c>
       <c r="H362" t="n">
         <v>108720</v>
@@ -10925,7 +10925,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G364" t="n">
-        <v>1.57641756534576</v>
+        <v>1.57641744613647</v>
       </c>
       <c r="H364" t="n">
         <v>87137</v>
@@ -10983,7 +10983,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G366" t="n">
-        <v>1.57445919513702</v>
+        <v>1.57445931434631</v>
       </c>
       <c r="H366" t="n">
         <v>153391</v>
@@ -11012,7 +11012,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G367" t="n">
-        <v>1.55879306793213</v>
+        <v>1.55879294872284</v>
       </c>
       <c r="H367" t="n">
         <v>59009</v>
@@ -11099,7 +11099,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G370" t="n">
-        <v>1.49319052696228</v>
+        <v>1.49319040775299</v>
       </c>
       <c r="H370" t="n">
         <v>198615</v>
@@ -11244,7 +11244,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G375" t="n">
-        <v>1.43933773040771</v>
+        <v>1.439337849617</v>
       </c>
       <c r="H375" t="n">
         <v>28060</v>
@@ -11360,7 +11360,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G379" t="n">
-        <v>1.48241996765137</v>
+        <v>1.48242008686066</v>
       </c>
       <c r="H379" t="n">
         <v>50853</v>
@@ -11418,7 +11418,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G381" t="n">
-        <v>1.46675372123718</v>
+        <v>1.46675360202789</v>
       </c>
       <c r="H381" t="n">
         <v>37418</v>
@@ -11795,7 +11795,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G394" t="n">
-        <v>1.3874431848526</v>
+        <v>1.38744330406189</v>
       </c>
       <c r="H394" t="n">
         <v>3217</v>
@@ -11882,7 +11882,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G397" t="n">
-        <v>1.46675372123718</v>
+        <v>1.46675360202789</v>
       </c>
       <c r="H397" t="n">
         <v>146942</v>
@@ -12288,7 +12288,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G411" t="n">
-        <v>1.49416971206665</v>
+        <v>1.49416959285736</v>
       </c>
       <c r="H411" t="n">
         <v>33895</v>
@@ -12491,7 +12491,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G418" t="n">
-        <v>1.88974261283875</v>
+        <v>1.88974273204803</v>
       </c>
       <c r="H418" t="n">
         <v>296041</v>
@@ -12549,7 +12549,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G420" t="n">
-        <v>1.94261622428894</v>
+        <v>1.94261634349823</v>
       </c>
       <c r="H420" t="n">
         <v>376100</v>
@@ -12636,7 +12636,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G423" t="n">
-        <v>1.88974261283875</v>
+        <v>1.88974273204803</v>
       </c>
       <c r="H423" t="n">
         <v>81649</v>
@@ -12694,7 +12694,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G425" t="n">
-        <v>2.16586065292358</v>
+        <v>2.165860414505</v>
       </c>
       <c r="H425" t="n">
         <v>662427</v>
@@ -12723,7 +12723,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>2.10515379905701</v>
+        <v>2.10515403747559</v>
       </c>
       <c r="H426" t="n">
         <v>303943</v>
@@ -12897,7 +12897,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G432" t="n">
-        <v>2.08361268043518</v>
+        <v>2.08361291885376</v>
       </c>
       <c r="H432" t="n">
         <v>120592</v>
@@ -12984,7 +12984,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G435" t="n">
-        <v>2.25398325920105</v>
+        <v>2.25398349761963</v>
       </c>
       <c r="H435" t="n">
         <v>446100</v>
@@ -13071,7 +13071,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G438" t="n">
-        <v>2.03857207298279</v>
+        <v>2.03857231140137</v>
       </c>
       <c r="H438" t="n">
         <v>376904</v>
@@ -13303,7 +13303,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G446" t="n">
-        <v>1.93086671829224</v>
+        <v>1.93086659908295</v>
       </c>
       <c r="H446" t="n">
         <v>226358</v>
@@ -13448,7 +13448,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G451" t="n">
-        <v>2.01507306098938</v>
+        <v>2.0150728225708</v>
       </c>
       <c r="H451" t="n">
         <v>124152</v>
@@ -13477,7 +13477,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G452" t="n">
-        <v>2.01507306098938</v>
+        <v>2.0150728225708</v>
       </c>
       <c r="H452" t="n">
         <v>122037</v>
@@ -13535,7 +13535,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G454" t="n">
-        <v>1.98569881916046</v>
+        <v>1.98569869995117</v>
       </c>
       <c r="H454" t="n">
         <v>31437</v>
@@ -13593,7 +13593,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G456" t="n">
-        <v>2.007239818573</v>
+        <v>2.00723958015442</v>
       </c>
       <c r="H456" t="n">
         <v>34457</v>
@@ -13622,7 +13622,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G457" t="n">
-        <v>2.01507306098938</v>
+        <v>2.0150728225708</v>
       </c>
       <c r="H457" t="n">
         <v>166275</v>
@@ -13738,7 +13738,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G461" t="n">
-        <v>1.98374032974243</v>
+        <v>1.98374044895172</v>
       </c>
       <c r="H461" t="n">
         <v>168464</v>
@@ -13767,7 +13767,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G462" t="n">
-        <v>1.95632445812225</v>
+        <v>1.95632433891296</v>
       </c>
       <c r="H462" t="n">
         <v>77596</v>
@@ -13825,7 +13825,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G464" t="n">
-        <v>1.98569881916046</v>
+        <v>1.98569869995117</v>
       </c>
       <c r="H464" t="n">
         <v>420317</v>
@@ -14144,7 +14144,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>1.93869972229004</v>
+        <v>1.93869984149933</v>
       </c>
       <c r="H475" t="n">
         <v>77792</v>
@@ -14463,7 +14463,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>1.93869972229004</v>
+        <v>1.93869984149933</v>
       </c>
       <c r="H486" t="n">
         <v>58282</v>
@@ -14550,7 +14550,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G489" t="n">
-        <v>2.05227994918823</v>
+        <v>2.05228018760681</v>
       </c>
       <c r="H489" t="n">
         <v>365431</v>
@@ -14579,7 +14579,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G490" t="n">
-        <v>2.007239818573</v>
+        <v>2.00723958015442</v>
       </c>
       <c r="H490" t="n">
         <v>127429</v>
@@ -14608,7 +14608,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G491" t="n">
-        <v>2.007239818573</v>
+        <v>2.00723958015442</v>
       </c>
       <c r="H491" t="n">
         <v>16967</v>
@@ -14869,7 +14869,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>1.97786545753479</v>
+        <v>1.9778653383255</v>
       </c>
       <c r="H500" t="n">
         <v>25172</v>
@@ -14898,7 +14898,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>1.97786545753479</v>
+        <v>1.9778653383255</v>
       </c>
       <c r="H501" t="n">
         <v>40934</v>
@@ -15101,7 +15101,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G508" t="n">
-        <v>1.93674159049988</v>
+        <v>1.93674147129059</v>
       </c>
       <c r="H508" t="n">
         <v>1738</v>
@@ -15246,7 +15246,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G513" t="n">
-        <v>1.89953410625458</v>
+        <v>1.89953422546387</v>
       </c>
       <c r="H513" t="n">
         <v>8507</v>
@@ -15333,7 +15333,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G516" t="n">
-        <v>1.97786545753479</v>
+        <v>1.9778653383255</v>
       </c>
       <c r="H516" t="n">
         <v>80856</v>
@@ -15507,7 +15507,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G522" t="n">
-        <v>1.95632445812225</v>
+        <v>1.95632433891296</v>
       </c>
       <c r="H522" t="n">
         <v>18050</v>
@@ -15536,7 +15536,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G523" t="n">
-        <v>1.96807396411896</v>
+        <v>1.96807408332825</v>
       </c>
       <c r="H523" t="n">
         <v>20616</v>
@@ -15623,7 +15623,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G526" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H526" t="n">
         <v>452689</v>
@@ -15942,7 +15942,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.10515379905701</v>
+        <v>2.10515403747559</v>
       </c>
       <c r="H537" t="n">
         <v>139101</v>
@@ -15971,7 +15971,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>2.10515379905701</v>
+        <v>2.10515403747559</v>
       </c>
       <c r="H538" t="n">
         <v>48637</v>
@@ -16058,7 +16058,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G541" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H541" t="n">
         <v>177454</v>
@@ -16087,7 +16087,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H542" t="n">
         <v>49635</v>
@@ -16145,7 +16145,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>2.18348503112793</v>
+        <v>2.18348526954651</v>
       </c>
       <c r="H544" t="n">
         <v>46864</v>
@@ -16203,7 +16203,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G546" t="n">
-        <v>2.19817233085632</v>
+        <v>2.19817209243774</v>
       </c>
       <c r="H546" t="n">
         <v>50060</v>
@@ -16232,7 +16232,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G547" t="n">
-        <v>2.18348503112793</v>
+        <v>2.18348526954651</v>
       </c>
       <c r="H547" t="n">
         <v>16948</v>
@@ -16261,7 +16261,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G548" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H548" t="n">
         <v>72087</v>
@@ -16319,7 +16319,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G550" t="n">
-        <v>2.19327664375305</v>
+        <v>2.19327640533447</v>
       </c>
       <c r="H550" t="n">
         <v>215281</v>
@@ -16348,7 +16348,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G551" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H551" t="n">
         <v>27372</v>
@@ -16377,7 +16377,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H552" t="n">
         <v>17856</v>
@@ -79951,6 +79951,64 @@
         <v>7502</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>1.8400000333786</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>1.8400000333786</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>1.76199996471405</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>1.76199996471405</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>1.76199996471405</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>12216</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>1.80999994277954</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>1.77600002288818</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>1.77600002288818</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>26354</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -485,7 +485,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G4" t="n">
-        <v>0.905705690383911</v>
+        <v>0.905705749988556</v>
       </c>
       <c r="H4" t="n">
         <v>67070</v>
@@ -514,7 +514,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G5" t="n">
-        <v>0.845978140830994</v>
+        <v>0.845978081226349</v>
       </c>
       <c r="H5" t="n">
         <v>488400</v>
@@ -572,7 +572,7 @@
         <v>0.838500022888184</v>
       </c>
       <c r="G7" t="n">
-        <v>0.821010053157806</v>
+        <v>0.821009993553162</v>
       </c>
       <c r="H7" t="n">
         <v>198049</v>
@@ -630,7 +630,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G9" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H9" t="n">
         <v>126512</v>
@@ -746,7 +746,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G13" t="n">
-        <v>0.704981803894043</v>
+        <v>0.704981744289398</v>
       </c>
       <c r="H13" t="n">
         <v>214274</v>
@@ -804,7 +804,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G15" t="n">
-        <v>0.741699516773224</v>
+        <v>0.741699576377869</v>
       </c>
       <c r="H15" t="n">
         <v>111111</v>
@@ -862,7 +862,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G17" t="n">
-        <v>0.805833280086517</v>
+        <v>0.805833339691162</v>
       </c>
       <c r="H17" t="n">
         <v>154076</v>
@@ -891,7 +891,7 @@
         <v>0.799499988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>0.782823443412781</v>
+        <v>0.782823503017426</v>
       </c>
       <c r="H18" t="n">
         <v>96322</v>
@@ -920,7 +920,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G19" t="n">
-        <v>0.769605040550232</v>
+        <v>0.769605100154877</v>
       </c>
       <c r="H19" t="n">
         <v>46236</v>
@@ -1181,7 +1181,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G28" t="n">
-        <v>0.741699516773224</v>
+        <v>0.741699576377869</v>
       </c>
       <c r="H28" t="n">
         <v>88730</v>
@@ -1384,7 +1384,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G35" t="n">
-        <v>0.846957206726074</v>
+        <v>0.846957266330719</v>
       </c>
       <c r="H35" t="n">
         <v>118859</v>
@@ -1413,7 +1413,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G36" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H36" t="n">
         <v>64920</v>
@@ -1877,7 +1877,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G52" t="n">
-        <v>0.814645528793335</v>
+        <v>0.81464558839798</v>
       </c>
       <c r="H52" t="n">
         <v>31840</v>
@@ -1906,7 +1906,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G53" t="n">
-        <v>0.820520401000977</v>
+        <v>0.820520460605621</v>
       </c>
       <c r="H53" t="n">
         <v>49839</v>
@@ -2051,7 +2051,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G58" t="n">
-        <v>0.862623512744904</v>
+        <v>0.862623453140259</v>
       </c>
       <c r="H58" t="n">
         <v>72793</v>
@@ -2080,7 +2080,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G59" t="n">
-        <v>0.840103209018707</v>
+        <v>0.840103268623352</v>
       </c>
       <c r="H59" t="n">
         <v>45401</v>
@@ -2196,7 +2196,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G63" t="n">
-        <v>0.829332649707794</v>
+        <v>0.829332709312439</v>
       </c>
       <c r="H63" t="n">
         <v>10567</v>
@@ -2254,7 +2254,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G65" t="n">
-        <v>0.829332649707794</v>
+        <v>0.829332709312439</v>
       </c>
       <c r="H65" t="n">
         <v>7361</v>
@@ -2283,7 +2283,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H66" t="n">
         <v>10600</v>
@@ -2312,7 +2312,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G67" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0.847500026226044</v>
       </c>
       <c r="G69" t="n">
-        <v>0.829822301864624</v>
+        <v>0.829822242259979</v>
       </c>
       <c r="H69" t="n">
         <v>46571</v>
@@ -2660,7 +2660,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G79" t="n">
-        <v>0.810239434242249</v>
+        <v>0.810239374637604</v>
       </c>
       <c r="H79" t="n">
         <v>5486</v>
@@ -2689,7 +2689,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G80" t="n">
-        <v>0.808770716190338</v>
+        <v>0.808770656585693</v>
       </c>
       <c r="H80" t="n">
         <v>1771</v>
@@ -2718,7 +2718,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G81" t="n">
-        <v>0.810239434242249</v>
+        <v>0.810239374637604</v>
       </c>
       <c r="H81" t="n">
         <v>5329</v>
@@ -2747,7 +2747,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G82" t="n">
-        <v>0.808770716190338</v>
+        <v>0.808770656585693</v>
       </c>
       <c r="H82" t="n">
         <v>2500</v>
@@ -3066,7 +3066,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G93" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H93" t="n">
         <v>2843</v>
@@ -3182,7 +3182,7 @@
         <v>0.863499999046326</v>
       </c>
       <c r="G97" t="n">
-        <v>0.845488488674164</v>
+        <v>0.845488548278809</v>
       </c>
       <c r="H97" t="n">
         <v>51892</v>
@@ -3211,7 +3211,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G98" t="n">
-        <v>0.842061519622803</v>
+        <v>0.842061579227448</v>
       </c>
       <c r="H98" t="n">
         <v>8247</v>
@@ -3588,7 +3588,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G111" t="n">
-        <v>0.906684875488281</v>
+        <v>0.906684815883636</v>
       </c>
       <c r="H111" t="n">
         <v>24383</v>
@@ -3675,7 +3675,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G114" t="n">
-        <v>0.910601437091827</v>
+        <v>0.910601377487183</v>
       </c>
       <c r="H114" t="n">
         <v>65821</v>
@@ -3820,7 +3820,7 @@
         <v>0.927500009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>0.908153533935547</v>
+        <v>0.908153593540192</v>
       </c>
       <c r="H119" t="n">
         <v>29744</v>
@@ -3965,7 +3965,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>0.905216157436371</v>
+        <v>0.905216097831726</v>
       </c>
       <c r="H124" t="n">
         <v>130254</v>
@@ -3994,7 +3994,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G125" t="n">
-        <v>0.90081000328064</v>
+        <v>0.900810062885284</v>
       </c>
       <c r="H125" t="n">
         <v>35381</v>
@@ -4197,7 +4197,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G132" t="n">
-        <v>0.877310693264008</v>
+        <v>0.877310633659363</v>
       </c>
       <c r="H132" t="n">
         <v>15386</v>
@@ -4284,7 +4284,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G135" t="n">
-        <v>0.899830937385559</v>
+        <v>0.899830877780914</v>
       </c>
       <c r="H135" t="n">
         <v>87599</v>
@@ -4458,7 +4458,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G141" t="n">
-        <v>0.910601437091827</v>
+        <v>0.910601377487183</v>
       </c>
       <c r="H141" t="n">
         <v>16200</v>
@@ -4487,7 +4487,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G142" t="n">
-        <v>0.930184245109558</v>
+        <v>0.930184185504913</v>
       </c>
       <c r="H142" t="n">
         <v>53191</v>
@@ -4574,7 +4574,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G145" t="n">
-        <v>0.910601437091827</v>
+        <v>0.910601377487183</v>
       </c>
       <c r="H145" t="n">
         <v>11693</v>
@@ -4661,7 +4661,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G148" t="n">
-        <v>0.905705690383911</v>
+        <v>0.905705749988556</v>
       </c>
       <c r="H148" t="n">
         <v>14838</v>
@@ -4690,7 +4690,7 @@
         <v>0.912500023841858</v>
       </c>
       <c r="G149" t="n">
-        <v>0.893466413021088</v>
+        <v>0.893466472625732</v>
       </c>
       <c r="H149" t="n">
         <v>11522</v>
@@ -4951,7 +4951,7 @@
         <v>0.918500006198883</v>
       </c>
       <c r="G158" t="n">
-        <v>0.899341285228729</v>
+        <v>0.899341344833374</v>
       </c>
       <c r="H158" t="n">
         <v>20356</v>
@@ -5009,7 +5009,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G160" t="n">
-        <v>0.899830937385559</v>
+        <v>0.899830877780914</v>
       </c>
       <c r="H160" t="n">
         <v>4032</v>
@@ -5067,7 +5067,7 @@
         <v>0.907000005245209</v>
       </c>
       <c r="G162" t="n">
-        <v>0.888081133365631</v>
+        <v>0.888081192970276</v>
       </c>
       <c r="H162" t="n">
         <v>5150</v>
@@ -5415,7 +5415,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G174" t="n">
-        <v>0.889060318470001</v>
+        <v>0.889060258865356</v>
       </c>
       <c r="H174" t="n">
         <v>7586</v>
@@ -5444,7 +5444,7 @@
         <v>0.911499977111816</v>
       </c>
       <c r="G175" t="n">
-        <v>0.892487287521362</v>
+        <v>0.892487227916718</v>
       </c>
       <c r="H175" t="n">
         <v>49377</v>
@@ -5531,7 +5531,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G178" t="n">
-        <v>0.98893266916275</v>
+        <v>0.988932728767395</v>
       </c>
       <c r="H178" t="n">
         <v>69152</v>
@@ -5560,7 +5560,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G179" t="n">
-        <v>1.01243221759796</v>
+        <v>1.01243209838867</v>
       </c>
       <c r="H179" t="n">
         <v>167469</v>
@@ -5618,7 +5618,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G181" t="n">
-        <v>0.978162169456482</v>
+        <v>0.978162229061127</v>
       </c>
       <c r="H181" t="n">
         <v>92947</v>
@@ -5676,7 +5676,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G183" t="n">
-        <v>0.949767112731934</v>
+        <v>0.949767053127289</v>
       </c>
       <c r="H183" t="n">
         <v>91824</v>
@@ -5705,7 +5705,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G184" t="n">
-        <v>0.965433299541473</v>
+        <v>0.965433359146118</v>
       </c>
       <c r="H184" t="n">
         <v>227509</v>
@@ -5734,7 +5734,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G185" t="n">
-        <v>0.978162169456482</v>
+        <v>0.978162229061127</v>
       </c>
       <c r="H185" t="n">
         <v>24534</v>
@@ -5821,7 +5821,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H188" t="n">
         <v>33543</v>
@@ -5937,7 +5937,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G192" t="n">
-        <v>0.963475048542023</v>
+        <v>0.963475108146667</v>
       </c>
       <c r="H192" t="n">
         <v>195703</v>
@@ -5966,7 +5966,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G193" t="n">
-        <v>0.963475048542023</v>
+        <v>0.963475108146667</v>
       </c>
       <c r="H193" t="n">
         <v>120124</v>
@@ -6024,7 +6024,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H195" t="n">
         <v>5609</v>
@@ -6053,7 +6053,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G196" t="n">
-        <v>0.97081857919693</v>
+        <v>0.970818638801575</v>
       </c>
       <c r="H196" t="n">
         <v>51474</v>
@@ -6082,7 +6082,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G197" t="n">
-        <v>0.978162169456482</v>
+        <v>0.978162229061127</v>
       </c>
       <c r="H197" t="n">
         <v>23009</v>
@@ -6198,7 +6198,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G201" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H201" t="n">
         <v>100047</v>
@@ -6314,7 +6314,7 @@
         <v>0.989000022411346</v>
       </c>
       <c r="G205" t="n">
-        <v>0.968370735645294</v>
+        <v>0.968370795249939</v>
       </c>
       <c r="H205" t="n">
         <v>36445</v>
@@ -6372,7 +6372,7 @@
         <v>0.984499990940094</v>
       </c>
       <c r="G207" t="n">
-        <v>0.963964641094208</v>
+        <v>0.963964581489563</v>
       </c>
       <c r="H207" t="n">
         <v>31937</v>
@@ -6517,7 +6517,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H212" t="n">
         <v>27813</v>
@@ -6546,7 +6546,7 @@
         <v>0.988499999046326</v>
       </c>
       <c r="G213" t="n">
-        <v>0.967881202697754</v>
+        <v>0.967881143093109</v>
       </c>
       <c r="H213" t="n">
         <v>28095</v>
@@ -6604,7 +6604,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G215" t="n">
-        <v>0.984037041664124</v>
+        <v>0.984036982059479</v>
       </c>
       <c r="H215" t="n">
         <v>16570</v>
@@ -6633,7 +6633,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G216" t="n">
-        <v>0.97081857919693</v>
+        <v>0.970818638801575</v>
       </c>
       <c r="H216" t="n">
         <v>41278</v>
@@ -6807,7 +6807,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G222" t="n">
-        <v>0.949767112731934</v>
+        <v>0.949767053127289</v>
       </c>
       <c r="H222" t="n">
         <v>32136</v>
@@ -6865,7 +6865,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G224" t="n">
-        <v>0.941933929920197</v>
+        <v>0.941933989524841</v>
       </c>
       <c r="H224" t="n">
         <v>5100</v>
@@ -6894,7 +6894,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G225" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H225" t="n">
         <v>125</v>
@@ -6923,7 +6923,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G226" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H226" t="n">
         <v>18525</v>
@@ -6952,7 +6952,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G227" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H227" t="n">
         <v>2641</v>
@@ -7010,7 +7010,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G229" t="n">
-        <v>0.90374743938446</v>
+        <v>0.903747379779816</v>
       </c>
       <c r="H229" t="n">
         <v>18509</v>
@@ -7097,7 +7097,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G232" t="n">
-        <v>0.905216157436371</v>
+        <v>0.905216097831726</v>
       </c>
       <c r="H232" t="n">
         <v>21022</v>
@@ -7213,7 +7213,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G236" t="n">
-        <v>0.90276825428009</v>
+        <v>0.902768313884735</v>
       </c>
       <c r="H236" t="n">
         <v>12738</v>
@@ -7242,7 +7242,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G237" t="n">
-        <v>0.90276825428009</v>
+        <v>0.902768313884735</v>
       </c>
       <c r="H237" t="n">
         <v>250</v>
@@ -7271,7 +7271,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G238" t="n">
-        <v>0.905216157436371</v>
+        <v>0.905216097831726</v>
       </c>
       <c r="H238" t="n">
         <v>12284</v>
@@ -7648,7 +7648,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G251" t="n">
-        <v>0.910601437091827</v>
+        <v>0.910601377487183</v>
       </c>
       <c r="H251" t="n">
         <v>31468</v>
@@ -7677,7 +7677,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G252" t="n">
-        <v>0.899830937385559</v>
+        <v>0.899830877780914</v>
       </c>
       <c r="H252" t="n">
         <v>15949</v>
@@ -7706,7 +7706,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G253" t="n">
-        <v>0.90081000328064</v>
+        <v>0.900810062885284</v>
       </c>
       <c r="H253" t="n">
         <v>3795</v>
@@ -7764,7 +7764,7 @@
         <v>0.938499987125397</v>
       </c>
       <c r="G255" t="n">
-        <v>0.91892409324646</v>
+        <v>0.918924152851105</v>
       </c>
       <c r="H255" t="n">
         <v>9204</v>
@@ -7851,7 +7851,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G258" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H258" t="n">
         <v>28836</v>
@@ -7909,7 +7909,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G260" t="n">
-        <v>0.932142496109009</v>
+        <v>0.932142555713654</v>
       </c>
       <c r="H260" t="n">
         <v>20022</v>
@@ -7967,7 +7967,7 @@
         <v>0.989000022411346</v>
       </c>
       <c r="G262" t="n">
-        <v>0.968370735645294</v>
+        <v>0.968370795249939</v>
       </c>
       <c r="H262" t="n">
         <v>22001</v>
@@ -8083,7 +8083,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G266" t="n">
-        <v>0.956621050834656</v>
+        <v>0.956621110439301</v>
       </c>
       <c r="H266" t="n">
         <v>146793</v>
@@ -8170,7 +8170,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G269" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H269" t="n">
         <v>69497</v>
@@ -8199,7 +8199,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H270" t="n">
         <v>61895</v>
@@ -8373,7 +8373,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H276" t="n">
         <v>31565</v>
@@ -8431,7 +8431,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>0.956621050834656</v>
+        <v>0.956621110439301</v>
       </c>
       <c r="H278" t="n">
         <v>48455</v>
@@ -8460,7 +8460,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G279" t="n">
-        <v>0.949767112731934</v>
+        <v>0.949767053127289</v>
       </c>
       <c r="H279" t="n">
         <v>34223</v>
@@ -8489,7 +8489,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H280" t="n">
         <v>16506</v>
@@ -8518,7 +8518,7 @@
         <v>0.987500011920929</v>
       </c>
       <c r="G281" t="n">
-        <v>0.966902017593384</v>
+        <v>0.966902077198029</v>
       </c>
       <c r="H281" t="n">
         <v>2162</v>
@@ -8576,7 +8576,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>0.956621050834656</v>
+        <v>0.956621110439301</v>
       </c>
       <c r="H283" t="n">
         <v>8218</v>
@@ -8605,7 +8605,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G284" t="n">
-        <v>0.965433299541473</v>
+        <v>0.965433359146118</v>
       </c>
       <c r="H284" t="n">
         <v>4642</v>
@@ -8750,7 +8750,7 @@
         <v>0.986999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>0.966412484645844</v>
+        <v>0.966412425041199</v>
       </c>
       <c r="H289" t="n">
         <v>37264</v>
@@ -8808,7 +8808,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G291" t="n">
-        <v>0.983057796955109</v>
+        <v>0.983057856559753</v>
       </c>
       <c r="H291" t="n">
         <v>27881</v>
@@ -8837,7 +8837,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G292" t="n">
-        <v>0.9869744181633</v>
+        <v>0.986974477767944</v>
       </c>
       <c r="H292" t="n">
         <v>63522</v>
@@ -8866,7 +8866,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G293" t="n">
-        <v>0.983057796955109</v>
+        <v>0.983057856559753</v>
       </c>
       <c r="H293" t="n">
         <v>53865</v>
@@ -8924,7 +8924,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G295" t="n">
-        <v>0.98893266916275</v>
+        <v>0.988932728767395</v>
       </c>
       <c r="H295" t="n">
         <v>40379</v>
@@ -8982,7 +8982,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H297" t="n">
         <v>20659</v>
@@ -9011,7 +9011,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G298" t="n">
-        <v>0.981099605560303</v>
+        <v>0.981099545955658</v>
       </c>
       <c r="H298" t="n">
         <v>114382</v>
@@ -9069,7 +9069,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>1.01830685138702</v>
+        <v>1.01830697059631</v>
       </c>
       <c r="H300" t="n">
         <v>269003</v>
@@ -9098,7 +9098,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G301" t="n">
-        <v>1.05257701873779</v>
+        <v>1.0525768995285</v>
       </c>
       <c r="H301" t="n">
         <v>358002</v>
@@ -9127,7 +9127,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G302" t="n">
-        <v>1.0829302072525</v>
+        <v>1.08293032646179</v>
       </c>
       <c r="H302" t="n">
         <v>259801</v>
@@ -9301,7 +9301,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G308" t="n">
-        <v>1.22098910808563</v>
+        <v>1.22098922729492</v>
       </c>
       <c r="H308" t="n">
         <v>47431</v>
@@ -9359,7 +9359,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G310" t="n">
-        <v>1.31694519519806</v>
+        <v>1.31694507598877</v>
       </c>
       <c r="H310" t="n">
         <v>204989</v>
@@ -9388,7 +9388,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G311" t="n">
-        <v>1.28267502784729</v>
+        <v>1.28267514705658</v>
       </c>
       <c r="H311" t="n">
         <v>321537</v>
@@ -9417,7 +9417,7 @@
         <v>1.29100000858307</v>
       </c>
       <c r="G312" t="n">
-        <v>1.26407134532928</v>
+        <v>1.26407146453857</v>
       </c>
       <c r="H312" t="n">
         <v>199047</v>
@@ -9446,7 +9446,7 @@
         <v>1.27100002765656</v>
       </c>
       <c r="G313" t="n">
-        <v>1.24448871612549</v>
+        <v>1.2444885969162</v>
       </c>
       <c r="H313" t="n">
         <v>96734</v>
@@ -9504,7 +9504,7 @@
         <v>1.25</v>
       </c>
       <c r="G315" t="n">
-        <v>1.22392654418945</v>
+        <v>1.22392666339874</v>
       </c>
       <c r="H315" t="n">
         <v>114680</v>
@@ -9765,7 +9765,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G324" t="n">
-        <v>1.32575726509094</v>
+        <v>1.32575738430023</v>
       </c>
       <c r="H324" t="n">
         <v>88859</v>
@@ -10142,7 +10142,7 @@
         <v>1.35699999332428</v>
       </c>
       <c r="G337" t="n">
-        <v>1.32869470119476</v>
+        <v>1.32869482040405</v>
       </c>
       <c r="H337" t="n">
         <v>108123</v>
@@ -10258,7 +10258,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G341" t="n">
-        <v>1.40996360778809</v>
+        <v>1.4099634885788</v>
       </c>
       <c r="H341" t="n">
         <v>114493</v>
@@ -10316,7 +10316,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G343" t="n">
-        <v>1.41975498199463</v>
+        <v>1.41975486278534</v>
       </c>
       <c r="H343" t="n">
         <v>91345</v>
@@ -10664,7 +10664,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>1.41975498199463</v>
+        <v>1.41975486278534</v>
       </c>
       <c r="H355" t="n">
         <v>66611</v>
@@ -10722,7 +10722,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G357" t="n">
-        <v>1.48437833786011</v>
+        <v>1.48437821865082</v>
       </c>
       <c r="H357" t="n">
         <v>402550</v>
@@ -10751,7 +10751,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>1.52746045589447</v>
+        <v>1.52746033668518</v>
       </c>
       <c r="H358" t="n">
         <v>214036</v>
@@ -10867,7 +10867,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G362" t="n">
-        <v>1.5264812707901</v>
+        <v>1.52648138999939</v>
       </c>
       <c r="H362" t="n">
         <v>108720</v>
@@ -10925,7 +10925,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G364" t="n">
-        <v>1.57641744613647</v>
+        <v>1.57641756534576</v>
       </c>
       <c r="H364" t="n">
         <v>87137</v>
@@ -10983,7 +10983,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G366" t="n">
-        <v>1.57445931434631</v>
+        <v>1.57445919513702</v>
       </c>
       <c r="H366" t="n">
         <v>153391</v>
@@ -11012,7 +11012,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G367" t="n">
-        <v>1.55879294872284</v>
+        <v>1.55879306793213</v>
       </c>
       <c r="H367" t="n">
         <v>59009</v>
@@ -11099,7 +11099,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G370" t="n">
-        <v>1.49319040775299</v>
+        <v>1.49319052696228</v>
       </c>
       <c r="H370" t="n">
         <v>198615</v>
@@ -11244,7 +11244,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G375" t="n">
-        <v>1.439337849617</v>
+        <v>1.43933773040771</v>
       </c>
       <c r="H375" t="n">
         <v>28060</v>
@@ -11360,7 +11360,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G379" t="n">
-        <v>1.48242008686066</v>
+        <v>1.48241996765137</v>
       </c>
       <c r="H379" t="n">
         <v>50853</v>
@@ -11418,7 +11418,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G381" t="n">
-        <v>1.46675360202789</v>
+        <v>1.46675372123718</v>
       </c>
       <c r="H381" t="n">
         <v>37418</v>
@@ -11795,7 +11795,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G394" t="n">
-        <v>1.38744330406189</v>
+        <v>1.3874431848526</v>
       </c>
       <c r="H394" t="n">
         <v>3217</v>
@@ -11882,7 +11882,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G397" t="n">
-        <v>1.46675360202789</v>
+        <v>1.46675372123718</v>
       </c>
       <c r="H397" t="n">
         <v>146942</v>
@@ -12288,7 +12288,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G411" t="n">
-        <v>1.49416959285736</v>
+        <v>1.49416971206665</v>
       </c>
       <c r="H411" t="n">
         <v>33895</v>
@@ -12491,7 +12491,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G418" t="n">
-        <v>1.88974273204803</v>
+        <v>1.88974261283875</v>
       </c>
       <c r="H418" t="n">
         <v>296041</v>
@@ -12549,7 +12549,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G420" t="n">
-        <v>1.94261634349823</v>
+        <v>1.94261622428894</v>
       </c>
       <c r="H420" t="n">
         <v>376100</v>
@@ -12636,7 +12636,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G423" t="n">
-        <v>1.88974273204803</v>
+        <v>1.88974261283875</v>
       </c>
       <c r="H423" t="n">
         <v>81649</v>
@@ -12694,7 +12694,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G425" t="n">
-        <v>2.165860414505</v>
+        <v>2.16586065292358</v>
       </c>
       <c r="H425" t="n">
         <v>662427</v>
@@ -12723,7 +12723,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>2.10515403747559</v>
+        <v>2.10515379905701</v>
       </c>
       <c r="H426" t="n">
         <v>303943</v>
@@ -12897,7 +12897,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G432" t="n">
-        <v>2.08361291885376</v>
+        <v>2.08361268043518</v>
       </c>
       <c r="H432" t="n">
         <v>120592</v>
@@ -12984,7 +12984,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G435" t="n">
-        <v>2.25398349761963</v>
+        <v>2.25398325920105</v>
       </c>
       <c r="H435" t="n">
         <v>446100</v>
@@ -13071,7 +13071,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G438" t="n">
-        <v>2.03857231140137</v>
+        <v>2.03857207298279</v>
       </c>
       <c r="H438" t="n">
         <v>376904</v>
@@ -13303,7 +13303,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G446" t="n">
-        <v>1.93086659908295</v>
+        <v>1.93086671829224</v>
       </c>
       <c r="H446" t="n">
         <v>226358</v>
@@ -13448,7 +13448,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G451" t="n">
-        <v>2.0150728225708</v>
+        <v>2.01507306098938</v>
       </c>
       <c r="H451" t="n">
         <v>124152</v>
@@ -13477,7 +13477,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G452" t="n">
-        <v>2.0150728225708</v>
+        <v>2.01507306098938</v>
       </c>
       <c r="H452" t="n">
         <v>122037</v>
@@ -13535,7 +13535,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G454" t="n">
-        <v>1.98569869995117</v>
+        <v>1.98569881916046</v>
       </c>
       <c r="H454" t="n">
         <v>31437</v>
@@ -13593,7 +13593,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G456" t="n">
-        <v>2.00723958015442</v>
+        <v>2.007239818573</v>
       </c>
       <c r="H456" t="n">
         <v>34457</v>
@@ -13622,7 +13622,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G457" t="n">
-        <v>2.0150728225708</v>
+        <v>2.01507306098938</v>
       </c>
       <c r="H457" t="n">
         <v>166275</v>
@@ -13738,7 +13738,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G461" t="n">
-        <v>1.98374044895172</v>
+        <v>1.98374032974243</v>
       </c>
       <c r="H461" t="n">
         <v>168464</v>
@@ -13767,7 +13767,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G462" t="n">
-        <v>1.95632433891296</v>
+        <v>1.95632445812225</v>
       </c>
       <c r="H462" t="n">
         <v>77596</v>
@@ -13825,7 +13825,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G464" t="n">
-        <v>1.98569869995117</v>
+        <v>1.98569881916046</v>
       </c>
       <c r="H464" t="n">
         <v>420317</v>
@@ -14144,7 +14144,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>1.93869984149933</v>
+        <v>1.93869972229004</v>
       </c>
       <c r="H475" t="n">
         <v>77792</v>
@@ -14463,7 +14463,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>1.93869984149933</v>
+        <v>1.93869972229004</v>
       </c>
       <c r="H486" t="n">
         <v>58282</v>
@@ -14550,7 +14550,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G489" t="n">
-        <v>2.05228018760681</v>
+        <v>2.05227994918823</v>
       </c>
       <c r="H489" t="n">
         <v>365431</v>
@@ -14579,7 +14579,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G490" t="n">
-        <v>2.00723958015442</v>
+        <v>2.007239818573</v>
       </c>
       <c r="H490" t="n">
         <v>127429</v>
@@ -14608,7 +14608,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G491" t="n">
-        <v>2.00723958015442</v>
+        <v>2.007239818573</v>
       </c>
       <c r="H491" t="n">
         <v>16967</v>
@@ -14869,7 +14869,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>1.9778653383255</v>
+        <v>1.97786545753479</v>
       </c>
       <c r="H500" t="n">
         <v>25172</v>
@@ -14898,7 +14898,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>1.9778653383255</v>
+        <v>1.97786545753479</v>
       </c>
       <c r="H501" t="n">
         <v>40934</v>
@@ -15101,7 +15101,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G508" t="n">
-        <v>1.93674147129059</v>
+        <v>1.93674159049988</v>
       </c>
       <c r="H508" t="n">
         <v>1738</v>
@@ -15246,7 +15246,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G513" t="n">
-        <v>1.89953422546387</v>
+        <v>1.89953410625458</v>
       </c>
       <c r="H513" t="n">
         <v>8507</v>
@@ -15333,7 +15333,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G516" t="n">
-        <v>1.9778653383255</v>
+        <v>1.97786545753479</v>
       </c>
       <c r="H516" t="n">
         <v>80856</v>
@@ -15507,7 +15507,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G522" t="n">
-        <v>1.95632433891296</v>
+        <v>1.95632445812225</v>
       </c>
       <c r="H522" t="n">
         <v>18050</v>
@@ -15536,7 +15536,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G523" t="n">
-        <v>1.96807408332825</v>
+        <v>1.96807396411896</v>
       </c>
       <c r="H523" t="n">
         <v>20616</v>
@@ -15623,7 +15623,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G526" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H526" t="n">
         <v>452689</v>
@@ -15942,7 +15942,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.10515403747559</v>
+        <v>2.10515379905701</v>
       </c>
       <c r="H537" t="n">
         <v>139101</v>
@@ -15971,7 +15971,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>2.10515403747559</v>
+        <v>2.10515379905701</v>
       </c>
       <c r="H538" t="n">
         <v>48637</v>
@@ -16058,7 +16058,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G541" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H541" t="n">
         <v>177454</v>
@@ -16087,7 +16087,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H542" t="n">
         <v>49635</v>
@@ -16145,7 +16145,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>2.18348526954651</v>
+        <v>2.18348503112793</v>
       </c>
       <c r="H544" t="n">
         <v>46864</v>
@@ -16203,7 +16203,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G546" t="n">
-        <v>2.19817209243774</v>
+        <v>2.19817233085632</v>
       </c>
       <c r="H546" t="n">
         <v>50060</v>
@@ -16232,7 +16232,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G547" t="n">
-        <v>2.18348526954651</v>
+        <v>2.18348503112793</v>
       </c>
       <c r="H547" t="n">
         <v>16948</v>
@@ -16261,7 +16261,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G548" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H548" t="n">
         <v>72087</v>
@@ -16319,7 +16319,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G550" t="n">
-        <v>2.19327640533447</v>
+        <v>2.19327664375305</v>
       </c>
       <c r="H550" t="n">
         <v>215281</v>
@@ -16348,7 +16348,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G551" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H551" t="n">
         <v>27372</v>
@@ -16377,7 +16377,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H552" t="n">
         <v>17856</v>
@@ -80009,6 +80009,35 @@
         <v>26354</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>1.82799994945526</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>1.78600001335144</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>33165</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -485,7 +485,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G4" t="n">
-        <v>0.905705749988556</v>
+        <v>0.905705690383911</v>
       </c>
       <c r="H4" t="n">
         <v>67070</v>
@@ -514,7 +514,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G5" t="n">
-        <v>0.845978081226349</v>
+        <v>0.845978140830994</v>
       </c>
       <c r="H5" t="n">
         <v>488400</v>
@@ -572,7 +572,7 @@
         <v>0.838500022888184</v>
       </c>
       <c r="G7" t="n">
-        <v>0.821009993553162</v>
+        <v>0.821010053157806</v>
       </c>
       <c r="H7" t="n">
         <v>198049</v>
@@ -630,7 +630,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G9" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H9" t="n">
         <v>126512</v>
@@ -746,7 +746,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G13" t="n">
-        <v>0.704981744289398</v>
+        <v>0.704981803894043</v>
       </c>
       <c r="H13" t="n">
         <v>214274</v>
@@ -804,7 +804,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G15" t="n">
-        <v>0.741699576377869</v>
+        <v>0.741699516773224</v>
       </c>
       <c r="H15" t="n">
         <v>111111</v>
@@ -862,7 +862,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G17" t="n">
-        <v>0.805833339691162</v>
+        <v>0.805833280086517</v>
       </c>
       <c r="H17" t="n">
         <v>154076</v>
@@ -891,7 +891,7 @@
         <v>0.799499988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>0.782823503017426</v>
+        <v>0.782823443412781</v>
       </c>
       <c r="H18" t="n">
         <v>96322</v>
@@ -920,7 +920,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G19" t="n">
-        <v>0.769605100154877</v>
+        <v>0.769605040550232</v>
       </c>
       <c r="H19" t="n">
         <v>46236</v>
@@ -1181,7 +1181,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G28" t="n">
-        <v>0.741699576377869</v>
+        <v>0.741699516773224</v>
       </c>
       <c r="H28" t="n">
         <v>88730</v>
@@ -1384,7 +1384,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G35" t="n">
-        <v>0.846957266330719</v>
+        <v>0.846957206726074</v>
       </c>
       <c r="H35" t="n">
         <v>118859</v>
@@ -1413,7 +1413,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G36" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H36" t="n">
         <v>64920</v>
@@ -1877,7 +1877,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G52" t="n">
-        <v>0.81464558839798</v>
+        <v>0.814645528793335</v>
       </c>
       <c r="H52" t="n">
         <v>31840</v>
@@ -1906,7 +1906,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G53" t="n">
-        <v>0.820520460605621</v>
+        <v>0.820520401000977</v>
       </c>
       <c r="H53" t="n">
         <v>49839</v>
@@ -2051,7 +2051,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G58" t="n">
-        <v>0.862623453140259</v>
+        <v>0.862623512744904</v>
       </c>
       <c r="H58" t="n">
         <v>72793</v>
@@ -2080,7 +2080,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G59" t="n">
-        <v>0.840103268623352</v>
+        <v>0.840103209018707</v>
       </c>
       <c r="H59" t="n">
         <v>45401</v>
@@ -2196,7 +2196,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G63" t="n">
-        <v>0.829332709312439</v>
+        <v>0.829332649707794</v>
       </c>
       <c r="H63" t="n">
         <v>10567</v>
@@ -2254,7 +2254,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G65" t="n">
-        <v>0.829332709312439</v>
+        <v>0.829332649707794</v>
       </c>
       <c r="H65" t="n">
         <v>7361</v>
@@ -2283,7 +2283,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H66" t="n">
         <v>10600</v>
@@ -2312,7 +2312,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G67" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0.847500026226044</v>
       </c>
       <c r="G69" t="n">
-        <v>0.829822242259979</v>
+        <v>0.829822301864624</v>
       </c>
       <c r="H69" t="n">
         <v>46571</v>
@@ -2660,7 +2660,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G79" t="n">
-        <v>0.810239374637604</v>
+        <v>0.810239434242249</v>
       </c>
       <c r="H79" t="n">
         <v>5486</v>
@@ -2689,7 +2689,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G80" t="n">
-        <v>0.808770656585693</v>
+        <v>0.808770716190338</v>
       </c>
       <c r="H80" t="n">
         <v>1771</v>
@@ -2718,7 +2718,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G81" t="n">
-        <v>0.810239374637604</v>
+        <v>0.810239434242249</v>
       </c>
       <c r="H81" t="n">
         <v>5329</v>
@@ -2747,7 +2747,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G82" t="n">
-        <v>0.808770656585693</v>
+        <v>0.808770716190338</v>
       </c>
       <c r="H82" t="n">
         <v>2500</v>
@@ -3066,7 +3066,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G93" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H93" t="n">
         <v>2843</v>
@@ -3182,7 +3182,7 @@
         <v>0.863499999046326</v>
       </c>
       <c r="G97" t="n">
-        <v>0.845488548278809</v>
+        <v>0.845488488674164</v>
       </c>
       <c r="H97" t="n">
         <v>51892</v>
@@ -3211,7 +3211,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G98" t="n">
-        <v>0.842061579227448</v>
+        <v>0.842061519622803</v>
       </c>
       <c r="H98" t="n">
         <v>8247</v>
@@ -3588,7 +3588,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G111" t="n">
-        <v>0.906684815883636</v>
+        <v>0.906684875488281</v>
       </c>
       <c r="H111" t="n">
         <v>24383</v>
@@ -3675,7 +3675,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G114" t="n">
-        <v>0.910601377487183</v>
+        <v>0.910601437091827</v>
       </c>
       <c r="H114" t="n">
         <v>65821</v>
@@ -3820,7 +3820,7 @@
         <v>0.927500009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>0.908153593540192</v>
+        <v>0.908153533935547</v>
       </c>
       <c r="H119" t="n">
         <v>29744</v>
@@ -3965,7 +3965,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>0.905216097831726</v>
+        <v>0.905216157436371</v>
       </c>
       <c r="H124" t="n">
         <v>130254</v>
@@ -3994,7 +3994,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G125" t="n">
-        <v>0.900810062885284</v>
+        <v>0.90081000328064</v>
       </c>
       <c r="H125" t="n">
         <v>35381</v>
@@ -4197,7 +4197,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G132" t="n">
-        <v>0.877310633659363</v>
+        <v>0.877310693264008</v>
       </c>
       <c r="H132" t="n">
         <v>15386</v>
@@ -4284,7 +4284,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G135" t="n">
-        <v>0.899830877780914</v>
+        <v>0.899830937385559</v>
       </c>
       <c r="H135" t="n">
         <v>87599</v>
@@ -4458,7 +4458,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G141" t="n">
-        <v>0.910601377487183</v>
+        <v>0.910601437091827</v>
       </c>
       <c r="H141" t="n">
         <v>16200</v>
@@ -4487,7 +4487,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G142" t="n">
-        <v>0.930184185504913</v>
+        <v>0.930184245109558</v>
       </c>
       <c r="H142" t="n">
         <v>53191</v>
@@ -4574,7 +4574,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G145" t="n">
-        <v>0.910601377487183</v>
+        <v>0.910601437091827</v>
       </c>
       <c r="H145" t="n">
         <v>11693</v>
@@ -4661,7 +4661,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G148" t="n">
-        <v>0.905705749988556</v>
+        <v>0.905705690383911</v>
       </c>
       <c r="H148" t="n">
         <v>14838</v>
@@ -4690,7 +4690,7 @@
         <v>0.912500023841858</v>
       </c>
       <c r="G149" t="n">
-        <v>0.893466472625732</v>
+        <v>0.893466413021088</v>
       </c>
       <c r="H149" t="n">
         <v>11522</v>
@@ -4951,7 +4951,7 @@
         <v>0.918500006198883</v>
       </c>
       <c r="G158" t="n">
-        <v>0.899341344833374</v>
+        <v>0.899341285228729</v>
       </c>
       <c r="H158" t="n">
         <v>20356</v>
@@ -5009,7 +5009,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G160" t="n">
-        <v>0.899830877780914</v>
+        <v>0.899830937385559</v>
       </c>
       <c r="H160" t="n">
         <v>4032</v>
@@ -5067,7 +5067,7 @@
         <v>0.907000005245209</v>
       </c>
       <c r="G162" t="n">
-        <v>0.888081192970276</v>
+        <v>0.888081133365631</v>
       </c>
       <c r="H162" t="n">
         <v>5150</v>
@@ -5415,7 +5415,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G174" t="n">
-        <v>0.889060258865356</v>
+        <v>0.889060318470001</v>
       </c>
       <c r="H174" t="n">
         <v>7586</v>
@@ -5444,7 +5444,7 @@
         <v>0.911499977111816</v>
       </c>
       <c r="G175" t="n">
-        <v>0.892487227916718</v>
+        <v>0.892487287521362</v>
       </c>
       <c r="H175" t="n">
         <v>49377</v>
@@ -5531,7 +5531,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G178" t="n">
-        <v>0.988932728767395</v>
+        <v>0.98893266916275</v>
       </c>
       <c r="H178" t="n">
         <v>69152</v>
@@ -5560,7 +5560,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G179" t="n">
-        <v>1.01243209838867</v>
+        <v>1.01243221759796</v>
       </c>
       <c r="H179" t="n">
         <v>167469</v>
@@ -5618,7 +5618,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G181" t="n">
-        <v>0.978162229061127</v>
+        <v>0.978162169456482</v>
       </c>
       <c r="H181" t="n">
         <v>92947</v>
@@ -5676,7 +5676,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G183" t="n">
-        <v>0.949767053127289</v>
+        <v>0.949767112731934</v>
       </c>
       <c r="H183" t="n">
         <v>91824</v>
@@ -5705,7 +5705,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G184" t="n">
-        <v>0.965433359146118</v>
+        <v>0.965433299541473</v>
       </c>
       <c r="H184" t="n">
         <v>227509</v>
@@ -5734,7 +5734,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G185" t="n">
-        <v>0.978162229061127</v>
+        <v>0.978162169456482</v>
       </c>
       <c r="H185" t="n">
         <v>24534</v>
@@ -5821,7 +5821,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H188" t="n">
         <v>33543</v>
@@ -5937,7 +5937,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G192" t="n">
-        <v>0.963475108146667</v>
+        <v>0.963475048542023</v>
       </c>
       <c r="H192" t="n">
         <v>195703</v>
@@ -5966,7 +5966,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G193" t="n">
-        <v>0.963475108146667</v>
+        <v>0.963475048542023</v>
       </c>
       <c r="H193" t="n">
         <v>120124</v>
@@ -6024,7 +6024,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H195" t="n">
         <v>5609</v>
@@ -6053,7 +6053,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G196" t="n">
-        <v>0.970818638801575</v>
+        <v>0.97081857919693</v>
       </c>
       <c r="H196" t="n">
         <v>51474</v>
@@ -6082,7 +6082,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G197" t="n">
-        <v>0.978162229061127</v>
+        <v>0.978162169456482</v>
       </c>
       <c r="H197" t="n">
         <v>23009</v>
@@ -6198,7 +6198,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G201" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H201" t="n">
         <v>100047</v>
@@ -6314,7 +6314,7 @@
         <v>0.989000022411346</v>
       </c>
       <c r="G205" t="n">
-        <v>0.968370795249939</v>
+        <v>0.968370735645294</v>
       </c>
       <c r="H205" t="n">
         <v>36445</v>
@@ -6372,7 +6372,7 @@
         <v>0.984499990940094</v>
       </c>
       <c r="G207" t="n">
-        <v>0.963964581489563</v>
+        <v>0.963964641094208</v>
       </c>
       <c r="H207" t="n">
         <v>31937</v>
@@ -6517,7 +6517,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H212" t="n">
         <v>27813</v>
@@ -6546,7 +6546,7 @@
         <v>0.988499999046326</v>
       </c>
       <c r="G213" t="n">
-        <v>0.967881143093109</v>
+        <v>0.967881202697754</v>
       </c>
       <c r="H213" t="n">
         <v>28095</v>
@@ -6604,7 +6604,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G215" t="n">
-        <v>0.984036982059479</v>
+        <v>0.984037041664124</v>
       </c>
       <c r="H215" t="n">
         <v>16570</v>
@@ -6633,7 +6633,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G216" t="n">
-        <v>0.970818638801575</v>
+        <v>0.97081857919693</v>
       </c>
       <c r="H216" t="n">
         <v>41278</v>
@@ -6807,7 +6807,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G222" t="n">
-        <v>0.949767053127289</v>
+        <v>0.949767112731934</v>
       </c>
       <c r="H222" t="n">
         <v>32136</v>
@@ -6865,7 +6865,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G224" t="n">
-        <v>0.941933989524841</v>
+        <v>0.941933929920197</v>
       </c>
       <c r="H224" t="n">
         <v>5100</v>
@@ -6894,7 +6894,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G225" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H225" t="n">
         <v>125</v>
@@ -6923,7 +6923,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G226" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H226" t="n">
         <v>18525</v>
@@ -6952,7 +6952,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G227" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H227" t="n">
         <v>2641</v>
@@ -7010,7 +7010,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G229" t="n">
-        <v>0.903747379779816</v>
+        <v>0.90374743938446</v>
       </c>
       <c r="H229" t="n">
         <v>18509</v>
@@ -7097,7 +7097,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G232" t="n">
-        <v>0.905216097831726</v>
+        <v>0.905216157436371</v>
       </c>
       <c r="H232" t="n">
         <v>21022</v>
@@ -7213,7 +7213,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G236" t="n">
-        <v>0.902768313884735</v>
+        <v>0.90276825428009</v>
       </c>
       <c r="H236" t="n">
         <v>12738</v>
@@ -7242,7 +7242,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G237" t="n">
-        <v>0.902768313884735</v>
+        <v>0.90276825428009</v>
       </c>
       <c r="H237" t="n">
         <v>250</v>
@@ -7271,7 +7271,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G238" t="n">
-        <v>0.905216097831726</v>
+        <v>0.905216157436371</v>
       </c>
       <c r="H238" t="n">
         <v>12284</v>
@@ -7648,7 +7648,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G251" t="n">
-        <v>0.910601377487183</v>
+        <v>0.910601437091827</v>
       </c>
       <c r="H251" t="n">
         <v>31468</v>
@@ -7677,7 +7677,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G252" t="n">
-        <v>0.899830877780914</v>
+        <v>0.899830937385559</v>
       </c>
       <c r="H252" t="n">
         <v>15949</v>
@@ -7706,7 +7706,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G253" t="n">
-        <v>0.900810062885284</v>
+        <v>0.90081000328064</v>
       </c>
       <c r="H253" t="n">
         <v>3795</v>
@@ -7764,7 +7764,7 @@
         <v>0.938499987125397</v>
       </c>
       <c r="G255" t="n">
-        <v>0.918924152851105</v>
+        <v>0.91892409324646</v>
       </c>
       <c r="H255" t="n">
         <v>9204</v>
@@ -7851,7 +7851,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G258" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H258" t="n">
         <v>28836</v>
@@ -7909,7 +7909,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G260" t="n">
-        <v>0.932142555713654</v>
+        <v>0.932142496109009</v>
       </c>
       <c r="H260" t="n">
         <v>20022</v>
@@ -7967,7 +7967,7 @@
         <v>0.989000022411346</v>
       </c>
       <c r="G262" t="n">
-        <v>0.968370795249939</v>
+        <v>0.968370735645294</v>
       </c>
       <c r="H262" t="n">
         <v>22001</v>
@@ -8083,7 +8083,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G266" t="n">
-        <v>0.956621110439301</v>
+        <v>0.956621050834656</v>
       </c>
       <c r="H266" t="n">
         <v>146793</v>
@@ -8170,7 +8170,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G269" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H269" t="n">
         <v>69497</v>
@@ -8199,7 +8199,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H270" t="n">
         <v>61895</v>
@@ -8373,7 +8373,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H276" t="n">
         <v>31565</v>
@@ -8431,7 +8431,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>0.956621110439301</v>
+        <v>0.956621050834656</v>
       </c>
       <c r="H278" t="n">
         <v>48455</v>
@@ -8460,7 +8460,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G279" t="n">
-        <v>0.949767053127289</v>
+        <v>0.949767112731934</v>
       </c>
       <c r="H279" t="n">
         <v>34223</v>
@@ -8489,7 +8489,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H280" t="n">
         <v>16506</v>
@@ -8518,7 +8518,7 @@
         <v>0.987500011920929</v>
       </c>
       <c r="G281" t="n">
-        <v>0.966902077198029</v>
+        <v>0.966902017593384</v>
       </c>
       <c r="H281" t="n">
         <v>2162</v>
@@ -8576,7 +8576,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>0.956621110439301</v>
+        <v>0.956621050834656</v>
       </c>
       <c r="H283" t="n">
         <v>8218</v>
@@ -8605,7 +8605,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G284" t="n">
-        <v>0.965433359146118</v>
+        <v>0.965433299541473</v>
       </c>
       <c r="H284" t="n">
         <v>4642</v>
@@ -8750,7 +8750,7 @@
         <v>0.986999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>0.966412425041199</v>
+        <v>0.966412484645844</v>
       </c>
       <c r="H289" t="n">
         <v>37264</v>
@@ -8808,7 +8808,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G291" t="n">
-        <v>0.983057856559753</v>
+        <v>0.983057796955109</v>
       </c>
       <c r="H291" t="n">
         <v>27881</v>
@@ -8837,7 +8837,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G292" t="n">
-        <v>0.986974477767944</v>
+        <v>0.9869744181633</v>
       </c>
       <c r="H292" t="n">
         <v>63522</v>
@@ -8866,7 +8866,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G293" t="n">
-        <v>0.983057856559753</v>
+        <v>0.983057796955109</v>
       </c>
       <c r="H293" t="n">
         <v>53865</v>
@@ -8924,7 +8924,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G295" t="n">
-        <v>0.988932728767395</v>
+        <v>0.98893266916275</v>
       </c>
       <c r="H295" t="n">
         <v>40379</v>
@@ -8982,7 +8982,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H297" t="n">
         <v>20659</v>
@@ -9011,7 +9011,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G298" t="n">
-        <v>0.981099545955658</v>
+        <v>0.981099605560303</v>
       </c>
       <c r="H298" t="n">
         <v>114382</v>
@@ -9069,7 +9069,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>1.01830697059631</v>
+        <v>1.01830685138702</v>
       </c>
       <c r="H300" t="n">
         <v>269003</v>
@@ -9098,7 +9098,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G301" t="n">
-        <v>1.0525768995285</v>
+        <v>1.05257701873779</v>
       </c>
       <c r="H301" t="n">
         <v>358002</v>
@@ -9127,7 +9127,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G302" t="n">
-        <v>1.08293032646179</v>
+        <v>1.0829302072525</v>
       </c>
       <c r="H302" t="n">
         <v>259801</v>
@@ -9301,7 +9301,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G308" t="n">
-        <v>1.22098922729492</v>
+        <v>1.22098910808563</v>
       </c>
       <c r="H308" t="n">
         <v>47431</v>
@@ -9359,7 +9359,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G310" t="n">
-        <v>1.31694507598877</v>
+        <v>1.31694519519806</v>
       </c>
       <c r="H310" t="n">
         <v>204989</v>
@@ -9388,7 +9388,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G311" t="n">
-        <v>1.28267514705658</v>
+        <v>1.28267502784729</v>
       </c>
       <c r="H311" t="n">
         <v>321537</v>
@@ -9417,7 +9417,7 @@
         <v>1.29100000858307</v>
       </c>
       <c r="G312" t="n">
-        <v>1.26407146453857</v>
+        <v>1.26407134532928</v>
       </c>
       <c r="H312" t="n">
         <v>199047</v>
@@ -9446,7 +9446,7 @@
         <v>1.27100002765656</v>
       </c>
       <c r="G313" t="n">
-        <v>1.2444885969162</v>
+        <v>1.24448871612549</v>
       </c>
       <c r="H313" t="n">
         <v>96734</v>
@@ -9504,7 +9504,7 @@
         <v>1.25</v>
       </c>
       <c r="G315" t="n">
-        <v>1.22392666339874</v>
+        <v>1.22392654418945</v>
       </c>
       <c r="H315" t="n">
         <v>114680</v>
@@ -9765,7 +9765,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G324" t="n">
-        <v>1.32575738430023</v>
+        <v>1.32575726509094</v>
       </c>
       <c r="H324" t="n">
         <v>88859</v>
@@ -10142,7 +10142,7 @@
         <v>1.35699999332428</v>
       </c>
       <c r="G337" t="n">
-        <v>1.32869482040405</v>
+        <v>1.32869470119476</v>
       </c>
       <c r="H337" t="n">
         <v>108123</v>
@@ -10258,7 +10258,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G341" t="n">
-        <v>1.4099634885788</v>
+        <v>1.40996360778809</v>
       </c>
       <c r="H341" t="n">
         <v>114493</v>
@@ -10316,7 +10316,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G343" t="n">
-        <v>1.41975486278534</v>
+        <v>1.41975498199463</v>
       </c>
       <c r="H343" t="n">
         <v>91345</v>
@@ -10664,7 +10664,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>1.41975486278534</v>
+        <v>1.41975498199463</v>
       </c>
       <c r="H355" t="n">
         <v>66611</v>
@@ -10722,7 +10722,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G357" t="n">
-        <v>1.48437821865082</v>
+        <v>1.48437833786011</v>
       </c>
       <c r="H357" t="n">
         <v>402550</v>
@@ -10751,7 +10751,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>1.52746033668518</v>
+        <v>1.52746045589447</v>
       </c>
       <c r="H358" t="n">
         <v>214036</v>
@@ -10867,7 +10867,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G362" t="n">
-        <v>1.52648138999939</v>
+        <v>1.5264812707901</v>
       </c>
       <c r="H362" t="n">
         <v>108720</v>
@@ -10925,7 +10925,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G364" t="n">
-        <v>1.57641756534576</v>
+        <v>1.57641744613647</v>
       </c>
       <c r="H364" t="n">
         <v>87137</v>
@@ -10983,7 +10983,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G366" t="n">
-        <v>1.57445919513702</v>
+        <v>1.57445931434631</v>
       </c>
       <c r="H366" t="n">
         <v>153391</v>
@@ -11012,7 +11012,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G367" t="n">
-        <v>1.55879306793213</v>
+        <v>1.55879294872284</v>
       </c>
       <c r="H367" t="n">
         <v>59009</v>
@@ -11099,7 +11099,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G370" t="n">
-        <v>1.49319052696228</v>
+        <v>1.49319040775299</v>
       </c>
       <c r="H370" t="n">
         <v>198615</v>
@@ -11244,7 +11244,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G375" t="n">
-        <v>1.43933773040771</v>
+        <v>1.439337849617</v>
       </c>
       <c r="H375" t="n">
         <v>28060</v>
@@ -11360,7 +11360,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G379" t="n">
-        <v>1.48241996765137</v>
+        <v>1.48242008686066</v>
       </c>
       <c r="H379" t="n">
         <v>50853</v>
@@ -11418,7 +11418,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G381" t="n">
-        <v>1.46675372123718</v>
+        <v>1.46675360202789</v>
       </c>
       <c r="H381" t="n">
         <v>37418</v>
@@ -11795,7 +11795,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G394" t="n">
-        <v>1.3874431848526</v>
+        <v>1.38744330406189</v>
       </c>
       <c r="H394" t="n">
         <v>3217</v>
@@ -11882,7 +11882,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G397" t="n">
-        <v>1.46675372123718</v>
+        <v>1.46675360202789</v>
       </c>
       <c r="H397" t="n">
         <v>146942</v>
@@ -12288,7 +12288,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G411" t="n">
-        <v>1.49416971206665</v>
+        <v>1.49416959285736</v>
       </c>
       <c r="H411" t="n">
         <v>33895</v>
@@ -12491,7 +12491,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G418" t="n">
-        <v>1.88974261283875</v>
+        <v>1.88974273204803</v>
       </c>
       <c r="H418" t="n">
         <v>296041</v>
@@ -12549,7 +12549,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G420" t="n">
-        <v>1.94261622428894</v>
+        <v>1.94261634349823</v>
       </c>
       <c r="H420" t="n">
         <v>376100</v>
@@ -12636,7 +12636,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G423" t="n">
-        <v>1.88974261283875</v>
+        <v>1.88974273204803</v>
       </c>
       <c r="H423" t="n">
         <v>81649</v>
@@ -12694,7 +12694,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G425" t="n">
-        <v>2.16586065292358</v>
+        <v>2.165860414505</v>
       </c>
       <c r="H425" t="n">
         <v>662427</v>
@@ -12723,7 +12723,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>2.10515379905701</v>
+        <v>2.10515403747559</v>
       </c>
       <c r="H426" t="n">
         <v>303943</v>
@@ -12897,7 +12897,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G432" t="n">
-        <v>2.08361268043518</v>
+        <v>2.08361291885376</v>
       </c>
       <c r="H432" t="n">
         <v>120592</v>
@@ -12984,7 +12984,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G435" t="n">
-        <v>2.25398325920105</v>
+        <v>2.25398349761963</v>
       </c>
       <c r="H435" t="n">
         <v>446100</v>
@@ -13071,7 +13071,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G438" t="n">
-        <v>2.03857207298279</v>
+        <v>2.03857231140137</v>
       </c>
       <c r="H438" t="n">
         <v>376904</v>
@@ -13303,7 +13303,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G446" t="n">
-        <v>1.93086671829224</v>
+        <v>1.93086659908295</v>
       </c>
       <c r="H446" t="n">
         <v>226358</v>
@@ -13448,7 +13448,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G451" t="n">
-        <v>2.01507306098938</v>
+        <v>2.0150728225708</v>
       </c>
       <c r="H451" t="n">
         <v>124152</v>
@@ -13477,7 +13477,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G452" t="n">
-        <v>2.01507306098938</v>
+        <v>2.0150728225708</v>
       </c>
       <c r="H452" t="n">
         <v>122037</v>
@@ -13535,7 +13535,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G454" t="n">
-        <v>1.98569881916046</v>
+        <v>1.98569869995117</v>
       </c>
       <c r="H454" t="n">
         <v>31437</v>
@@ -13593,7 +13593,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G456" t="n">
-        <v>2.007239818573</v>
+        <v>2.00723958015442</v>
       </c>
       <c r="H456" t="n">
         <v>34457</v>
@@ -13622,7 +13622,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G457" t="n">
-        <v>2.01507306098938</v>
+        <v>2.0150728225708</v>
       </c>
       <c r="H457" t="n">
         <v>166275</v>
@@ -13738,7 +13738,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G461" t="n">
-        <v>1.98374032974243</v>
+        <v>1.98374044895172</v>
       </c>
       <c r="H461" t="n">
         <v>168464</v>
@@ -13767,7 +13767,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G462" t="n">
-        <v>1.95632445812225</v>
+        <v>1.95632433891296</v>
       </c>
       <c r="H462" t="n">
         <v>77596</v>
@@ -13825,7 +13825,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G464" t="n">
-        <v>1.98569881916046</v>
+        <v>1.98569869995117</v>
       </c>
       <c r="H464" t="n">
         <v>420317</v>
@@ -14144,7 +14144,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>1.93869972229004</v>
+        <v>1.93869984149933</v>
       </c>
       <c r="H475" t="n">
         <v>77792</v>
@@ -14463,7 +14463,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>1.93869972229004</v>
+        <v>1.93869984149933</v>
       </c>
       <c r="H486" t="n">
         <v>58282</v>
@@ -14550,7 +14550,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G489" t="n">
-        <v>2.05227994918823</v>
+        <v>2.05228018760681</v>
       </c>
       <c r="H489" t="n">
         <v>365431</v>
@@ -14579,7 +14579,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G490" t="n">
-        <v>2.007239818573</v>
+        <v>2.00723958015442</v>
       </c>
       <c r="H490" t="n">
         <v>127429</v>
@@ -14608,7 +14608,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G491" t="n">
-        <v>2.007239818573</v>
+        <v>2.00723958015442</v>
       </c>
       <c r="H491" t="n">
         <v>16967</v>
@@ -14869,7 +14869,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>1.97786545753479</v>
+        <v>1.9778653383255</v>
       </c>
       <c r="H500" t="n">
         <v>25172</v>
@@ -14898,7 +14898,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>1.97786545753479</v>
+        <v>1.9778653383255</v>
       </c>
       <c r="H501" t="n">
         <v>40934</v>
@@ -15101,7 +15101,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G508" t="n">
-        <v>1.93674159049988</v>
+        <v>1.93674147129059</v>
       </c>
       <c r="H508" t="n">
         <v>1738</v>
@@ -15246,7 +15246,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G513" t="n">
-        <v>1.89953410625458</v>
+        <v>1.89953422546387</v>
       </c>
       <c r="H513" t="n">
         <v>8507</v>
@@ -15333,7 +15333,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G516" t="n">
-        <v>1.97786545753479</v>
+        <v>1.9778653383255</v>
       </c>
       <c r="H516" t="n">
         <v>80856</v>
@@ -15507,7 +15507,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G522" t="n">
-        <v>1.95632445812225</v>
+        <v>1.95632433891296</v>
       </c>
       <c r="H522" t="n">
         <v>18050</v>
@@ -15536,7 +15536,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G523" t="n">
-        <v>1.96807396411896</v>
+        <v>1.96807408332825</v>
       </c>
       <c r="H523" t="n">
         <v>20616</v>
@@ -15623,7 +15623,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G526" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H526" t="n">
         <v>452689</v>
@@ -15942,7 +15942,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.10515379905701</v>
+        <v>2.10515403747559</v>
       </c>
       <c r="H537" t="n">
         <v>139101</v>
@@ -15971,7 +15971,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>2.10515379905701</v>
+        <v>2.10515403747559</v>
       </c>
       <c r="H538" t="n">
         <v>48637</v>
@@ -16058,7 +16058,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G541" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H541" t="n">
         <v>177454</v>
@@ -16087,7 +16087,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H542" t="n">
         <v>49635</v>
@@ -16145,7 +16145,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>2.18348503112793</v>
+        <v>2.18348526954651</v>
       </c>
       <c r="H544" t="n">
         <v>46864</v>
@@ -16203,7 +16203,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G546" t="n">
-        <v>2.19817233085632</v>
+        <v>2.19817209243774</v>
       </c>
       <c r="H546" t="n">
         <v>50060</v>
@@ -16232,7 +16232,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G547" t="n">
-        <v>2.18348503112793</v>
+        <v>2.18348526954651</v>
       </c>
       <c r="H547" t="n">
         <v>16948</v>
@@ -16261,7 +16261,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G548" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H548" t="n">
         <v>72087</v>
@@ -16319,7 +16319,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G550" t="n">
-        <v>2.19327664375305</v>
+        <v>2.19327640533447</v>
       </c>
       <c r="H550" t="n">
         <v>215281</v>
@@ -16348,7 +16348,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G551" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H551" t="n">
         <v>27372</v>
@@ -16377,7 +16377,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H552" t="n">
         <v>17856</v>
@@ -80038,6 +80038,35 @@
         <v>33165</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>1.78799998760223</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>1.82799994945526</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>1.78799998760223</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>14102</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -80070,6 +80070,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>1.82000005245209</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>1.78799998760223</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>1.78600001335144</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>1.78600001335144</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>13467</v>
+      </c>
+      <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -485,7 +485,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G4" t="n">
-        <v>0.905705690383911</v>
+        <v>0.905705749988556</v>
       </c>
       <c r="H4" t="n">
         <v>67070</v>
@@ -514,7 +514,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G5" t="n">
-        <v>0.845978140830994</v>
+        <v>0.845978081226349</v>
       </c>
       <c r="H5" t="n">
         <v>488400</v>
@@ -572,7 +572,7 @@
         <v>0.838500022888184</v>
       </c>
       <c r="G7" t="n">
-        <v>0.821010053157806</v>
+        <v>0.821009993553162</v>
       </c>
       <c r="H7" t="n">
         <v>198049</v>
@@ -630,7 +630,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G9" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H9" t="n">
         <v>126512</v>
@@ -746,7 +746,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G13" t="n">
-        <v>0.704981803894043</v>
+        <v>0.704981744289398</v>
       </c>
       <c r="H13" t="n">
         <v>214274</v>
@@ -804,7 +804,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G15" t="n">
-        <v>0.741699516773224</v>
+        <v>0.741699576377869</v>
       </c>
       <c r="H15" t="n">
         <v>111111</v>
@@ -862,7 +862,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G17" t="n">
-        <v>0.805833280086517</v>
+        <v>0.805833339691162</v>
       </c>
       <c r="H17" t="n">
         <v>154076</v>
@@ -891,7 +891,7 @@
         <v>0.799499988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>0.782823443412781</v>
+        <v>0.782823503017426</v>
       </c>
       <c r="H18" t="n">
         <v>96322</v>
@@ -920,7 +920,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G19" t="n">
-        <v>0.769605040550232</v>
+        <v>0.769605100154877</v>
       </c>
       <c r="H19" t="n">
         <v>46236</v>
@@ -1181,7 +1181,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G28" t="n">
-        <v>0.741699516773224</v>
+        <v>0.741699576377869</v>
       </c>
       <c r="H28" t="n">
         <v>88730</v>
@@ -1384,7 +1384,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G35" t="n">
-        <v>0.846957206726074</v>
+        <v>0.846957266330719</v>
       </c>
       <c r="H35" t="n">
         <v>118859</v>
@@ -1413,7 +1413,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G36" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H36" t="n">
         <v>64920</v>
@@ -1877,7 +1877,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G52" t="n">
-        <v>0.814645528793335</v>
+        <v>0.81464558839798</v>
       </c>
       <c r="H52" t="n">
         <v>31840</v>
@@ -1906,7 +1906,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G53" t="n">
-        <v>0.820520401000977</v>
+        <v>0.820520460605621</v>
       </c>
       <c r="H53" t="n">
         <v>49839</v>
@@ -2051,7 +2051,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G58" t="n">
-        <v>0.862623512744904</v>
+        <v>0.862623453140259</v>
       </c>
       <c r="H58" t="n">
         <v>72793</v>
@@ -2080,7 +2080,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G59" t="n">
-        <v>0.840103209018707</v>
+        <v>0.840103268623352</v>
       </c>
       <c r="H59" t="n">
         <v>45401</v>
@@ -2196,7 +2196,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G63" t="n">
-        <v>0.829332649707794</v>
+        <v>0.829332709312439</v>
       </c>
       <c r="H63" t="n">
         <v>10567</v>
@@ -2254,7 +2254,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G65" t="n">
-        <v>0.829332649707794</v>
+        <v>0.829332709312439</v>
       </c>
       <c r="H65" t="n">
         <v>7361</v>
@@ -2283,7 +2283,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H66" t="n">
         <v>10600</v>
@@ -2312,7 +2312,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G67" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0.847500026226044</v>
       </c>
       <c r="G69" t="n">
-        <v>0.829822301864624</v>
+        <v>0.829822242259979</v>
       </c>
       <c r="H69" t="n">
         <v>46571</v>
@@ -2660,7 +2660,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G79" t="n">
-        <v>0.810239434242249</v>
+        <v>0.810239374637604</v>
       </c>
       <c r="H79" t="n">
         <v>5486</v>
@@ -2689,7 +2689,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G80" t="n">
-        <v>0.808770716190338</v>
+        <v>0.808770656585693</v>
       </c>
       <c r="H80" t="n">
         <v>1771</v>
@@ -2718,7 +2718,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G81" t="n">
-        <v>0.810239434242249</v>
+        <v>0.810239374637604</v>
       </c>
       <c r="H81" t="n">
         <v>5329</v>
@@ -2747,7 +2747,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G82" t="n">
-        <v>0.808770716190338</v>
+        <v>0.808770656585693</v>
       </c>
       <c r="H82" t="n">
         <v>2500</v>
@@ -3066,7 +3066,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G93" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H93" t="n">
         <v>2843</v>
@@ -3182,7 +3182,7 @@
         <v>0.863499999046326</v>
       </c>
       <c r="G97" t="n">
-        <v>0.845488488674164</v>
+        <v>0.845488548278809</v>
       </c>
       <c r="H97" t="n">
         <v>51892</v>
@@ -3211,7 +3211,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G98" t="n">
-        <v>0.842061519622803</v>
+        <v>0.842061579227448</v>
       </c>
       <c r="H98" t="n">
         <v>8247</v>
@@ -3588,7 +3588,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G111" t="n">
-        <v>0.906684875488281</v>
+        <v>0.906684815883636</v>
       </c>
       <c r="H111" t="n">
         <v>24383</v>
@@ -3675,7 +3675,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G114" t="n">
-        <v>0.910601437091827</v>
+        <v>0.910601377487183</v>
       </c>
       <c r="H114" t="n">
         <v>65821</v>
@@ -3820,7 +3820,7 @@
         <v>0.927500009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>0.908153533935547</v>
+        <v>0.908153593540192</v>
       </c>
       <c r="H119" t="n">
         <v>29744</v>
@@ -3965,7 +3965,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>0.905216157436371</v>
+        <v>0.905216097831726</v>
       </c>
       <c r="H124" t="n">
         <v>130254</v>
@@ -3994,7 +3994,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G125" t="n">
-        <v>0.90081000328064</v>
+        <v>0.900810062885284</v>
       </c>
       <c r="H125" t="n">
         <v>35381</v>
@@ -4197,7 +4197,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G132" t="n">
-        <v>0.877310693264008</v>
+        <v>0.877310633659363</v>
       </c>
       <c r="H132" t="n">
         <v>15386</v>
@@ -4284,7 +4284,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G135" t="n">
-        <v>0.899830937385559</v>
+        <v>0.899830877780914</v>
       </c>
       <c r="H135" t="n">
         <v>87599</v>
@@ -4458,7 +4458,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G141" t="n">
-        <v>0.910601437091827</v>
+        <v>0.910601377487183</v>
       </c>
       <c r="H141" t="n">
         <v>16200</v>
@@ -4487,7 +4487,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G142" t="n">
-        <v>0.930184245109558</v>
+        <v>0.930184185504913</v>
       </c>
       <c r="H142" t="n">
         <v>53191</v>
@@ -4574,7 +4574,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G145" t="n">
-        <v>0.910601437091827</v>
+        <v>0.910601377487183</v>
       </c>
       <c r="H145" t="n">
         <v>11693</v>
@@ -4661,7 +4661,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G148" t="n">
-        <v>0.905705690383911</v>
+        <v>0.905705749988556</v>
       </c>
       <c r="H148" t="n">
         <v>14838</v>
@@ -4690,7 +4690,7 @@
         <v>0.912500023841858</v>
       </c>
       <c r="G149" t="n">
-        <v>0.893466413021088</v>
+        <v>0.893466472625732</v>
       </c>
       <c r="H149" t="n">
         <v>11522</v>
@@ -4951,7 +4951,7 @@
         <v>0.918500006198883</v>
       </c>
       <c r="G158" t="n">
-        <v>0.899341285228729</v>
+        <v>0.899341344833374</v>
       </c>
       <c r="H158" t="n">
         <v>20356</v>
@@ -5009,7 +5009,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G160" t="n">
-        <v>0.899830937385559</v>
+        <v>0.899830877780914</v>
       </c>
       <c r="H160" t="n">
         <v>4032</v>
@@ -5067,7 +5067,7 @@
         <v>0.907000005245209</v>
       </c>
       <c r="G162" t="n">
-        <v>0.888081133365631</v>
+        <v>0.888081192970276</v>
       </c>
       <c r="H162" t="n">
         <v>5150</v>
@@ -5415,7 +5415,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G174" t="n">
-        <v>0.889060318470001</v>
+        <v>0.889060258865356</v>
       </c>
       <c r="H174" t="n">
         <v>7586</v>
@@ -5444,7 +5444,7 @@
         <v>0.911499977111816</v>
       </c>
       <c r="G175" t="n">
-        <v>0.892487287521362</v>
+        <v>0.892487227916718</v>
       </c>
       <c r="H175" t="n">
         <v>49377</v>
@@ -5531,7 +5531,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G178" t="n">
-        <v>0.98893266916275</v>
+        <v>0.988932728767395</v>
       </c>
       <c r="H178" t="n">
         <v>69152</v>
@@ -5560,7 +5560,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G179" t="n">
-        <v>1.01243221759796</v>
+        <v>1.01243209838867</v>
       </c>
       <c r="H179" t="n">
         <v>167469</v>
@@ -5618,7 +5618,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G181" t="n">
-        <v>0.978162169456482</v>
+        <v>0.978162229061127</v>
       </c>
       <c r="H181" t="n">
         <v>92947</v>
@@ -5676,7 +5676,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G183" t="n">
-        <v>0.949767112731934</v>
+        <v>0.949767053127289</v>
       </c>
       <c r="H183" t="n">
         <v>91824</v>
@@ -5705,7 +5705,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G184" t="n">
-        <v>0.965433299541473</v>
+        <v>0.965433359146118</v>
       </c>
       <c r="H184" t="n">
         <v>227509</v>
@@ -5734,7 +5734,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G185" t="n">
-        <v>0.978162169456482</v>
+        <v>0.978162229061127</v>
       </c>
       <c r="H185" t="n">
         <v>24534</v>
@@ -5821,7 +5821,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H188" t="n">
         <v>33543</v>
@@ -5937,7 +5937,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G192" t="n">
-        <v>0.963475048542023</v>
+        <v>0.963475108146667</v>
       </c>
       <c r="H192" t="n">
         <v>195703</v>
@@ -5966,7 +5966,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G193" t="n">
-        <v>0.963475048542023</v>
+        <v>0.963475108146667</v>
       </c>
       <c r="H193" t="n">
         <v>120124</v>
@@ -6024,7 +6024,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H195" t="n">
         <v>5609</v>
@@ -6053,7 +6053,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G196" t="n">
-        <v>0.97081857919693</v>
+        <v>0.970818638801575</v>
       </c>
       <c r="H196" t="n">
         <v>51474</v>
@@ -6082,7 +6082,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G197" t="n">
-        <v>0.978162169456482</v>
+        <v>0.978162229061127</v>
       </c>
       <c r="H197" t="n">
         <v>23009</v>
@@ -6198,7 +6198,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G201" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H201" t="n">
         <v>100047</v>
@@ -6314,7 +6314,7 @@
         <v>0.989000022411346</v>
       </c>
       <c r="G205" t="n">
-        <v>0.968370735645294</v>
+        <v>0.968370795249939</v>
       </c>
       <c r="H205" t="n">
         <v>36445</v>
@@ -6372,7 +6372,7 @@
         <v>0.984499990940094</v>
       </c>
       <c r="G207" t="n">
-        <v>0.963964641094208</v>
+        <v>0.963964581489563</v>
       </c>
       <c r="H207" t="n">
         <v>31937</v>
@@ -6517,7 +6517,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H212" t="n">
         <v>27813</v>
@@ -6546,7 +6546,7 @@
         <v>0.988499999046326</v>
       </c>
       <c r="G213" t="n">
-        <v>0.967881202697754</v>
+        <v>0.967881143093109</v>
       </c>
       <c r="H213" t="n">
         <v>28095</v>
@@ -6604,7 +6604,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G215" t="n">
-        <v>0.984037041664124</v>
+        <v>0.984036982059479</v>
       </c>
       <c r="H215" t="n">
         <v>16570</v>
@@ -6633,7 +6633,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G216" t="n">
-        <v>0.97081857919693</v>
+        <v>0.970818638801575</v>
       </c>
       <c r="H216" t="n">
         <v>41278</v>
@@ -6807,7 +6807,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G222" t="n">
-        <v>0.949767112731934</v>
+        <v>0.949767053127289</v>
       </c>
       <c r="H222" t="n">
         <v>32136</v>
@@ -6865,7 +6865,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G224" t="n">
-        <v>0.941933929920197</v>
+        <v>0.941933989524841</v>
       </c>
       <c r="H224" t="n">
         <v>5100</v>
@@ -6894,7 +6894,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G225" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H225" t="n">
         <v>125</v>
@@ -6923,7 +6923,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G226" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H226" t="n">
         <v>18525</v>
@@ -6952,7 +6952,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G227" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H227" t="n">
         <v>2641</v>
@@ -7010,7 +7010,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G229" t="n">
-        <v>0.90374743938446</v>
+        <v>0.903747379779816</v>
       </c>
       <c r="H229" t="n">
         <v>18509</v>
@@ -7097,7 +7097,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G232" t="n">
-        <v>0.905216157436371</v>
+        <v>0.905216097831726</v>
       </c>
       <c r="H232" t="n">
         <v>21022</v>
@@ -7213,7 +7213,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G236" t="n">
-        <v>0.90276825428009</v>
+        <v>0.902768313884735</v>
       </c>
       <c r="H236" t="n">
         <v>12738</v>
@@ -7242,7 +7242,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G237" t="n">
-        <v>0.90276825428009</v>
+        <v>0.902768313884735</v>
       </c>
       <c r="H237" t="n">
         <v>250</v>
@@ -7271,7 +7271,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G238" t="n">
-        <v>0.905216157436371</v>
+        <v>0.905216097831726</v>
       </c>
       <c r="H238" t="n">
         <v>12284</v>
@@ -7648,7 +7648,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G251" t="n">
-        <v>0.910601437091827</v>
+        <v>0.910601377487183</v>
       </c>
       <c r="H251" t="n">
         <v>31468</v>
@@ -7677,7 +7677,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G252" t="n">
-        <v>0.899830937385559</v>
+        <v>0.899830877780914</v>
       </c>
       <c r="H252" t="n">
         <v>15949</v>
@@ -7706,7 +7706,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G253" t="n">
-        <v>0.90081000328064</v>
+        <v>0.900810062885284</v>
       </c>
       <c r="H253" t="n">
         <v>3795</v>
@@ -7764,7 +7764,7 @@
         <v>0.938499987125397</v>
       </c>
       <c r="G255" t="n">
-        <v>0.91892409324646</v>
+        <v>0.918924152851105</v>
       </c>
       <c r="H255" t="n">
         <v>9204</v>
@@ -7851,7 +7851,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G258" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H258" t="n">
         <v>28836</v>
@@ -7909,7 +7909,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G260" t="n">
-        <v>0.932142496109009</v>
+        <v>0.932142555713654</v>
       </c>
       <c r="H260" t="n">
         <v>20022</v>
@@ -7967,7 +7967,7 @@
         <v>0.989000022411346</v>
       </c>
       <c r="G262" t="n">
-        <v>0.968370735645294</v>
+        <v>0.968370795249939</v>
       </c>
       <c r="H262" t="n">
         <v>22001</v>
@@ -8083,7 +8083,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G266" t="n">
-        <v>0.956621050834656</v>
+        <v>0.956621110439301</v>
       </c>
       <c r="H266" t="n">
         <v>146793</v>
@@ -8170,7 +8170,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G269" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H269" t="n">
         <v>69497</v>
@@ -8199,7 +8199,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H270" t="n">
         <v>61895</v>
@@ -8373,7 +8373,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H276" t="n">
         <v>31565</v>
@@ -8431,7 +8431,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>0.956621050834656</v>
+        <v>0.956621110439301</v>
       </c>
       <c r="H278" t="n">
         <v>48455</v>
@@ -8460,7 +8460,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G279" t="n">
-        <v>0.949767112731934</v>
+        <v>0.949767053127289</v>
       </c>
       <c r="H279" t="n">
         <v>34223</v>
@@ -8489,7 +8489,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H280" t="n">
         <v>16506</v>
@@ -8518,7 +8518,7 @@
         <v>0.987500011920929</v>
       </c>
       <c r="G281" t="n">
-        <v>0.966902017593384</v>
+        <v>0.966902077198029</v>
       </c>
       <c r="H281" t="n">
         <v>2162</v>
@@ -8576,7 +8576,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>0.956621050834656</v>
+        <v>0.956621110439301</v>
       </c>
       <c r="H283" t="n">
         <v>8218</v>
@@ -8605,7 +8605,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G284" t="n">
-        <v>0.965433299541473</v>
+        <v>0.965433359146118</v>
       </c>
       <c r="H284" t="n">
         <v>4642</v>
@@ -8750,7 +8750,7 @@
         <v>0.986999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>0.966412484645844</v>
+        <v>0.966412425041199</v>
       </c>
       <c r="H289" t="n">
         <v>37264</v>
@@ -8808,7 +8808,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G291" t="n">
-        <v>0.983057796955109</v>
+        <v>0.983057856559753</v>
       </c>
       <c r="H291" t="n">
         <v>27881</v>
@@ -8837,7 +8837,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G292" t="n">
-        <v>0.9869744181633</v>
+        <v>0.986974477767944</v>
       </c>
       <c r="H292" t="n">
         <v>63522</v>
@@ -8866,7 +8866,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G293" t="n">
-        <v>0.983057796955109</v>
+        <v>0.983057856559753</v>
       </c>
       <c r="H293" t="n">
         <v>53865</v>
@@ -8924,7 +8924,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G295" t="n">
-        <v>0.98893266916275</v>
+        <v>0.988932728767395</v>
       </c>
       <c r="H295" t="n">
         <v>40379</v>
@@ -8982,7 +8982,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H297" t="n">
         <v>20659</v>
@@ -9011,7 +9011,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G298" t="n">
-        <v>0.981099605560303</v>
+        <v>0.981099545955658</v>
       </c>
       <c r="H298" t="n">
         <v>114382</v>
@@ -9069,7 +9069,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>1.01830685138702</v>
+        <v>1.01830697059631</v>
       </c>
       <c r="H300" t="n">
         <v>269003</v>
@@ -9098,7 +9098,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G301" t="n">
-        <v>1.05257701873779</v>
+        <v>1.0525768995285</v>
       </c>
       <c r="H301" t="n">
         <v>358002</v>
@@ -9127,7 +9127,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G302" t="n">
-        <v>1.0829302072525</v>
+        <v>1.08293032646179</v>
       </c>
       <c r="H302" t="n">
         <v>259801</v>
@@ -9301,7 +9301,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G308" t="n">
-        <v>1.22098910808563</v>
+        <v>1.22098922729492</v>
       </c>
       <c r="H308" t="n">
         <v>47431</v>
@@ -9359,7 +9359,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G310" t="n">
-        <v>1.31694519519806</v>
+        <v>1.31694507598877</v>
       </c>
       <c r="H310" t="n">
         <v>204989</v>
@@ -9388,7 +9388,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G311" t="n">
-        <v>1.28267502784729</v>
+        <v>1.28267514705658</v>
       </c>
       <c r="H311" t="n">
         <v>321537</v>
@@ -9417,7 +9417,7 @@
         <v>1.29100000858307</v>
       </c>
       <c r="G312" t="n">
-        <v>1.26407134532928</v>
+        <v>1.26407146453857</v>
       </c>
       <c r="H312" t="n">
         <v>199047</v>
@@ -9446,7 +9446,7 @@
         <v>1.27100002765656</v>
       </c>
       <c r="G313" t="n">
-        <v>1.24448871612549</v>
+        <v>1.2444885969162</v>
       </c>
       <c r="H313" t="n">
         <v>96734</v>
@@ -9504,7 +9504,7 @@
         <v>1.25</v>
       </c>
       <c r="G315" t="n">
-        <v>1.22392654418945</v>
+        <v>1.22392666339874</v>
       </c>
       <c r="H315" t="n">
         <v>114680</v>
@@ -9765,7 +9765,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G324" t="n">
-        <v>1.32575726509094</v>
+        <v>1.32575738430023</v>
       </c>
       <c r="H324" t="n">
         <v>88859</v>
@@ -10142,7 +10142,7 @@
         <v>1.35699999332428</v>
       </c>
       <c r="G337" t="n">
-        <v>1.32869470119476</v>
+        <v>1.32869482040405</v>
       </c>
       <c r="H337" t="n">
         <v>108123</v>
@@ -10258,7 +10258,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G341" t="n">
-        <v>1.40996360778809</v>
+        <v>1.4099634885788</v>
       </c>
       <c r="H341" t="n">
         <v>114493</v>
@@ -10316,7 +10316,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G343" t="n">
-        <v>1.41975498199463</v>
+        <v>1.41975486278534</v>
       </c>
       <c r="H343" t="n">
         <v>91345</v>
@@ -10664,7 +10664,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>1.41975498199463</v>
+        <v>1.41975486278534</v>
       </c>
       <c r="H355" t="n">
         <v>66611</v>
@@ -10722,7 +10722,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G357" t="n">
-        <v>1.48437833786011</v>
+        <v>1.48437821865082</v>
       </c>
       <c r="H357" t="n">
         <v>402550</v>
@@ -10751,7 +10751,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>1.52746045589447</v>
+        <v>1.52746033668518</v>
       </c>
       <c r="H358" t="n">
         <v>214036</v>
@@ -10867,7 +10867,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G362" t="n">
-        <v>1.5264812707901</v>
+        <v>1.52648138999939</v>
       </c>
       <c r="H362" t="n">
         <v>108720</v>
@@ -10925,7 +10925,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G364" t="n">
-        <v>1.57641744613647</v>
+        <v>1.57641756534576</v>
       </c>
       <c r="H364" t="n">
         <v>87137</v>
@@ -10983,7 +10983,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G366" t="n">
-        <v>1.57445931434631</v>
+        <v>1.57445919513702</v>
       </c>
       <c r="H366" t="n">
         <v>153391</v>
@@ -11012,7 +11012,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G367" t="n">
-        <v>1.55879294872284</v>
+        <v>1.55879306793213</v>
       </c>
       <c r="H367" t="n">
         <v>59009</v>
@@ -11099,7 +11099,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G370" t="n">
-        <v>1.49319040775299</v>
+        <v>1.49319052696228</v>
       </c>
       <c r="H370" t="n">
         <v>198615</v>
@@ -11244,7 +11244,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G375" t="n">
-        <v>1.439337849617</v>
+        <v>1.43933773040771</v>
       </c>
       <c r="H375" t="n">
         <v>28060</v>
@@ -11360,7 +11360,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G379" t="n">
-        <v>1.48242008686066</v>
+        <v>1.48241996765137</v>
       </c>
       <c r="H379" t="n">
         <v>50853</v>
@@ -11418,7 +11418,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G381" t="n">
-        <v>1.46675360202789</v>
+        <v>1.46675372123718</v>
       </c>
       <c r="H381" t="n">
         <v>37418</v>
@@ -11795,7 +11795,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G394" t="n">
-        <v>1.38744330406189</v>
+        <v>1.3874431848526</v>
       </c>
       <c r="H394" t="n">
         <v>3217</v>
@@ -11882,7 +11882,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G397" t="n">
-        <v>1.46675360202789</v>
+        <v>1.46675372123718</v>
       </c>
       <c r="H397" t="n">
         <v>146942</v>
@@ -12288,7 +12288,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G411" t="n">
-        <v>1.49416959285736</v>
+        <v>1.49416971206665</v>
       </c>
       <c r="H411" t="n">
         <v>33895</v>
@@ -12491,7 +12491,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G418" t="n">
-        <v>1.88974273204803</v>
+        <v>1.88974261283875</v>
       </c>
       <c r="H418" t="n">
         <v>296041</v>
@@ -12549,7 +12549,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G420" t="n">
-        <v>1.94261634349823</v>
+        <v>1.94261622428894</v>
       </c>
       <c r="H420" t="n">
         <v>376100</v>
@@ -12636,7 +12636,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G423" t="n">
-        <v>1.88974273204803</v>
+        <v>1.88974261283875</v>
       </c>
       <c r="H423" t="n">
         <v>81649</v>
@@ -12694,7 +12694,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G425" t="n">
-        <v>2.165860414505</v>
+        <v>2.16586065292358</v>
       </c>
       <c r="H425" t="n">
         <v>662427</v>
@@ -12723,7 +12723,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>2.10515403747559</v>
+        <v>2.10515379905701</v>
       </c>
       <c r="H426" t="n">
         <v>303943</v>
@@ -12897,7 +12897,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G432" t="n">
-        <v>2.08361291885376</v>
+        <v>2.08361268043518</v>
       </c>
       <c r="H432" t="n">
         <v>120592</v>
@@ -12984,7 +12984,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G435" t="n">
-        <v>2.25398349761963</v>
+        <v>2.25398325920105</v>
       </c>
       <c r="H435" t="n">
         <v>446100</v>
@@ -13071,7 +13071,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G438" t="n">
-        <v>2.03857231140137</v>
+        <v>2.03857207298279</v>
       </c>
       <c r="H438" t="n">
         <v>376904</v>
@@ -13303,7 +13303,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G446" t="n">
-        <v>1.93086659908295</v>
+        <v>1.93086671829224</v>
       </c>
       <c r="H446" t="n">
         <v>226358</v>
@@ -13448,7 +13448,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G451" t="n">
-        <v>2.0150728225708</v>
+        <v>2.01507306098938</v>
       </c>
       <c r="H451" t="n">
         <v>124152</v>
@@ -13477,7 +13477,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G452" t="n">
-        <v>2.0150728225708</v>
+        <v>2.01507306098938</v>
       </c>
       <c r="H452" t="n">
         <v>122037</v>
@@ -13535,7 +13535,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G454" t="n">
-        <v>1.98569869995117</v>
+        <v>1.98569881916046</v>
       </c>
       <c r="H454" t="n">
         <v>31437</v>
@@ -13593,7 +13593,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G456" t="n">
-        <v>2.00723958015442</v>
+        <v>2.007239818573</v>
       </c>
       <c r="H456" t="n">
         <v>34457</v>
@@ -13622,7 +13622,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G457" t="n">
-        <v>2.0150728225708</v>
+        <v>2.01507306098938</v>
       </c>
       <c r="H457" t="n">
         <v>166275</v>
@@ -13738,7 +13738,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G461" t="n">
-        <v>1.98374044895172</v>
+        <v>1.98374032974243</v>
       </c>
       <c r="H461" t="n">
         <v>168464</v>
@@ -13767,7 +13767,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G462" t="n">
-        <v>1.95632433891296</v>
+        <v>1.95632445812225</v>
       </c>
       <c r="H462" t="n">
         <v>77596</v>
@@ -13825,7 +13825,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G464" t="n">
-        <v>1.98569869995117</v>
+        <v>1.98569881916046</v>
       </c>
       <c r="H464" t="n">
         <v>420317</v>
@@ -14144,7 +14144,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>1.93869984149933</v>
+        <v>1.93869972229004</v>
       </c>
       <c r="H475" t="n">
         <v>77792</v>
@@ -14463,7 +14463,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>1.93869984149933</v>
+        <v>1.93869972229004</v>
       </c>
       <c r="H486" t="n">
         <v>58282</v>
@@ -14550,7 +14550,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G489" t="n">
-        <v>2.05228018760681</v>
+        <v>2.05227994918823</v>
       </c>
       <c r="H489" t="n">
         <v>365431</v>
@@ -14579,7 +14579,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G490" t="n">
-        <v>2.00723958015442</v>
+        <v>2.007239818573</v>
       </c>
       <c r="H490" t="n">
         <v>127429</v>
@@ -14608,7 +14608,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G491" t="n">
-        <v>2.00723958015442</v>
+        <v>2.007239818573</v>
       </c>
       <c r="H491" t="n">
         <v>16967</v>
@@ -14869,7 +14869,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>1.9778653383255</v>
+        <v>1.97786545753479</v>
       </c>
       <c r="H500" t="n">
         <v>25172</v>
@@ -14898,7 +14898,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>1.9778653383255</v>
+        <v>1.97786545753479</v>
       </c>
       <c r="H501" t="n">
         <v>40934</v>
@@ -15101,7 +15101,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G508" t="n">
-        <v>1.93674147129059</v>
+        <v>1.93674159049988</v>
       </c>
       <c r="H508" t="n">
         <v>1738</v>
@@ -15246,7 +15246,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G513" t="n">
-        <v>1.89953422546387</v>
+        <v>1.89953410625458</v>
       </c>
       <c r="H513" t="n">
         <v>8507</v>
@@ -15333,7 +15333,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G516" t="n">
-        <v>1.9778653383255</v>
+        <v>1.97786545753479</v>
       </c>
       <c r="H516" t="n">
         <v>80856</v>
@@ -15507,7 +15507,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G522" t="n">
-        <v>1.95632433891296</v>
+        <v>1.95632445812225</v>
       </c>
       <c r="H522" t="n">
         <v>18050</v>
@@ -15536,7 +15536,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G523" t="n">
-        <v>1.96807408332825</v>
+        <v>1.96807396411896</v>
       </c>
       <c r="H523" t="n">
         <v>20616</v>
@@ -15623,7 +15623,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G526" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H526" t="n">
         <v>452689</v>
@@ -15942,7 +15942,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.10515403747559</v>
+        <v>2.10515379905701</v>
       </c>
       <c r="H537" t="n">
         <v>139101</v>
@@ -15971,7 +15971,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>2.10515403747559</v>
+        <v>2.10515379905701</v>
       </c>
       <c r="H538" t="n">
         <v>48637</v>
@@ -16058,7 +16058,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G541" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H541" t="n">
         <v>177454</v>
@@ -16087,7 +16087,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H542" t="n">
         <v>49635</v>
@@ -16145,7 +16145,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>2.18348526954651</v>
+        <v>2.18348503112793</v>
       </c>
       <c r="H544" t="n">
         <v>46864</v>
@@ -16203,7 +16203,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G546" t="n">
-        <v>2.19817209243774</v>
+        <v>2.19817233085632</v>
       </c>
       <c r="H546" t="n">
         <v>50060</v>
@@ -16232,7 +16232,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G547" t="n">
-        <v>2.18348526954651</v>
+        <v>2.18348503112793</v>
       </c>
       <c r="H547" t="n">
         <v>16948</v>
@@ -16261,7 +16261,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G548" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H548" t="n">
         <v>72087</v>
@@ -16319,7 +16319,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G550" t="n">
-        <v>2.19327640533447</v>
+        <v>2.19327664375305</v>
       </c>
       <c r="H550" t="n">
         <v>215281</v>
@@ -16348,7 +16348,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G551" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H551" t="n">
         <v>27372</v>
@@ -16377,7 +16377,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H552" t="n">
         <v>17856</v>
@@ -80084,7 +80084,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="E2749" t="n">
-        <v>1.78799998760223</v>
+        <v>1.78600001335144</v>
       </c>
       <c r="F2749" t="n">
         <v>1.78600001335144</v>
@@ -80096,6 +80096,35 @@
         <v>13467</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>1.82000005245209</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>1.78600001335144</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>1.7940000295639</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>1.7940000295639</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>100</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -485,7 +485,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G4" t="n">
-        <v>0.905705749988556</v>
+        <v>0.905705690383911</v>
       </c>
       <c r="H4" t="n">
         <v>67070</v>
@@ -514,7 +514,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G5" t="n">
-        <v>0.845978081226349</v>
+        <v>0.845978140830994</v>
       </c>
       <c r="H5" t="n">
         <v>488400</v>
@@ -572,7 +572,7 @@
         <v>0.838500022888184</v>
       </c>
       <c r="G7" t="n">
-        <v>0.821009993553162</v>
+        <v>0.821010053157806</v>
       </c>
       <c r="H7" t="n">
         <v>198049</v>
@@ -630,7 +630,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G9" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H9" t="n">
         <v>126512</v>
@@ -746,7 +746,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G13" t="n">
-        <v>0.704981744289398</v>
+        <v>0.704981803894043</v>
       </c>
       <c r="H13" t="n">
         <v>214274</v>
@@ -804,7 +804,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G15" t="n">
-        <v>0.741699576377869</v>
+        <v>0.741699516773224</v>
       </c>
       <c r="H15" t="n">
         <v>111111</v>
@@ -862,7 +862,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G17" t="n">
-        <v>0.805833339691162</v>
+        <v>0.805833280086517</v>
       </c>
       <c r="H17" t="n">
         <v>154076</v>
@@ -891,7 +891,7 @@
         <v>0.799499988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>0.782823503017426</v>
+        <v>0.782823443412781</v>
       </c>
       <c r="H18" t="n">
         <v>96322</v>
@@ -920,7 +920,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G19" t="n">
-        <v>0.769605100154877</v>
+        <v>0.769605040550232</v>
       </c>
       <c r="H19" t="n">
         <v>46236</v>
@@ -1181,7 +1181,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G28" t="n">
-        <v>0.741699576377869</v>
+        <v>0.741699516773224</v>
       </c>
       <c r="H28" t="n">
         <v>88730</v>
@@ -1384,7 +1384,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G35" t="n">
-        <v>0.846957266330719</v>
+        <v>0.846957206726074</v>
       </c>
       <c r="H35" t="n">
         <v>118859</v>
@@ -1413,7 +1413,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G36" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H36" t="n">
         <v>64920</v>
@@ -1877,7 +1877,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G52" t="n">
-        <v>0.81464558839798</v>
+        <v>0.814645528793335</v>
       </c>
       <c r="H52" t="n">
         <v>31840</v>
@@ -1906,7 +1906,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G53" t="n">
-        <v>0.820520460605621</v>
+        <v>0.820520401000977</v>
       </c>
       <c r="H53" t="n">
         <v>49839</v>
@@ -2051,7 +2051,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G58" t="n">
-        <v>0.862623453140259</v>
+        <v>0.862623512744904</v>
       </c>
       <c r="H58" t="n">
         <v>72793</v>
@@ -2080,7 +2080,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G59" t="n">
-        <v>0.840103268623352</v>
+        <v>0.840103209018707</v>
       </c>
       <c r="H59" t="n">
         <v>45401</v>
@@ -2196,7 +2196,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G63" t="n">
-        <v>0.829332709312439</v>
+        <v>0.829332649707794</v>
       </c>
       <c r="H63" t="n">
         <v>10567</v>
@@ -2254,7 +2254,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G65" t="n">
-        <v>0.829332709312439</v>
+        <v>0.829332649707794</v>
       </c>
       <c r="H65" t="n">
         <v>7361</v>
@@ -2283,7 +2283,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H66" t="n">
         <v>10600</v>
@@ -2312,7 +2312,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G67" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0.847500026226044</v>
       </c>
       <c r="G69" t="n">
-        <v>0.829822242259979</v>
+        <v>0.829822301864624</v>
       </c>
       <c r="H69" t="n">
         <v>46571</v>
@@ -2660,7 +2660,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G79" t="n">
-        <v>0.810239374637604</v>
+        <v>0.810239434242249</v>
       </c>
       <c r="H79" t="n">
         <v>5486</v>
@@ -2689,7 +2689,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G80" t="n">
-        <v>0.808770656585693</v>
+        <v>0.808770716190338</v>
       </c>
       <c r="H80" t="n">
         <v>1771</v>
@@ -2718,7 +2718,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G81" t="n">
-        <v>0.810239374637604</v>
+        <v>0.810239434242249</v>
       </c>
       <c r="H81" t="n">
         <v>5329</v>
@@ -2747,7 +2747,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G82" t="n">
-        <v>0.808770656585693</v>
+        <v>0.808770716190338</v>
       </c>
       <c r="H82" t="n">
         <v>2500</v>
@@ -3066,7 +3066,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G93" t="n">
-        <v>0.830801427364349</v>
+        <v>0.830801367759705</v>
       </c>
       <c r="H93" t="n">
         <v>2843</v>
@@ -3182,7 +3182,7 @@
         <v>0.863499999046326</v>
       </c>
       <c r="G97" t="n">
-        <v>0.845488548278809</v>
+        <v>0.845488488674164</v>
       </c>
       <c r="H97" t="n">
         <v>51892</v>
@@ -3211,7 +3211,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G98" t="n">
-        <v>0.842061579227448</v>
+        <v>0.842061519622803</v>
       </c>
       <c r="H98" t="n">
         <v>8247</v>
@@ -3588,7 +3588,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G111" t="n">
-        <v>0.906684815883636</v>
+        <v>0.906684875488281</v>
       </c>
       <c r="H111" t="n">
         <v>24383</v>
@@ -3675,7 +3675,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G114" t="n">
-        <v>0.910601377487183</v>
+        <v>0.910601437091827</v>
       </c>
       <c r="H114" t="n">
         <v>65821</v>
@@ -3820,7 +3820,7 @@
         <v>0.927500009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>0.908153593540192</v>
+        <v>0.908153533935547</v>
       </c>
       <c r="H119" t="n">
         <v>29744</v>
@@ -3965,7 +3965,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>0.905216097831726</v>
+        <v>0.905216157436371</v>
       </c>
       <c r="H124" t="n">
         <v>130254</v>
@@ -3994,7 +3994,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G125" t="n">
-        <v>0.900810062885284</v>
+        <v>0.90081000328064</v>
       </c>
       <c r="H125" t="n">
         <v>35381</v>
@@ -4197,7 +4197,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G132" t="n">
-        <v>0.877310633659363</v>
+        <v>0.877310693264008</v>
       </c>
       <c r="H132" t="n">
         <v>15386</v>
@@ -4284,7 +4284,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G135" t="n">
-        <v>0.899830877780914</v>
+        <v>0.899830937385559</v>
       </c>
       <c r="H135" t="n">
         <v>87599</v>
@@ -4458,7 +4458,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G141" t="n">
-        <v>0.910601377487183</v>
+        <v>0.910601437091827</v>
       </c>
       <c r="H141" t="n">
         <v>16200</v>
@@ -4487,7 +4487,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G142" t="n">
-        <v>0.930184185504913</v>
+        <v>0.930184245109558</v>
       </c>
       <c r="H142" t="n">
         <v>53191</v>
@@ -4574,7 +4574,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G145" t="n">
-        <v>0.910601377487183</v>
+        <v>0.910601437091827</v>
       </c>
       <c r="H145" t="n">
         <v>11693</v>
@@ -4661,7 +4661,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G148" t="n">
-        <v>0.905705749988556</v>
+        <v>0.905705690383911</v>
       </c>
       <c r="H148" t="n">
         <v>14838</v>
@@ -4690,7 +4690,7 @@
         <v>0.912500023841858</v>
       </c>
       <c r="G149" t="n">
-        <v>0.893466472625732</v>
+        <v>0.893466413021088</v>
       </c>
       <c r="H149" t="n">
         <v>11522</v>
@@ -4951,7 +4951,7 @@
         <v>0.918500006198883</v>
       </c>
       <c r="G158" t="n">
-        <v>0.899341344833374</v>
+        <v>0.899341285228729</v>
       </c>
       <c r="H158" t="n">
         <v>20356</v>
@@ -5009,7 +5009,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G160" t="n">
-        <v>0.899830877780914</v>
+        <v>0.899830937385559</v>
       </c>
       <c r="H160" t="n">
         <v>4032</v>
@@ -5067,7 +5067,7 @@
         <v>0.907000005245209</v>
       </c>
       <c r="G162" t="n">
-        <v>0.888081192970276</v>
+        <v>0.888081133365631</v>
       </c>
       <c r="H162" t="n">
         <v>5150</v>
@@ -5415,7 +5415,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G174" t="n">
-        <v>0.889060258865356</v>
+        <v>0.889060318470001</v>
       </c>
       <c r="H174" t="n">
         <v>7586</v>
@@ -5444,7 +5444,7 @@
         <v>0.911499977111816</v>
       </c>
       <c r="G175" t="n">
-        <v>0.892487227916718</v>
+        <v>0.892487287521362</v>
       </c>
       <c r="H175" t="n">
         <v>49377</v>
@@ -5531,7 +5531,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G178" t="n">
-        <v>0.988932728767395</v>
+        <v>0.98893266916275</v>
       </c>
       <c r="H178" t="n">
         <v>69152</v>
@@ -5560,7 +5560,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G179" t="n">
-        <v>1.01243209838867</v>
+        <v>1.01243221759796</v>
       </c>
       <c r="H179" t="n">
         <v>167469</v>
@@ -5618,7 +5618,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G181" t="n">
-        <v>0.978162229061127</v>
+        <v>0.978162169456482</v>
       </c>
       <c r="H181" t="n">
         <v>92947</v>
@@ -5676,7 +5676,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G183" t="n">
-        <v>0.949767053127289</v>
+        <v>0.949767112731934</v>
       </c>
       <c r="H183" t="n">
         <v>91824</v>
@@ -5705,7 +5705,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G184" t="n">
-        <v>0.965433359146118</v>
+        <v>0.965433299541473</v>
       </c>
       <c r="H184" t="n">
         <v>227509</v>
@@ -5734,7 +5734,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G185" t="n">
-        <v>0.978162229061127</v>
+        <v>0.978162169456482</v>
       </c>
       <c r="H185" t="n">
         <v>24534</v>
@@ -5821,7 +5821,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H188" t="n">
         <v>33543</v>
@@ -5937,7 +5937,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G192" t="n">
-        <v>0.963475108146667</v>
+        <v>0.963475048542023</v>
       </c>
       <c r="H192" t="n">
         <v>195703</v>
@@ -5966,7 +5966,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G193" t="n">
-        <v>0.963475108146667</v>
+        <v>0.963475048542023</v>
       </c>
       <c r="H193" t="n">
         <v>120124</v>
@@ -6024,7 +6024,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H195" t="n">
         <v>5609</v>
@@ -6053,7 +6053,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G196" t="n">
-        <v>0.970818638801575</v>
+        <v>0.97081857919693</v>
       </c>
       <c r="H196" t="n">
         <v>51474</v>
@@ -6082,7 +6082,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G197" t="n">
-        <v>0.978162229061127</v>
+        <v>0.978162169456482</v>
       </c>
       <c r="H197" t="n">
         <v>23009</v>
@@ -6198,7 +6198,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G201" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H201" t="n">
         <v>100047</v>
@@ -6314,7 +6314,7 @@
         <v>0.989000022411346</v>
       </c>
       <c r="G205" t="n">
-        <v>0.968370795249939</v>
+        <v>0.968370735645294</v>
       </c>
       <c r="H205" t="n">
         <v>36445</v>
@@ -6372,7 +6372,7 @@
         <v>0.984499990940094</v>
       </c>
       <c r="G207" t="n">
-        <v>0.963964581489563</v>
+        <v>0.963964641094208</v>
       </c>
       <c r="H207" t="n">
         <v>31937</v>
@@ -6517,7 +6517,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H212" t="n">
         <v>27813</v>
@@ -6546,7 +6546,7 @@
         <v>0.988499999046326</v>
       </c>
       <c r="G213" t="n">
-        <v>0.967881143093109</v>
+        <v>0.967881202697754</v>
       </c>
       <c r="H213" t="n">
         <v>28095</v>
@@ -6604,7 +6604,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G215" t="n">
-        <v>0.984036982059479</v>
+        <v>0.984037041664124</v>
       </c>
       <c r="H215" t="n">
         <v>16570</v>
@@ -6633,7 +6633,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G216" t="n">
-        <v>0.970818638801575</v>
+        <v>0.97081857919693</v>
       </c>
       <c r="H216" t="n">
         <v>41278</v>
@@ -6807,7 +6807,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G222" t="n">
-        <v>0.949767053127289</v>
+        <v>0.949767112731934</v>
       </c>
       <c r="H222" t="n">
         <v>32136</v>
@@ -6865,7 +6865,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G224" t="n">
-        <v>0.941933989524841</v>
+        <v>0.941933929920197</v>
       </c>
       <c r="H224" t="n">
         <v>5100</v>
@@ -6894,7 +6894,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G225" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H225" t="n">
         <v>125</v>
@@ -6923,7 +6923,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G226" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H226" t="n">
         <v>18525</v>
@@ -6952,7 +6952,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G227" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H227" t="n">
         <v>2641</v>
@@ -7010,7 +7010,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G229" t="n">
-        <v>0.903747379779816</v>
+        <v>0.90374743938446</v>
       </c>
       <c r="H229" t="n">
         <v>18509</v>
@@ -7097,7 +7097,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G232" t="n">
-        <v>0.905216097831726</v>
+        <v>0.905216157436371</v>
       </c>
       <c r="H232" t="n">
         <v>21022</v>
@@ -7213,7 +7213,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G236" t="n">
-        <v>0.902768313884735</v>
+        <v>0.90276825428009</v>
       </c>
       <c r="H236" t="n">
         <v>12738</v>
@@ -7242,7 +7242,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G237" t="n">
-        <v>0.902768313884735</v>
+        <v>0.90276825428009</v>
       </c>
       <c r="H237" t="n">
         <v>250</v>
@@ -7271,7 +7271,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G238" t="n">
-        <v>0.905216097831726</v>
+        <v>0.905216157436371</v>
       </c>
       <c r="H238" t="n">
         <v>12284</v>
@@ -7648,7 +7648,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G251" t="n">
-        <v>0.910601377487183</v>
+        <v>0.910601437091827</v>
       </c>
       <c r="H251" t="n">
         <v>31468</v>
@@ -7677,7 +7677,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G252" t="n">
-        <v>0.899830877780914</v>
+        <v>0.899830937385559</v>
       </c>
       <c r="H252" t="n">
         <v>15949</v>
@@ -7706,7 +7706,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G253" t="n">
-        <v>0.900810062885284</v>
+        <v>0.90081000328064</v>
       </c>
       <c r="H253" t="n">
         <v>3795</v>
@@ -7764,7 +7764,7 @@
         <v>0.938499987125397</v>
       </c>
       <c r="G255" t="n">
-        <v>0.918924152851105</v>
+        <v>0.91892409324646</v>
       </c>
       <c r="H255" t="n">
         <v>9204</v>
@@ -7851,7 +7851,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G258" t="n">
-        <v>0.939975619316101</v>
+        <v>0.939975678920746</v>
       </c>
       <c r="H258" t="n">
         <v>28836</v>
@@ -7909,7 +7909,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G260" t="n">
-        <v>0.932142555713654</v>
+        <v>0.932142496109009</v>
       </c>
       <c r="H260" t="n">
         <v>20022</v>
@@ -7967,7 +7967,7 @@
         <v>0.989000022411346</v>
       </c>
       <c r="G262" t="n">
-        <v>0.968370795249939</v>
+        <v>0.968370735645294</v>
       </c>
       <c r="H262" t="n">
         <v>22001</v>
@@ -8083,7 +8083,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G266" t="n">
-        <v>0.956621110439301</v>
+        <v>0.956621050834656</v>
       </c>
       <c r="H266" t="n">
         <v>146793</v>
@@ -8170,7 +8170,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G269" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H269" t="n">
         <v>69497</v>
@@ -8199,7 +8199,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H270" t="n">
         <v>61895</v>
@@ -8373,7 +8373,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H276" t="n">
         <v>31565</v>
@@ -8431,7 +8431,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>0.956621110439301</v>
+        <v>0.956621050834656</v>
       </c>
       <c r="H278" t="n">
         <v>48455</v>
@@ -8460,7 +8460,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G279" t="n">
-        <v>0.949767053127289</v>
+        <v>0.949767112731934</v>
       </c>
       <c r="H279" t="n">
         <v>34223</v>
@@ -8489,7 +8489,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H280" t="n">
         <v>16506</v>
@@ -8518,7 +8518,7 @@
         <v>0.987500011920929</v>
       </c>
       <c r="G281" t="n">
-        <v>0.966902077198029</v>
+        <v>0.966902017593384</v>
       </c>
       <c r="H281" t="n">
         <v>2162</v>
@@ -8576,7 +8576,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>0.956621110439301</v>
+        <v>0.956621050834656</v>
       </c>
       <c r="H283" t="n">
         <v>8218</v>
@@ -8605,7 +8605,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G284" t="n">
-        <v>0.965433359146118</v>
+        <v>0.965433299541473</v>
       </c>
       <c r="H284" t="n">
         <v>4642</v>
@@ -8750,7 +8750,7 @@
         <v>0.986999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>0.966412425041199</v>
+        <v>0.966412484645844</v>
       </c>
       <c r="H289" t="n">
         <v>37264</v>
@@ -8808,7 +8808,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G291" t="n">
-        <v>0.983057856559753</v>
+        <v>0.983057796955109</v>
       </c>
       <c r="H291" t="n">
         <v>27881</v>
@@ -8837,7 +8837,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G292" t="n">
-        <v>0.986974477767944</v>
+        <v>0.9869744181633</v>
       </c>
       <c r="H292" t="n">
         <v>63522</v>
@@ -8866,7 +8866,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G293" t="n">
-        <v>0.983057856559753</v>
+        <v>0.983057796955109</v>
       </c>
       <c r="H293" t="n">
         <v>53865</v>
@@ -8924,7 +8924,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G295" t="n">
-        <v>0.988932728767395</v>
+        <v>0.98893266916275</v>
       </c>
       <c r="H295" t="n">
         <v>40379</v>
@@ -8982,7 +8982,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>0.96934986114502</v>
+        <v>0.969349920749664</v>
       </c>
       <c r="H297" t="n">
         <v>20659</v>
@@ -9011,7 +9011,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G298" t="n">
-        <v>0.981099545955658</v>
+        <v>0.981099605560303</v>
       </c>
       <c r="H298" t="n">
         <v>114382</v>
@@ -9069,7 +9069,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>1.01830697059631</v>
+        <v>1.01830685138702</v>
       </c>
       <c r="H300" t="n">
         <v>269003</v>
@@ -9098,7 +9098,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G301" t="n">
-        <v>1.0525768995285</v>
+        <v>1.05257701873779</v>
       </c>
       <c r="H301" t="n">
         <v>358002</v>
@@ -9127,7 +9127,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G302" t="n">
-        <v>1.08293032646179</v>
+        <v>1.0829302072525</v>
       </c>
       <c r="H302" t="n">
         <v>259801</v>
@@ -9301,7 +9301,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G308" t="n">
-        <v>1.22098922729492</v>
+        <v>1.22098910808563</v>
       </c>
       <c r="H308" t="n">
         <v>47431</v>
@@ -9359,7 +9359,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G310" t="n">
-        <v>1.31694507598877</v>
+        <v>1.31694519519806</v>
       </c>
       <c r="H310" t="n">
         <v>204989</v>
@@ -9388,7 +9388,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G311" t="n">
-        <v>1.28267514705658</v>
+        <v>1.28267502784729</v>
       </c>
       <c r="H311" t="n">
         <v>321537</v>
@@ -9417,7 +9417,7 @@
         <v>1.29100000858307</v>
       </c>
       <c r="G312" t="n">
-        <v>1.26407146453857</v>
+        <v>1.26407134532928</v>
       </c>
       <c r="H312" t="n">
         <v>199047</v>
@@ -9446,7 +9446,7 @@
         <v>1.27100002765656</v>
       </c>
       <c r="G313" t="n">
-        <v>1.2444885969162</v>
+        <v>1.24448871612549</v>
       </c>
       <c r="H313" t="n">
         <v>96734</v>
@@ -9504,7 +9504,7 @@
         <v>1.25</v>
       </c>
       <c r="G315" t="n">
-        <v>1.22392666339874</v>
+        <v>1.22392654418945</v>
       </c>
       <c r="H315" t="n">
         <v>114680</v>
@@ -9765,7 +9765,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G324" t="n">
-        <v>1.32575738430023</v>
+        <v>1.32575726509094</v>
       </c>
       <c r="H324" t="n">
         <v>88859</v>
@@ -10142,7 +10142,7 @@
         <v>1.35699999332428</v>
       </c>
       <c r="G337" t="n">
-        <v>1.32869482040405</v>
+        <v>1.32869470119476</v>
       </c>
       <c r="H337" t="n">
         <v>108123</v>
@@ -10258,7 +10258,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G341" t="n">
-        <v>1.4099634885788</v>
+        <v>1.40996360778809</v>
       </c>
       <c r="H341" t="n">
         <v>114493</v>
@@ -10316,7 +10316,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G343" t="n">
-        <v>1.41975486278534</v>
+        <v>1.41975498199463</v>
       </c>
       <c r="H343" t="n">
         <v>91345</v>
@@ -10664,7 +10664,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>1.41975486278534</v>
+        <v>1.41975498199463</v>
       </c>
       <c r="H355" t="n">
         <v>66611</v>
@@ -10722,7 +10722,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G357" t="n">
-        <v>1.48437821865082</v>
+        <v>1.48437833786011</v>
       </c>
       <c r="H357" t="n">
         <v>402550</v>
@@ -10751,7 +10751,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>1.52746033668518</v>
+        <v>1.52746045589447</v>
       </c>
       <c r="H358" t="n">
         <v>214036</v>
@@ -10867,7 +10867,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G362" t="n">
-        <v>1.52648138999939</v>
+        <v>1.5264812707901</v>
       </c>
       <c r="H362" t="n">
         <v>108720</v>
@@ -10925,7 +10925,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G364" t="n">
-        <v>1.57641756534576</v>
+        <v>1.57641744613647</v>
       </c>
       <c r="H364" t="n">
         <v>87137</v>
@@ -10983,7 +10983,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G366" t="n">
-        <v>1.57445919513702</v>
+        <v>1.57445931434631</v>
       </c>
       <c r="H366" t="n">
         <v>153391</v>
@@ -11012,7 +11012,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G367" t="n">
-        <v>1.55879306793213</v>
+        <v>1.55879294872284</v>
       </c>
       <c r="H367" t="n">
         <v>59009</v>
@@ -11099,7 +11099,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G370" t="n">
-        <v>1.49319052696228</v>
+        <v>1.49319040775299</v>
       </c>
       <c r="H370" t="n">
         <v>198615</v>
@@ -11244,7 +11244,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G375" t="n">
-        <v>1.43933773040771</v>
+        <v>1.439337849617</v>
       </c>
       <c r="H375" t="n">
         <v>28060</v>
@@ -11360,7 +11360,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G379" t="n">
-        <v>1.48241996765137</v>
+        <v>1.48242008686066</v>
       </c>
       <c r="H379" t="n">
         <v>50853</v>
@@ -11418,7 +11418,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G381" t="n">
-        <v>1.46675372123718</v>
+        <v>1.46675360202789</v>
       </c>
       <c r="H381" t="n">
         <v>37418</v>
@@ -11795,7 +11795,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G394" t="n">
-        <v>1.3874431848526</v>
+        <v>1.38744330406189</v>
       </c>
       <c r="H394" t="n">
         <v>3217</v>
@@ -11882,7 +11882,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G397" t="n">
-        <v>1.46675372123718</v>
+        <v>1.46675360202789</v>
       </c>
       <c r="H397" t="n">
         <v>146942</v>
@@ -12288,7 +12288,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G411" t="n">
-        <v>1.49416971206665</v>
+        <v>1.49416959285736</v>
       </c>
       <c r="H411" t="n">
         <v>33895</v>
@@ -12491,7 +12491,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G418" t="n">
-        <v>1.88974261283875</v>
+        <v>1.88974273204803</v>
       </c>
       <c r="H418" t="n">
         <v>296041</v>
@@ -12549,7 +12549,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G420" t="n">
-        <v>1.94261622428894</v>
+        <v>1.94261634349823</v>
       </c>
       <c r="H420" t="n">
         <v>376100</v>
@@ -12636,7 +12636,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G423" t="n">
-        <v>1.88974261283875</v>
+        <v>1.88974273204803</v>
       </c>
       <c r="H423" t="n">
         <v>81649</v>
@@ -12694,7 +12694,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G425" t="n">
-        <v>2.16586065292358</v>
+        <v>2.165860414505</v>
       </c>
       <c r="H425" t="n">
         <v>662427</v>
@@ -12723,7 +12723,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>2.10515379905701</v>
+        <v>2.10515403747559</v>
       </c>
       <c r="H426" t="n">
         <v>303943</v>
@@ -12897,7 +12897,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G432" t="n">
-        <v>2.08361268043518</v>
+        <v>2.08361291885376</v>
       </c>
       <c r="H432" t="n">
         <v>120592</v>
@@ -12984,7 +12984,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G435" t="n">
-        <v>2.25398325920105</v>
+        <v>2.25398349761963</v>
       </c>
       <c r="H435" t="n">
         <v>446100</v>
@@ -13071,7 +13071,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G438" t="n">
-        <v>2.03857207298279</v>
+        <v>2.03857231140137</v>
       </c>
       <c r="H438" t="n">
         <v>376904</v>
@@ -13303,7 +13303,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G446" t="n">
-        <v>1.93086671829224</v>
+        <v>1.93086659908295</v>
       </c>
       <c r="H446" t="n">
         <v>226358</v>
@@ -13448,7 +13448,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G451" t="n">
-        <v>2.01507306098938</v>
+        <v>2.0150728225708</v>
       </c>
       <c r="H451" t="n">
         <v>124152</v>
@@ -13477,7 +13477,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G452" t="n">
-        <v>2.01507306098938</v>
+        <v>2.0150728225708</v>
       </c>
       <c r="H452" t="n">
         <v>122037</v>
@@ -13535,7 +13535,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G454" t="n">
-        <v>1.98569881916046</v>
+        <v>1.98569869995117</v>
       </c>
       <c r="H454" t="n">
         <v>31437</v>
@@ -13593,7 +13593,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G456" t="n">
-        <v>2.007239818573</v>
+        <v>2.00723958015442</v>
       </c>
       <c r="H456" t="n">
         <v>34457</v>
@@ -13622,7 +13622,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G457" t="n">
-        <v>2.01507306098938</v>
+        <v>2.0150728225708</v>
       </c>
       <c r="H457" t="n">
         <v>166275</v>
@@ -13738,7 +13738,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G461" t="n">
-        <v>1.98374032974243</v>
+        <v>1.98374044895172</v>
       </c>
       <c r="H461" t="n">
         <v>168464</v>
@@ -13767,7 +13767,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G462" t="n">
-        <v>1.95632445812225</v>
+        <v>1.95632433891296</v>
       </c>
       <c r="H462" t="n">
         <v>77596</v>
@@ -13825,7 +13825,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G464" t="n">
-        <v>1.98569881916046</v>
+        <v>1.98569869995117</v>
       </c>
       <c r="H464" t="n">
         <v>420317</v>
@@ -14144,7 +14144,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>1.93869972229004</v>
+        <v>1.93869984149933</v>
       </c>
       <c r="H475" t="n">
         <v>77792</v>
@@ -14463,7 +14463,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>1.93869972229004</v>
+        <v>1.93869984149933</v>
       </c>
       <c r="H486" t="n">
         <v>58282</v>
@@ -14550,7 +14550,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G489" t="n">
-        <v>2.05227994918823</v>
+        <v>2.05228018760681</v>
       </c>
       <c r="H489" t="n">
         <v>365431</v>
@@ -14579,7 +14579,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G490" t="n">
-        <v>2.007239818573</v>
+        <v>2.00723958015442</v>
       </c>
       <c r="H490" t="n">
         <v>127429</v>
@@ -14608,7 +14608,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G491" t="n">
-        <v>2.007239818573</v>
+        <v>2.00723958015442</v>
       </c>
       <c r="H491" t="n">
         <v>16967</v>
@@ -14869,7 +14869,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>1.97786545753479</v>
+        <v>1.9778653383255</v>
       </c>
       <c r="H500" t="n">
         <v>25172</v>
@@ -14898,7 +14898,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>1.97786545753479</v>
+        <v>1.9778653383255</v>
       </c>
       <c r="H501" t="n">
         <v>40934</v>
@@ -15101,7 +15101,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G508" t="n">
-        <v>1.93674159049988</v>
+        <v>1.93674147129059</v>
       </c>
       <c r="H508" t="n">
         <v>1738</v>
@@ -15246,7 +15246,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G513" t="n">
-        <v>1.89953410625458</v>
+        <v>1.89953422546387</v>
       </c>
       <c r="H513" t="n">
         <v>8507</v>
@@ -15333,7 +15333,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G516" t="n">
-        <v>1.97786545753479</v>
+        <v>1.9778653383255</v>
       </c>
       <c r="H516" t="n">
         <v>80856</v>
@@ -15507,7 +15507,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G522" t="n">
-        <v>1.95632445812225</v>
+        <v>1.95632433891296</v>
       </c>
       <c r="H522" t="n">
         <v>18050</v>
@@ -15536,7 +15536,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G523" t="n">
-        <v>1.96807396411896</v>
+        <v>1.96807408332825</v>
       </c>
       <c r="H523" t="n">
         <v>20616</v>
@@ -15623,7 +15623,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G526" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H526" t="n">
         <v>452689</v>
@@ -15942,7 +15942,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.10515379905701</v>
+        <v>2.10515403747559</v>
       </c>
       <c r="H537" t="n">
         <v>139101</v>
@@ -15971,7 +15971,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>2.10515379905701</v>
+        <v>2.10515403747559</v>
       </c>
       <c r="H538" t="n">
         <v>48637</v>
@@ -16058,7 +16058,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G541" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H541" t="n">
         <v>177454</v>
@@ -16087,7 +16087,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H542" t="n">
         <v>49635</v>
@@ -16145,7 +16145,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>2.18348503112793</v>
+        <v>2.18348526954651</v>
       </c>
       <c r="H544" t="n">
         <v>46864</v>
@@ -16203,7 +16203,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G546" t="n">
-        <v>2.19817233085632</v>
+        <v>2.19817209243774</v>
       </c>
       <c r="H546" t="n">
         <v>50060</v>
@@ -16232,7 +16232,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G547" t="n">
-        <v>2.18348503112793</v>
+        <v>2.18348526954651</v>
       </c>
       <c r="H547" t="n">
         <v>16948</v>
@@ -16261,7 +16261,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G548" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H548" t="n">
         <v>72087</v>
@@ -16319,7 +16319,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G550" t="n">
-        <v>2.19327664375305</v>
+        <v>2.19327640533447</v>
       </c>
       <c r="H550" t="n">
         <v>215281</v>
@@ -16348,7 +16348,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G551" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H551" t="n">
         <v>27372</v>
@@ -16377,7 +16377,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>2.17369365692139</v>
+        <v>2.17369389533997</v>
       </c>
       <c r="H552" t="n">
         <v>17856</v>
@@ -80107,13 +80107,13 @@
         <v>46321.3333333333</v>
       </c>
       <c r="C2750" t="n">
-        <v>1.79999995231628</v>
+        <v>1.7940000295639</v>
       </c>
       <c r="D2750" t="n">
-        <v>1.82000005245209</v>
+        <v>1.7940000295639</v>
       </c>
       <c r="E2750" t="n">
-        <v>1.78600001335144</v>
+        <v>1.7940000295639</v>
       </c>
       <c r="F2750" t="n">
         <v>1.7940000295639</v>
@@ -80125,6 +80125,35 @@
         <v>100</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>1.82000005245209</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>1.89800000190735</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>1.81400001049042</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>1.81400001049042</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>1.81400001049042</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>37543</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -80157,6 +80157,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>1.88399994373322</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>1.88399994373322</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>1.84200000762939</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>1.84599995613098</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>1.84599995613098</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>20566</v>
+      </c>
+      <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -80186,6 +80186,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>1.89999997615814</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>1.84200000762939</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>1.85000002384186</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>1.85000002384186</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>28896</v>
+      </c>
+      <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IGV.MI.xlsx
+++ b/data/IGV.MI.xlsx
@@ -485,7 +485,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G4" t="n">
-        <v>0.905705690383911</v>
+        <v>0.905705749988556</v>
       </c>
       <c r="H4" t="n">
         <v>67070</v>
@@ -514,7 +514,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G5" t="n">
-        <v>0.845978140830994</v>
+        <v>0.845978081226349</v>
       </c>
       <c r="H5" t="n">
         <v>488400</v>
@@ -572,7 +572,7 @@
         <v>0.838500022888184</v>
       </c>
       <c r="G7" t="n">
-        <v>0.821010053157806</v>
+        <v>0.821009993553162</v>
       </c>
       <c r="H7" t="n">
         <v>198049</v>
@@ -630,7 +630,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G9" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H9" t="n">
         <v>126512</v>
@@ -746,7 +746,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G13" t="n">
-        <v>0.704981803894043</v>
+        <v>0.704981744289398</v>
       </c>
       <c r="H13" t="n">
         <v>214274</v>
@@ -804,7 +804,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G15" t="n">
-        <v>0.741699516773224</v>
+        <v>0.741699576377869</v>
       </c>
       <c r="H15" t="n">
         <v>111111</v>
@@ -862,7 +862,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G17" t="n">
-        <v>0.805833280086517</v>
+        <v>0.805833339691162</v>
       </c>
       <c r="H17" t="n">
         <v>154076</v>
@@ -891,7 +891,7 @@
         <v>0.799499988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>0.782823443412781</v>
+        <v>0.782823503017426</v>
       </c>
       <c r="H18" t="n">
         <v>96322</v>
@@ -920,7 +920,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G19" t="n">
-        <v>0.769605040550232</v>
+        <v>0.769605100154877</v>
       </c>
       <c r="H19" t="n">
         <v>46236</v>
@@ -1181,7 +1181,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G28" t="n">
-        <v>0.741699516773224</v>
+        <v>0.741699576377869</v>
       </c>
       <c r="H28" t="n">
         <v>88730</v>
@@ -1384,7 +1384,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G35" t="n">
-        <v>0.846957206726074</v>
+        <v>0.846957266330719</v>
       </c>
       <c r="H35" t="n">
         <v>118859</v>
@@ -1413,7 +1413,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G36" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H36" t="n">
         <v>64920</v>
@@ -1877,7 +1877,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G52" t="n">
-        <v>0.814645528793335</v>
+        <v>0.81464558839798</v>
       </c>
       <c r="H52" t="n">
         <v>31840</v>
@@ -1906,7 +1906,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G53" t="n">
-        <v>0.820520401000977</v>
+        <v>0.820520460605621</v>
       </c>
       <c r="H53" t="n">
         <v>49839</v>
@@ -2051,7 +2051,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G58" t="n">
-        <v>0.862623512744904</v>
+        <v>0.862623453140259</v>
       </c>
       <c r="H58" t="n">
         <v>72793</v>
@@ -2080,7 +2080,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G59" t="n">
-        <v>0.840103209018707</v>
+        <v>0.840103268623352</v>
       </c>
       <c r="H59" t="n">
         <v>45401</v>
@@ -2196,7 +2196,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G63" t="n">
-        <v>0.829332649707794</v>
+        <v>0.829332709312439</v>
       </c>
       <c r="H63" t="n">
         <v>10567</v>
@@ -2254,7 +2254,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G65" t="n">
-        <v>0.829332649707794</v>
+        <v>0.829332709312439</v>
       </c>
       <c r="H65" t="n">
         <v>7361</v>
@@ -2283,7 +2283,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H66" t="n">
         <v>10600</v>
@@ -2312,7 +2312,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G67" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0.847500026226044</v>
       </c>
       <c r="G69" t="n">
-        <v>0.829822301864624</v>
+        <v>0.829822242259979</v>
       </c>
       <c r="H69" t="n">
         <v>46571</v>
@@ -2660,7 +2660,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G79" t="n">
-        <v>0.810239434242249</v>
+        <v>0.810239374637604</v>
       </c>
       <c r="H79" t="n">
         <v>5486</v>
@@ -2689,7 +2689,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G80" t="n">
-        <v>0.808770716190338</v>
+        <v>0.808770656585693</v>
       </c>
       <c r="H80" t="n">
         <v>1771</v>
@@ -2718,7 +2718,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G81" t="n">
-        <v>0.810239434242249</v>
+        <v>0.810239374637604</v>
       </c>
       <c r="H81" t="n">
         <v>5329</v>
@@ -2747,7 +2747,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G82" t="n">
-        <v>0.808770716190338</v>
+        <v>0.808770656585693</v>
       </c>
       <c r="H82" t="n">
         <v>2500</v>
@@ -3066,7 +3066,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G93" t="n">
-        <v>0.830801367759705</v>
+        <v>0.830801427364349</v>
       </c>
       <c r="H93" t="n">
         <v>2843</v>
@@ -3182,7 +3182,7 @@
         <v>0.863499999046326</v>
       </c>
       <c r="G97" t="n">
-        <v>0.845488488674164</v>
+        <v>0.845488548278809</v>
       </c>
       <c r="H97" t="n">
         <v>51892</v>
@@ -3211,7 +3211,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G98" t="n">
-        <v>0.842061519622803</v>
+        <v>0.842061579227448</v>
       </c>
       <c r="H98" t="n">
         <v>8247</v>
@@ -3588,7 +3588,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G111" t="n">
-        <v>0.906684875488281</v>
+        <v>0.906684815883636</v>
       </c>
       <c r="H111" t="n">
         <v>24383</v>
@@ -3675,7 +3675,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G114" t="n">
-        <v>0.910601437091827</v>
+        <v>0.910601377487183</v>
       </c>
       <c r="H114" t="n">
         <v>65821</v>
@@ -3820,7 +3820,7 @@
         <v>0.927500009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>0.908153533935547</v>
+        <v>0.908153593540192</v>
       </c>
       <c r="H119" t="n">
         <v>29744</v>
@@ -3965,7 +3965,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>0.905216157436371</v>
+        <v>0.905216097831726</v>
       </c>
       <c r="H124" t="n">
         <v>130254</v>
@@ -3994,7 +3994,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G125" t="n">
-        <v>0.90081000328064</v>
+        <v>0.900810062885284</v>
       </c>
       <c r="H125" t="n">
         <v>35381</v>
@@ -4197,7 +4197,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G132" t="n">
-        <v>0.877310693264008</v>
+        <v>0.877310633659363</v>
       </c>
       <c r="H132" t="n">
         <v>15386</v>
@@ -4284,7 +4284,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G135" t="n">
-        <v>0.899830937385559</v>
+        <v>0.899830877780914</v>
       </c>
       <c r="H135" t="n">
         <v>87599</v>
@@ -4458,7 +4458,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G141" t="n">
-        <v>0.910601437091827</v>
+        <v>0.910601377487183</v>
       </c>
       <c r="H141" t="n">
         <v>16200</v>
@@ -4487,7 +4487,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G142" t="n">
-        <v>0.930184245109558</v>
+        <v>0.930184185504913</v>
       </c>
       <c r="H142" t="n">
         <v>53191</v>
@@ -4574,7 +4574,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G145" t="n">
-        <v>0.910601437091827</v>
+        <v>0.910601377487183</v>
       </c>
       <c r="H145" t="n">
         <v>11693</v>
@@ -4661,7 +4661,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G148" t="n">
-        <v>0.905705690383911</v>
+        <v>0.905705749988556</v>
       </c>
       <c r="H148" t="n">
         <v>14838</v>
@@ -4690,7 +4690,7 @@
         <v>0.912500023841858</v>
       </c>
       <c r="G149" t="n">
-        <v>0.893466413021088</v>
+        <v>0.893466472625732</v>
       </c>
       <c r="H149" t="n">
         <v>11522</v>
@@ -4951,7 +4951,7 @@
         <v>0.918500006198883</v>
       </c>
       <c r="G158" t="n">
-        <v>0.899341285228729</v>
+        <v>0.899341344833374</v>
       </c>
       <c r="H158" t="n">
         <v>20356</v>
@@ -5009,7 +5009,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G160" t="n">
-        <v>0.899830937385559</v>
+        <v>0.899830877780914</v>
       </c>
       <c r="H160" t="n">
         <v>4032</v>
@@ -5067,7 +5067,7 @@
         <v>0.907000005245209</v>
       </c>
       <c r="G162" t="n">
-        <v>0.888081133365631</v>
+        <v>0.888081192970276</v>
       </c>
       <c r="H162" t="n">
         <v>5150</v>
@@ -5415,7 +5415,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G174" t="n">
-        <v>0.889060318470001</v>
+        <v>0.889060258865356</v>
       </c>
       <c r="H174" t="n">
         <v>7586</v>
@@ -5444,7 +5444,7 @@
         <v>0.911499977111816</v>
       </c>
       <c r="G175" t="n">
-        <v>0.892487287521362</v>
+        <v>0.892487227916718</v>
       </c>
       <c r="H175" t="n">
         <v>49377</v>
@@ -5531,7 +5531,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G178" t="n">
-        <v>0.98893266916275</v>
+        <v>0.988932728767395</v>
       </c>
       <c r="H178" t="n">
         <v>69152</v>
@@ -5560,7 +5560,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G179" t="n">
-        <v>1.01243221759796</v>
+        <v>1.01243209838867</v>
       </c>
       <c r="H179" t="n">
         <v>167469</v>
@@ -5618,7 +5618,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G181" t="n">
-        <v>0.978162169456482</v>
+        <v>0.978162229061127</v>
       </c>
       <c r="H181" t="n">
         <v>92947</v>
@@ -5676,7 +5676,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G183" t="n">
-        <v>0.949767112731934</v>
+        <v>0.949767053127289</v>
       </c>
       <c r="H183" t="n">
         <v>91824</v>
@@ -5705,7 +5705,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G184" t="n">
-        <v>0.965433299541473</v>
+        <v>0.965433359146118</v>
       </c>
       <c r="H184" t="n">
         <v>227509</v>
@@ -5734,7 +5734,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G185" t="n">
-        <v>0.978162169456482</v>
+        <v>0.978162229061127</v>
       </c>
       <c r="H185" t="n">
         <v>24534</v>
@@ -5821,7 +5821,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H188" t="n">
         <v>33543</v>
@@ -5937,7 +5937,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G192" t="n">
-        <v>0.963475048542023</v>
+        <v>0.963475108146667</v>
       </c>
       <c r="H192" t="n">
         <v>195703</v>
@@ -5966,7 +5966,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G193" t="n">
-        <v>0.963475048542023</v>
+        <v>0.963475108146667</v>
       </c>
       <c r="H193" t="n">
         <v>120124</v>
@@ -6024,7 +6024,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H195" t="n">
         <v>5609</v>
@@ -6053,7 +6053,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G196" t="n">
-        <v>0.97081857919693</v>
+        <v>0.970818638801575</v>
       </c>
       <c r="H196" t="n">
         <v>51474</v>
@@ -6082,7 +6082,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G197" t="n">
-        <v>0.978162169456482</v>
+        <v>0.978162229061127</v>
       </c>
       <c r="H197" t="n">
         <v>23009</v>
@@ -6198,7 +6198,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G201" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H201" t="n">
         <v>100047</v>
@@ -6314,7 +6314,7 @@
         <v>0.989000022411346</v>
       </c>
       <c r="G205" t="n">
-        <v>0.968370735645294</v>
+        <v>0.968370795249939</v>
       </c>
       <c r="H205" t="n">
         <v>36445</v>
@@ -6372,7 +6372,7 @@
         <v>0.984499990940094</v>
       </c>
       <c r="G207" t="n">
-        <v>0.963964641094208</v>
+        <v>0.963964581489563</v>
       </c>
       <c r="H207" t="n">
         <v>31937</v>
@@ -6517,7 +6517,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H212" t="n">
         <v>27813</v>
@@ -6546,7 +6546,7 @@
         <v>0.988499999046326</v>
       </c>
       <c r="G213" t="n">
-        <v>0.967881202697754</v>
+        <v>0.967881143093109</v>
       </c>
       <c r="H213" t="n">
         <v>28095</v>
@@ -6604,7 +6604,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G215" t="n">
-        <v>0.984037041664124</v>
+        <v>0.984036982059479</v>
       </c>
       <c r="H215" t="n">
         <v>16570</v>
@@ -6633,7 +6633,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G216" t="n">
-        <v>0.97081857919693</v>
+        <v>0.970818638801575</v>
       </c>
       <c r="H216" t="n">
         <v>41278</v>
@@ -6807,7 +6807,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G222" t="n">
-        <v>0.949767112731934</v>
+        <v>0.949767053127289</v>
       </c>
       <c r="H222" t="n">
         <v>32136</v>
@@ -6865,7 +6865,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G224" t="n">
-        <v>0.941933929920197</v>
+        <v>0.941933989524841</v>
       </c>
       <c r="H224" t="n">
         <v>5100</v>
@@ -6894,7 +6894,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G225" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H225" t="n">
         <v>125</v>
@@ -6923,7 +6923,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G226" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H226" t="n">
         <v>18525</v>
@@ -6952,7 +6952,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G227" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H227" t="n">
         <v>2641</v>
@@ -7010,7 +7010,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G229" t="n">
-        <v>0.90374743938446</v>
+        <v>0.903747379779816</v>
       </c>
       <c r="H229" t="n">
         <v>18509</v>
@@ -7097,7 +7097,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G232" t="n">
-        <v>0.905216157436371</v>
+        <v>0.905216097831726</v>
       </c>
       <c r="H232" t="n">
         <v>21022</v>
@@ -7213,7 +7213,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G236" t="n">
-        <v>0.90276825428009</v>
+        <v>0.902768313884735</v>
       </c>
       <c r="H236" t="n">
         <v>12738</v>
@@ -7242,7 +7242,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G237" t="n">
-        <v>0.90276825428009</v>
+        <v>0.902768313884735</v>
       </c>
       <c r="H237" t="n">
         <v>250</v>
@@ -7271,7 +7271,7 @@
         <v>0.924499988555908</v>
       </c>
       <c r="G238" t="n">
-        <v>0.905216157436371</v>
+        <v>0.905216097831726</v>
       </c>
       <c r="H238" t="n">
         <v>12284</v>
@@ -7648,7 +7648,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G251" t="n">
-        <v>0.910601437091827</v>
+        <v>0.910601377487183</v>
       </c>
       <c r="H251" t="n">
         <v>31468</v>
@@ -7677,7 +7677,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G252" t="n">
-        <v>0.899830937385559</v>
+        <v>0.899830877780914</v>
       </c>
       <c r="H252" t="n">
         <v>15949</v>
@@ -7706,7 +7706,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G253" t="n">
-        <v>0.90081000328064</v>
+        <v>0.900810062885284</v>
       </c>
       <c r="H253" t="n">
         <v>3795</v>
@@ -7764,7 +7764,7 @@
         <v>0.938499987125397</v>
       </c>
       <c r="G255" t="n">
-        <v>0.91892409324646</v>
+        <v>0.918924152851105</v>
       </c>
       <c r="H255" t="n">
         <v>9204</v>
@@ -7851,7 +7851,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G258" t="n">
-        <v>0.939975678920746</v>
+        <v>0.939975619316101</v>
       </c>
       <c r="H258" t="n">
         <v>28836</v>
@@ -7909,7 +7909,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G260" t="n">
-        <v>0.932142496109009</v>
+        <v>0.932142555713654</v>
       </c>
       <c r="H260" t="n">
         <v>20022</v>
@@ -7967,7 +7967,7 @@
         <v>0.989000022411346</v>
       </c>
       <c r="G262" t="n">
-        <v>0.968370735645294</v>
+        <v>0.968370795249939</v>
       </c>
       <c r="H262" t="n">
         <v>22001</v>
@@ -8083,7 +8083,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G266" t="n">
-        <v>0.956621050834656</v>
+        <v>0.956621110439301</v>
       </c>
       <c r="H266" t="n">
         <v>146793</v>
@@ -8170,7 +8170,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G269" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H269" t="n">
         <v>69497</v>
@@ -8199,7 +8199,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H270" t="n">
         <v>61895</v>
@@ -8373,7 +8373,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H276" t="n">
         <v>31565</v>
@@ -8431,7 +8431,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>0.956621050834656</v>
+        <v>0.956621110439301</v>
       </c>
       <c r="H278" t="n">
         <v>48455</v>
@@ -8460,7 +8460,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G279" t="n">
-        <v>0.949767112731934</v>
+        <v>0.949767053127289</v>
       </c>
       <c r="H279" t="n">
         <v>34223</v>
@@ -8489,7 +8489,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H280" t="n">
         <v>16506</v>
@@ -8518,7 +8518,7 @@
         <v>0.987500011920929</v>
       </c>
       <c r="G281" t="n">
-        <v>0.966902017593384</v>
+        <v>0.966902077198029</v>
       </c>
       <c r="H281" t="n">
         <v>2162</v>
@@ -8576,7 +8576,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>0.956621050834656</v>
+        <v>0.956621110439301</v>
       </c>
       <c r="H283" t="n">
         <v>8218</v>
@@ -8605,7 +8605,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G284" t="n">
-        <v>0.965433299541473</v>
+        <v>0.965433359146118</v>
       </c>
       <c r="H284" t="n">
         <v>4642</v>
@@ -8750,7 +8750,7 @@
         <v>0.986999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>0.966412484645844</v>
+        <v>0.966412425041199</v>
       </c>
       <c r="H289" t="n">
         <v>37264</v>
@@ -8808,7 +8808,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G291" t="n">
-        <v>0.983057796955109</v>
+        <v>0.983057856559753</v>
       </c>
       <c r="H291" t="n">
         <v>27881</v>
@@ -8837,7 +8837,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G292" t="n">
-        <v>0.9869744181633</v>
+        <v>0.986974477767944</v>
       </c>
       <c r="H292" t="n">
         <v>63522</v>
@@ -8866,7 +8866,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G293" t="n">
-        <v>0.983057796955109</v>
+        <v>0.983057856559753</v>
       </c>
       <c r="H293" t="n">
         <v>53865</v>
@@ -8924,7 +8924,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G295" t="n">
-        <v>0.98893266916275</v>
+        <v>0.988932728767395</v>
       </c>
       <c r="H295" t="n">
         <v>40379</v>
@@ -8982,7 +8982,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>0.969349920749664</v>
+        <v>0.96934986114502</v>
       </c>
       <c r="H297" t="n">
         <v>20659</v>
@@ -9011,7 +9011,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G298" t="n">
-        <v>0.981099605560303</v>
+        <v>0.981099545955658</v>
       </c>
       <c r="H298" t="n">
         <v>114382</v>
@@ -9069,7 +9069,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>1.01830685138702</v>
+        <v>1.01830697059631</v>
       </c>
       <c r="H300" t="n">
         <v>269003</v>
@@ -9098,7 +9098,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G301" t="n">
-        <v>1.05257701873779</v>
+        <v>1.0525768995285</v>
       </c>
       <c r="H301" t="n">
         <v>358002</v>
@@ -9127,7 +9127,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G302" t="n">
-        <v>1.0829302072525</v>
+        <v>1.08293032646179</v>
       </c>
       <c r="H302" t="n">
         <v>259801</v>
@@ -9301,7 +9301,7 @@
         <v>1.24699997901917</v>
       </c>
       <c r="G308" t="n">
-        <v>1.22098910808563</v>
+        <v>1.22098922729492</v>
       </c>
       <c r="H308" t="n">
         <v>47431</v>
@@ -9359,7 +9359,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G310" t="n">
-        <v>1.31694519519806</v>
+        <v>1.31694507598877</v>
       </c>
       <c r="H310" t="n">
         <v>204989</v>
@@ -9388,7 +9388,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G311" t="n">
-        <v>1.28267502784729</v>
+        <v>1.28267514705658</v>
       </c>
       <c r="H311" t="n">
         <v>321537</v>
@@ -9417,7 +9417,7 @@
         <v>1.29100000858307</v>
       </c>
       <c r="G312" t="n">
-        <v>1.26407134532928</v>
+        <v>1.26407146453857</v>
       </c>
       <c r="H312" t="n">
         <v>199047</v>
@@ -9446,7 +9446,7 @@
         <v>1.27100002765656</v>
       </c>
       <c r="G313" t="n">
-        <v>1.24448871612549</v>
+        <v>1.2444885969162</v>
       </c>
       <c r="H313" t="n">
         <v>96734</v>
@@ -9504,7 +9504,7 @@
         <v>1.25</v>
       </c>
       <c r="G315" t="n">
-        <v>1.22392654418945</v>
+        <v>1.22392666339874</v>
       </c>
       <c r="H315" t="n">
         <v>114680</v>
@@ -9765,7 +9765,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G324" t="n">
-        <v>1.32575726509094</v>
+        <v>1.32575738430023</v>
       </c>
       <c r="H324" t="n">
         <v>88859</v>
@@ -10142,7 +10142,7 @@
         <v>1.35699999332428</v>
       </c>
       <c r="G337" t="n">
-        <v>1.32869470119476</v>
+        <v>1.32869482040405</v>
       </c>
       <c r="H337" t="n">
         <v>108123</v>
@@ -10258,7 +10258,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G341" t="n">
-        <v>1.40996360778809</v>
+        <v>1.4099634885788</v>
       </c>
       <c r="H341" t="n">
         <v>114493</v>
@@ -10316,7 +10316,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G343" t="n">
-        <v>1.41975498199463</v>
+        <v>1.41975486278534</v>
       </c>
       <c r="H343" t="n">
         <v>91345</v>
@@ -10664,7 +10664,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>1.41975498199463</v>
+        <v>1.41975486278534</v>
       </c>
       <c r="H355" t="n">
         <v>66611</v>
@@ -10722,7 +10722,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G357" t="n">
-        <v>1.48437833786011</v>
+        <v>1.48437821865082</v>
       </c>
       <c r="H357" t="n">
         <v>402550</v>
@@ -10751,7 +10751,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>1.52746045589447</v>
+        <v>1.52746033668518</v>
       </c>
       <c r="H358" t="n">
         <v>214036</v>
@@ -10867,7 +10867,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G362" t="n">
-        <v>1.5264812707901</v>
+        <v>1.52648138999939</v>
       </c>
       <c r="H362" t="n">
         <v>108720</v>
@@ -10925,7 +10925,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G364" t="n">
-        <v>1.57641744613647</v>
+        <v>1.57641756534576</v>
       </c>
       <c r="H364" t="n">
         <v>87137</v>
@@ -10983,7 +10983,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G366" t="n">
-        <v>1.57445931434631</v>
+        <v>1.57445919513702</v>
       </c>
       <c r="H366" t="n">
         <v>153391</v>
@@ -11012,7 +11012,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G367" t="n">
-        <v>1.55879294872284</v>
+        <v>1.55879306793213</v>
       </c>
       <c r="H367" t="n">
         <v>59009</v>
@@ -11099,7 +11099,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G370" t="n">
-        <v>1.49319040775299</v>
+        <v>1.49319052696228</v>
       </c>
       <c r="H370" t="n">
         <v>198615</v>
@@ -11244,7 +11244,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G375" t="n">
-        <v>1.439337849617</v>
+        <v>1.43933773040771</v>
       </c>
       <c r="H375" t="n">
         <v>28060</v>
@@ -11360,7 +11360,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G379" t="n">
-        <v>1.48242008686066</v>
+        <v>1.48241996765137</v>
       </c>
       <c r="H379" t="n">
         <v>50853</v>
@@ -11418,7 +11418,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G381" t="n">
-        <v>1.46675360202789</v>
+        <v>1.46675372123718</v>
       </c>
       <c r="H381" t="n">
         <v>37418</v>
@@ -11795,7 +11795,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G394" t="n">
-        <v>1.38744330406189</v>
+        <v>1.3874431848526</v>
       </c>
       <c r="H394" t="n">
         <v>3217</v>
@@ -11882,7 +11882,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G397" t="n">
-        <v>1.46675360202789</v>
+        <v>1.46675372123718</v>
       </c>
       <c r="H397" t="n">
         <v>146942</v>
@@ -12288,7 +12288,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G411" t="n">
-        <v>1.49416959285736</v>
+        <v>1.49416971206665</v>
       </c>
       <c r="H411" t="n">
         <v>33895</v>
@@ -12491,7 +12491,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G418" t="n">
-        <v>1.88974273204803</v>
+        <v>1.88974261283875</v>
       </c>
       <c r="H418" t="n">
         <v>296041</v>
@@ -12549,7 +12549,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G420" t="n">
-        <v>1.94261634349823</v>
+        <v>1.94261622428894</v>
       </c>
       <c r="H420" t="n">
         <v>376100</v>
@@ -12636,7 +12636,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G423" t="n">
-        <v>1.88974273204803</v>
+        <v>1.88974261283875</v>
       </c>
       <c r="H423" t="n">
         <v>81649</v>
@@ -12694,7 +12694,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G425" t="n">
-        <v>2.165860414505</v>
+        <v>2.16586065292358</v>
       </c>
       <c r="H425" t="n">
         <v>662427</v>
@@ -12723,7 +12723,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>2.10515403747559</v>
+        <v>2.10515379905701</v>
       </c>
       <c r="H426" t="n">
         <v>303943</v>
@@ -12897,7 +12897,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G432" t="n">
-        <v>2.08361291885376</v>
+        <v>2.08361268043518</v>
       </c>
       <c r="H432" t="n">
         <v>120592</v>
@@ -12984,7 +12984,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G435" t="n">
-        <v>2.25398349761963</v>
+        <v>2.25398325920105</v>
       </c>
       <c r="H435" t="n">
         <v>446100</v>
@@ -13071,7 +13071,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G438" t="n">
-        <v>2.03857231140137</v>
+        <v>2.03857207298279</v>
       </c>
       <c r="H438" t="n">
         <v>376904</v>
@@ -13303,7 +13303,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G446" t="n">
-        <v>1.93086659908295</v>
+        <v>1.93086671829224</v>
       </c>
       <c r="H446" t="n">
         <v>226358</v>
@@ -13448,7 +13448,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G451" t="n">
-        <v>2.0150728225708</v>
+        <v>2.01507306098938</v>
       </c>
       <c r="H451" t="n">
         <v>124152</v>
@@ -13477,7 +13477,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G452" t="n">
-        <v>2.0150728225708</v>
+        <v>2.01507306098938</v>
       </c>
       <c r="H452" t="n">
         <v>122037</v>
@@ -13535,7 +13535,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G454" t="n">
-        <v>1.98569869995117</v>
+        <v>1.98569881916046</v>
       </c>
       <c r="H454" t="n">
         <v>31437</v>
@@ -13593,7 +13593,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G456" t="n">
-        <v>2.00723958015442</v>
+        <v>2.007239818573</v>
       </c>
       <c r="H456" t="n">
         <v>34457</v>
@@ -13622,7 +13622,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G457" t="n">
-        <v>2.0150728225708</v>
+        <v>2.01507306098938</v>
       </c>
       <c r="H457" t="n">
         <v>166275</v>
@@ -13738,7 +13738,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G461" t="n">
-        <v>1.98374044895172</v>
+        <v>1.98374032974243</v>
       </c>
       <c r="H461" t="n">
         <v>168464</v>
@@ -13767,7 +13767,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G462" t="n">
-        <v>1.95632433891296</v>
+        <v>1.95632445812225</v>
       </c>
       <c r="H462" t="n">
         <v>77596</v>
@@ -13825,7 +13825,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G464" t="n">
-        <v>1.98569869995117</v>
+        <v>1.98569881916046</v>
       </c>
       <c r="H464" t="n">
         <v>420317</v>
@@ -14144,7 +14144,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G475" t="n">
-        <v>1.93869984149933</v>
+        <v>1.93869972229004</v>
       </c>
       <c r="H475" t="n">
         <v>77792</v>
@@ -14463,7 +14463,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>1.93869984149933</v>
+        <v>1.93869972229004</v>
       </c>
       <c r="H486" t="n">
         <v>58282</v>
@@ -14550,7 +14550,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G489" t="n">
-        <v>2.05228018760681</v>
+        <v>2.05227994918823</v>
       </c>
       <c r="H489" t="n">
         <v>365431</v>
@@ -14579,7 +14579,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G490" t="n">
-        <v>2.00723958015442</v>
+        <v>2.007239818573</v>
       </c>
       <c r="H490" t="n">
         <v>127429</v>
@@ -14608,7 +14608,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G491" t="n">
-        <v>2.00723958015442</v>
+        <v>2.007239818573</v>
       </c>
       <c r="H491" t="n">
         <v>16967</v>
@@ -14869,7 +14869,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>1.9778653383255</v>
+        <v>1.97786545753479</v>
       </c>
       <c r="H500" t="n">
         <v>25172</v>
@@ -14898,7 +14898,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>1.9778653383255</v>
+        <v>1.97786545753479</v>
       </c>
       <c r="H501" t="n">
         <v>40934</v>
@@ -15101,7 +15101,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G508" t="n">
-        <v>1.93674147129059</v>
+        <v>1.93674159049988</v>
       </c>
       <c r="H508" t="n">
         <v>1738</v>
@@ -15246,7 +15246,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G513" t="n">
-        <v>1.89953422546387</v>
+        <v>1.89953410625458</v>
       </c>
       <c r="H513" t="n">
         <v>8507</v>
@@ -15333,7 +15333,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G516" t="n">
-        <v>1.9778653383255</v>
+        <v>1.97786545753479</v>
       </c>
       <c r="H516" t="n">
         <v>80856</v>
@@ -15507,7 +15507,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G522" t="n">
-        <v>1.95632433891296</v>
+        <v>1.95632445812225</v>
       </c>
       <c r="H522" t="n">
         <v>18050</v>
@@ -15536,7 +15536,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G523" t="n">
-        <v>1.96807408332825</v>
+        <v>1.96807396411896</v>
       </c>
       <c r="H523" t="n">
         <v>20616</v>
@@ -15623,7 +15623,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G526" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H526" t="n">
         <v>452689</v>
@@ -15942,7 +15942,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.10515403747559</v>
+        <v>2.10515379905701</v>
       </c>
       <c r="H537" t="n">
         <v>139101</v>
@@ -15971,7 +15971,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>2.10515403747559</v>
+        <v>2.10515379905701</v>
       </c>
       <c r="H538" t="n">
         <v>48637</v>
@@ -16058,7 +16058,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G541" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H541" t="n">
         <v>177454</v>
@@ -16087,7 +16087,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H542" t="n">
         <v>49635</v>
@@ -16145,7 +16145,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G544" t="n">
-        <v>2.18348526954651</v>
+        <v>2.18348503112793</v>
       </c>
       <c r="H544" t="n">
         <v>46864</v>
@@ -16203,7 +16203,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G546" t="n">
-        <v>2.19817209243774</v>
+        <v>2.19817233085632</v>
       </c>
       <c r="H546" t="n">
         <v>50060</v>
@@ -16232,7 +16232,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G547" t="n">
-        <v>2.18348526954651</v>
+        <v>2.18348503112793</v>
       </c>
       <c r="H547" t="n">
         <v>16948</v>
@@ -16261,7 +16261,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G548" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H548" t="n">
         <v>72087</v>
@@ -16319,7 +16319,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G550" t="n">
-        <v>2.19327640533447</v>
+        <v>2.19327664375305</v>
       </c>
       <c r="H550" t="n">
         <v>215281</v>
@@ -16348,7 +16348,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G551" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H551" t="n">
         <v>27372</v>
@@ -16377,7 +16377,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>2.17369389533997</v>
+        <v>2.17369365692139</v>
       </c>
       <c r="H552" t="n">
         <v>17856</v>
@@ -80212,6 +80212,35 @@
         <v>28896</v>
       </c>
       <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>1.8639999628067</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>1.85000002384186</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>1.8639999628067</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>1.8639999628067</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>13493</v>
+      </c>
+      <c r="I2754" t="s">
         <v>9</v>
       </c>
     </row>
